--- a/data.xlsx
+++ b/data.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m2610025/Desktop/チェックイン/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{272141D1-D529-074A-9197-5FF968C50845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910163A6-FDB4-9247-BE43-7940A34242C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="940" yWindow="1160" windowWidth="27900" windowHeight="16760" xr2:uid="{348E8972-E72E-5A4B-9183-B2C2B4112549}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="89">
   <si>
     <t>近江弘翔</t>
   </si>
@@ -310,6 +310,24 @@
     </rPh>
     <rPh sb="3" eb="4">
       <t xml:space="preserve">アカ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>綱引き青</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>競技名</t>
+    <rPh sb="0" eb="3">
+      <t>キョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>氏名</t>
+    <rPh sb="0" eb="2">
+      <t>🈯️</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -504,95 +522,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FFFFFFFF"/>
@@ -1011,24 +941,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E04C86-53A8-4C49-AB0F-61EBA36494D7}">
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" ht="21" thickBot="1">
       <c r="A1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>87</v>
+      </c>
+      <c r="B1" t="s">
+        <v>88</v>
       </c>
       <c r="C1" s="6"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
+        <v>86</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="C2" s="2"/>
     </row>
@@ -1037,7 +967,7 @@
         <v>84</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2"/>
     </row>
@@ -1046,7 +976,7 @@
         <v>84</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2"/>
     </row>
@@ -1055,7 +985,7 @@
         <v>84</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2"/>
     </row>
@@ -1064,7 +994,7 @@
         <v>84</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2"/>
     </row>
@@ -1073,7 +1003,7 @@
         <v>84</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2"/>
     </row>
@@ -1082,7 +1012,7 @@
         <v>84</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C8" s="2"/>
     </row>
@@ -1091,7 +1021,7 @@
         <v>84</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C9" s="2"/>
     </row>
@@ -1100,7 +1030,7 @@
         <v>84</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" s="2"/>
     </row>
@@ -1109,7 +1039,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C11" s="2"/>
     </row>
@@ -1118,7 +1048,7 @@
         <v>84</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C12" s="2"/>
     </row>
@@ -1127,7 +1057,7 @@
         <v>84</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C13" s="2"/>
     </row>
@@ -1136,7 +1066,7 @@
         <v>84</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C14" s="2"/>
     </row>
@@ -1145,7 +1075,7 @@
         <v>84</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C15" s="2"/>
     </row>
@@ -1154,7 +1084,7 @@
         <v>84</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C16" s="2"/>
     </row>
@@ -1163,7 +1093,7 @@
         <v>84</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C17" s="2"/>
     </row>
@@ -1172,7 +1102,7 @@
         <v>84</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C18" s="3"/>
     </row>
@@ -1181,7 +1111,7 @@
         <v>84</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C19" s="3"/>
     </row>
@@ -1190,7 +1120,7 @@
         <v>84</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C20" s="3"/>
     </row>
@@ -1198,25 +1128,25 @@
       <c r="A21" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="5"/>
+    </row>
+    <row r="22" spans="1:3" ht="21" thickBot="1">
+      <c r="A22" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="C21" s="5"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>84</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>84</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>2</v>
+      <c r="B23" s="6" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1224,7 +1154,7 @@
         <v>84</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1232,7 +1162,7 @@
         <v>84</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1240,7 +1170,7 @@
         <v>84</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1248,7 +1178,7 @@
         <v>84</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1256,7 +1186,7 @@
         <v>84</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1264,7 +1194,7 @@
         <v>84</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1272,7 +1202,7 @@
         <v>84</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1280,7 +1210,7 @@
         <v>84</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1288,7 +1218,7 @@
         <v>84</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1296,7 +1226,7 @@
         <v>84</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1304,7 +1234,7 @@
         <v>84</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1312,7 +1242,7 @@
         <v>84</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1320,7 +1250,7 @@
         <v>84</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1328,7 +1258,7 @@
         <v>84</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1336,15 +1266,15 @@
         <v>84</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>84</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>34</v>
+      <c r="B39" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1352,7 +1282,7 @@
         <v>84</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1360,23 +1290,23 @@
         <v>84</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>84</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="21" thickBot="1">
-      <c r="A42" t="s">
-        <v>84</v>
-      </c>
-      <c r="B42" s="5" t="s">
+    <row r="43" spans="1:3" ht="21" thickBot="1">
+      <c r="A43" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
-        <v>85</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>42</v>
       </c>
       <c r="C43" s="7"/>
     </row>
@@ -1385,7 +1315,7 @@
         <v>85</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C44" s="7"/>
     </row>
@@ -1394,7 +1324,7 @@
         <v>85</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C45" s="7"/>
     </row>
@@ -1403,7 +1333,7 @@
         <v>85</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C46" s="7"/>
     </row>
@@ -1412,7 +1342,7 @@
         <v>85</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C47" s="7"/>
     </row>
@@ -1421,7 +1351,7 @@
         <v>85</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C48" s="7"/>
     </row>
@@ -1430,7 +1360,7 @@
         <v>85</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C49" s="7"/>
     </row>
@@ -1439,7 +1369,7 @@
         <v>85</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C50" s="7"/>
     </row>
@@ -1448,7 +1378,7 @@
         <v>85</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C51" s="7"/>
     </row>
@@ -1457,7 +1387,7 @@
         <v>85</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C52" s="7"/>
     </row>
@@ -1466,7 +1396,7 @@
         <v>85</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C53" s="7"/>
     </row>
@@ -1475,7 +1405,7 @@
         <v>85</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C54" s="7"/>
     </row>
@@ -1484,7 +1414,7 @@
         <v>85</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C55" s="7"/>
     </row>
@@ -1493,7 +1423,7 @@
         <v>85</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C56" s="7"/>
     </row>
@@ -1502,7 +1432,7 @@
         <v>85</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C57" s="7"/>
     </row>
@@ -1511,7 +1441,7 @@
         <v>85</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C58" s="7"/>
     </row>
@@ -1520,7 +1450,7 @@
         <v>85</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C59" s="7"/>
     </row>
@@ -1529,7 +1459,7 @@
         <v>85</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C60" s="7"/>
     </row>
@@ -1538,7 +1468,7 @@
         <v>85</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C61" s="7"/>
     </row>
@@ -1547,7 +1477,7 @@
         <v>85</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C62" s="7"/>
     </row>
@@ -1555,17 +1485,17 @@
       <c r="A63" t="s">
         <v>85</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C63" s="8"/>
+    </row>
+    <row r="64" spans="1:3" ht="21" thickBot="1">
+      <c r="A64" t="s">
+        <v>85</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>82</v>
-      </c>
-      <c r="C63" s="8"/>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" t="s">
-        <v>85</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1573,7 +1503,7 @@
         <v>85</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1581,7 +1511,7 @@
         <v>85</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1589,7 +1519,7 @@
         <v>85</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1597,7 +1527,7 @@
         <v>85</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1605,7 +1535,7 @@
         <v>85</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1613,7 +1543,7 @@
         <v>85</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1621,7 +1551,7 @@
         <v>85</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1629,7 +1559,7 @@
         <v>85</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1637,7 +1567,7 @@
         <v>85</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1645,7 +1575,7 @@
         <v>85</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1653,7 +1583,7 @@
         <v>85</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1661,7 +1591,7 @@
         <v>85</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1669,7 +1599,7 @@
         <v>85</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1677,7 +1607,7 @@
         <v>85</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1685,7 +1615,7 @@
         <v>85</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1693,7 +1623,7 @@
         <v>85</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1701,7 +1631,7 @@
         <v>85</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1709,7 +1639,7 @@
         <v>85</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1717,62 +1647,42 @@
         <v>85</v>
       </c>
       <c r="B83" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>85</v>
+      </c>
+      <c r="B84" s="7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="21" thickBot="1">
-      <c r="A84" t="s">
-        <v>85</v>
-      </c>
-      <c r="B84" s="8" t="s">
+    <row r="85" spans="1:2" ht="21" thickBot="1">
+      <c r="A85" t="s">
+        <v>85</v>
+      </c>
+      <c r="B85" s="8" t="s">
         <v>83</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B1:C21">
-    <cfRule type="cellIs" dxfId="15" priority="13" operator="equal">
+  <conditionalFormatting sqref="C1:C21 C43:C63 B2:B64">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
       <formula>"赤団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
       <formula>"青団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="11" operator="equal">
       <formula>"黄団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="12" operator="equal">
       <formula>"黒団"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B22:B42">
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
-      <formula>"赤団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
-      <formula>"青団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
-      <formula>"黄団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
-      <formula>"黒団"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B43:C63">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
-      <formula>"赤団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
-      <formula>"青団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
-      <formula>"黄団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
-      <formula>"黒団"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B64:B84">
+  <conditionalFormatting sqref="B65:B85">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"赤団"</formula>
     </cfRule>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m2610025/Desktop/チェックイン/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D01186B-9648-4444-A59E-D93844756500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7757B1C-EBD2-FB41-B6CF-67E97DBE420F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{348E8972-E72E-5A4B-9183-B2C2B4112549}"/>
   </bookViews>
@@ -1561,15 +1561,15 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="9">
     <dxf>
       <font>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
+          <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF0000FF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1590,27 +1590,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFFF0000"/>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="8"/>
-          <bgColor theme="8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1626,555 +1607,10 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="8"/>
           <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="8"/>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="8"/>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="8"/>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="8"/>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="8"/>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="8"/>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="8"/>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="8"/>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="8"/>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5519,227 +4955,35 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="C1:C21 C43:C63">
-    <cfRule type="cellIs" dxfId="62" priority="64" operator="equal">
+  <conditionalFormatting sqref="B2:B344">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"赤団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="65" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"青団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
       <formula>"黄団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="67" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>"黒団"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B36">
-    <cfRule type="expression" dxfId="54" priority="55">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>COUNTIF(INDIRECT("綱引き!A:Z"),B2)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B36">
-    <cfRule type="cellIs" dxfId="53" priority="51" operator="equal">
+  <conditionalFormatting sqref="C1:C21 C43:C63">
+    <cfRule type="cellIs" dxfId="3" priority="67" operator="equal">
+      <formula>"黒団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="64" operator="equal">
       <formula>"赤団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="52" operator="equal">
-      <formula>"青団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="66" operator="equal">
       <formula>"黄団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="54" operator="equal">
-      <formula>"黒団"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B37:B71">
-    <cfRule type="expression" dxfId="49" priority="50">
-      <formula>COUNTIF(INDIRECT("綱引き!A:Z"),B37)&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B37:B71">
-    <cfRule type="cellIs" dxfId="48" priority="46" operator="equal">
-      <formula>"赤団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="65" operator="equal">
       <formula>"青団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="48" operator="equal">
-      <formula>"黄団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="49" operator="equal">
-      <formula>"黒団"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B72:B106">
-    <cfRule type="expression" dxfId="44" priority="45">
-      <formula>COUNTIF(INDIRECT("綱引き!A:Z"),B72)&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B72:B106">
-    <cfRule type="cellIs" dxfId="43" priority="41" operator="equal">
-      <formula>"赤団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="42" operator="equal">
-      <formula>"青団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="43" operator="equal">
-      <formula>"黄団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="44" operator="equal">
-      <formula>"黒団"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B107:B141">
-    <cfRule type="expression" dxfId="39" priority="40">
-      <formula>COUNTIF(INDIRECT("綱引き!A:Z"),B107)&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B107:B141">
-    <cfRule type="cellIs" dxfId="38" priority="36" operator="equal">
-      <formula>"赤団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="37" operator="equal">
-      <formula>"青団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="38" operator="equal">
-      <formula>"黄団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="39" operator="equal">
-      <formula>"黒団"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B142:B176">
-    <cfRule type="expression" dxfId="34" priority="35">
-      <formula>COUNTIF(INDIRECT("綱引き!A:Z"),B142)&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B142:B176">
-    <cfRule type="cellIs" dxfId="33" priority="31" operator="equal">
-      <formula>"赤団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="32" operator="equal">
-      <formula>"青団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="33" operator="equal">
-      <formula>"黄団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="34" operator="equal">
-      <formula>"黒団"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B177:B211">
-    <cfRule type="expression" dxfId="29" priority="30">
-      <formula>COUNTIF(INDIRECT("綱引き!A:Z"),B177)&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B177:B211">
-    <cfRule type="cellIs" dxfId="28" priority="26" operator="equal">
-      <formula>"赤団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="27" operator="equal">
-      <formula>"青団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="28" operator="equal">
-      <formula>"黄団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="29" operator="equal">
-      <formula>"黒団"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B212:B246">
-    <cfRule type="expression" dxfId="24" priority="25">
-      <formula>COUNTIF(INDIRECT("綱引き!A:Z"),B212)&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B212:B246">
-    <cfRule type="cellIs" dxfId="23" priority="21" operator="equal">
-      <formula>"赤団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="22" operator="equal">
-      <formula>"青団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="23" operator="equal">
-      <formula>"黄団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="24" operator="equal">
-      <formula>"黒団"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B247:B281">
-    <cfRule type="expression" dxfId="19" priority="20">
-      <formula>COUNTIF(INDIRECT("綱引き!A:Z"),B247)&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B247:B281">
-    <cfRule type="cellIs" dxfId="18" priority="16" operator="equal">
-      <formula>"赤団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="17" operator="equal">
-      <formula>"青団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
-      <formula>"黄団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="19" operator="equal">
-      <formula>"黒団"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B282:B302">
-    <cfRule type="expression" dxfId="14" priority="15">
-      <formula>COUNTIF(INDIRECT("綱引き!A:Z"),B282)&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B282:B302">
-    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
-      <formula>"赤団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
-      <formula>"青団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
-      <formula>"黄団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="14" operator="equal">
-      <formula>"黒団"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B303:B323">
-    <cfRule type="expression" dxfId="9" priority="10">
-      <formula>COUNTIF(INDIRECT("綱引き!A:Z"),B303)&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B303:B323">
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
-      <formula>"赤団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
-      <formula>"青団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
-      <formula>"黄団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
-      <formula>"黒団"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B324:B344">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>COUNTIF(INDIRECT("綱引き!A:Z"),B324)&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B324:B344">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>"赤団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
-      <formula>"青団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
-      <formula>"黄団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
-      <formula>"黒団"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m2610025/Desktop/チェックイン/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7757B1C-EBD2-FB41-B6CF-67E97DBE420F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEF8E3EC-9B56-4045-8306-1A6C80F6428B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{348E8972-E72E-5A4B-9183-B2C2B4112549}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="561">
   <si>
     <t>澤田七聖</t>
   </si>
@@ -1276,12 +1276,611 @@
   <si>
     <t>中島のの愛</t>
   </si>
+  <si>
+    <t>藤田セス和登</t>
+  </si>
+  <si>
+    <t>水嶋謙一郎</t>
+  </si>
+  <si>
+    <t>飯田歩夢</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">戸田悠心 </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>梅津俊壱</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小薗宗一郎</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中松英資</t>
+  </si>
+  <si>
+    <t>井上嘉希 </t>
+  </si>
+  <si>
+    <t>青木 七音 </t>
+  </si>
+  <si>
+    <t>藤原惺也 </t>
+  </si>
+  <si>
+    <t>市村心咲 </t>
+  </si>
+  <si>
+    <t>北川颯章 </t>
+  </si>
+  <si>
+    <t>西本 圭佑 </t>
+  </si>
+  <si>
+    <t>伊藤 悠木 </t>
+  </si>
+  <si>
+    <t>稲童丸怜 </t>
+  </si>
+  <si>
+    <t>山本みのり </t>
+  </si>
+  <si>
+    <t>小川 智由 </t>
+  </si>
+  <si>
+    <t>福元佑征 </t>
+  </si>
+  <si>
+    <t>山森瑛太 </t>
+  </si>
+  <si>
+    <t>井畑 奏人 </t>
+  </si>
+  <si>
+    <t>日下 遥斗 </t>
+  </si>
+  <si>
+    <t>森遥 来仁 </t>
+  </si>
+  <si>
+    <t>井上 玲音 </t>
+  </si>
+  <si>
+    <t>小猿 健太郎 </t>
+  </si>
+  <si>
+    <t>梶健留 </t>
+  </si>
+  <si>
+    <t>松本 悠聖 </t>
+  </si>
+  <si>
+    <t>橋目 龍之介</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ハシメ </t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>🐉</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t xml:space="preserve">ノスケ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上野 圭太</t>
+  </si>
+  <si>
+    <t>中尾 優仁</t>
+  </si>
+  <si>
+    <t>濱中美侑</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>五十嵐晃太</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>皆川 蒼斗</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>川手 智裕</t>
+  </si>
+  <si>
+    <t>吉海夏凪</t>
+  </si>
+  <si>
+    <t>平沼心結</t>
+  </si>
+  <si>
+    <t>長谷川結愛</t>
+  </si>
+  <si>
+    <t>斉藤 綾乃</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>八藤丸颯太</t>
+  </si>
+  <si>
+    <t>細井琴葉</t>
+  </si>
+  <si>
+    <t>門田愛奈</t>
+  </si>
+  <si>
+    <t>上原　颯太郎</t>
+  </si>
+  <si>
+    <t>杉本 和香奈</t>
+  </si>
+  <si>
+    <t>村上遼介</t>
+  </si>
+  <si>
+    <t>大継悠日</t>
+  </si>
+  <si>
+    <t>前佛祐介</t>
+  </si>
+  <si>
+    <t>坂下　登大</t>
+  </si>
+  <si>
+    <t>竹内 凛太郎</t>
+  </si>
+  <si>
+    <t>井用みのり</t>
+  </si>
+  <si>
+    <t>田中颯人</t>
+  </si>
+  <si>
+    <t>掘出駿</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>片桐渚沙</t>
+  </si>
+  <si>
+    <t>日下 由菜</t>
+  </si>
+  <si>
+    <t>藤田智樹</t>
+  </si>
+  <si>
+    <t>高橋碧</t>
+  </si>
+  <si>
+    <t>石田克希</t>
+  </si>
+  <si>
+    <t>五味駿太朗</t>
+  </si>
+  <si>
+    <t>苅谷 美咲</t>
+  </si>
+  <si>
+    <t>森中啓仁</t>
+  </si>
+  <si>
+    <t>徳田拓夢</t>
+  </si>
+  <si>
+    <t>上野あゆ美</t>
+  </si>
+  <si>
+    <t>井出 駿人</t>
+  </si>
+  <si>
+    <t>伊藤 胡花</t>
+  </si>
+  <si>
+    <t>池尻煌人</t>
+  </si>
+  <si>
+    <t>石川蒼真</t>
+  </si>
+  <si>
+    <t>藤田洸太</t>
+  </si>
+  <si>
+    <t>美濃昂幸</t>
+  </si>
+  <si>
+    <t>松井蓮太郎</t>
+  </si>
+  <si>
+    <t>宮田 櫂</t>
+  </si>
+  <si>
+    <t>森本詩史</t>
+  </si>
+  <si>
+    <t>越野 紗良</t>
+  </si>
+  <si>
+    <t>久保田 航生</t>
+  </si>
+  <si>
+    <t>矢野天心</t>
+  </si>
+  <si>
+    <t>前田旺佑</t>
+  </si>
+  <si>
+    <t>村井 大和</t>
+  </si>
+  <si>
+    <t>安田 悠乃</t>
+  </si>
+  <si>
+    <t>下田 湧生</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>浅川瞬生</t>
+  </si>
+  <si>
+    <t>藤川 結灯</t>
+  </si>
+  <si>
+    <t>竹末 亘志</t>
+  </si>
+  <si>
+    <t>藤谷沙希</t>
+  </si>
+  <si>
+    <t>青木悠鈍</t>
+  </si>
+  <si>
+    <t>小曽戸大聖</t>
+  </si>
+  <si>
+    <t>前川 大和</t>
+  </si>
+  <si>
+    <t>下堂 聖真</t>
+  </si>
+  <si>
+    <t>柴原貴橙</t>
+  </si>
+  <si>
+    <t>木場優征</t>
+  </si>
+  <si>
+    <t>太田悠佑</t>
+  </si>
+  <si>
+    <t>木村圭都</t>
+  </si>
+  <si>
+    <t>本郷 隆太</t>
+  </si>
+  <si>
+    <t>三崎淳平</t>
+  </si>
+  <si>
+    <t>羽山 和希</t>
+  </si>
+  <si>
+    <t>津田 翔馬</t>
+  </si>
+  <si>
+    <t>香山諒太</t>
+  </si>
+  <si>
+    <t>長嶋 優衣</t>
+  </si>
+  <si>
+    <t>高木柚</t>
+  </si>
+  <si>
+    <t>及川 智大</t>
+  </si>
+  <si>
+    <t>山中  雅貴</t>
+  </si>
+  <si>
+    <t>山本賢汰</t>
+  </si>
+  <si>
+    <t>吉田 和生</t>
+  </si>
+  <si>
+    <t>倉橋一葉</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>八鍬 莉空</t>
+  </si>
+  <si>
+    <t>橋本 解</t>
+  </si>
+  <si>
+    <t>サンティ</t>
+  </si>
+  <si>
+    <t>梅本 夏帆</t>
+  </si>
+  <si>
+    <t>舟橋千隼</t>
+  </si>
+  <si>
+    <t>水野 颯仁</t>
+  </si>
+  <si>
+    <t>水口 諦</t>
+  </si>
+  <si>
+    <t>越智 太靖</t>
+  </si>
+  <si>
+    <t>小林 咲登</t>
+  </si>
+  <si>
+    <t>赤壁朋果</t>
+  </si>
+  <si>
+    <t>木村 駿杜</t>
+  </si>
+  <si>
+    <t>今井千瑛</t>
+  </si>
+  <si>
+    <t>窪田 莉子</t>
+  </si>
+  <si>
+    <t>中島咲桜</t>
+  </si>
+  <si>
+    <t>コリア</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>石崎 脩也</t>
+  </si>
+  <si>
+    <t>藤田彩香</t>
+  </si>
+  <si>
+    <t>相川 翔太郎</t>
+  </si>
+  <si>
+    <t>細岡大起</t>
+  </si>
+  <si>
+    <t>内田 雄貴</t>
+  </si>
+  <si>
+    <t>山﨑 彰大</t>
+  </si>
+  <si>
+    <t>前波花香</t>
+  </si>
+  <si>
+    <t>林田 一真</t>
+  </si>
+  <si>
+    <t>星川快鋳</t>
+  </si>
+  <si>
+    <t>山本 敦</t>
+  </si>
+  <si>
+    <t>西村大</t>
+  </si>
+  <si>
+    <t>成田惺真</t>
+  </si>
+  <si>
+    <t>能勢 陸斗</t>
+  </si>
+  <si>
+    <t>古川桃子</t>
+  </si>
+  <si>
+    <t>蒔田 大椰</t>
+  </si>
+  <si>
+    <t>村上 律</t>
+  </si>
+  <si>
+    <t>奥村知隼</t>
+  </si>
+  <si>
+    <t>石田 歩夢</t>
+  </si>
+  <si>
+    <t>小林咲</t>
+  </si>
+  <si>
+    <t>篠原 大悟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">長谷 悠生 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">前川 大祐 </t>
+  </si>
+  <si>
+    <t>相坂 明里</t>
+  </si>
+  <si>
+    <t>松岡 健太郎</t>
+  </si>
+  <si>
+    <t>小林翔大</t>
+  </si>
+  <si>
+    <t>熊谷蘭武</t>
+  </si>
+  <si>
+    <t xml:space="preserve">奥野智貴 </t>
+  </si>
+  <si>
+    <t>山中萌衣</t>
+  </si>
+  <si>
+    <t>中西倫子</t>
+  </si>
+  <si>
+    <t>瀧口隼</t>
+  </si>
+  <si>
+    <t>若松 咲月</t>
+  </si>
+  <si>
+    <t>伊藤 大晴</t>
+  </si>
+  <si>
+    <t>向所杏笑</t>
+  </si>
+  <si>
+    <t>田畑鷹悠</t>
+  </si>
+  <si>
+    <t>中野睦斗</t>
+  </si>
+  <si>
+    <t>西下洸太朗</t>
+  </si>
+  <si>
+    <t>渡辺柊有</t>
+  </si>
+  <si>
+    <t>山口翔雅</t>
+  </si>
+  <si>
+    <t>橋本春</t>
+  </si>
+  <si>
+    <t>平岡陸</t>
+  </si>
+  <si>
+    <t>大西勇毅</t>
+  </si>
+  <si>
+    <t>逢坂柊真</t>
+  </si>
+  <si>
+    <t>有田駈</t>
+  </si>
+  <si>
+    <t>廣田昇大</t>
+  </si>
+  <si>
+    <t>坂井康介</t>
+  </si>
+  <si>
+    <t>船富 遥斗</t>
+  </si>
+  <si>
+    <t>岡田 蒼介</t>
+  </si>
+  <si>
+    <t>石山詢人</t>
+  </si>
+  <si>
+    <t>杉本優太郎</t>
+  </si>
+  <si>
+    <t>真木洋斗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">増井 一太 </t>
+  </si>
+  <si>
+    <t>佐野 智優希</t>
+  </si>
+  <si>
+    <t>関隼太郎</t>
+  </si>
+  <si>
+    <t>前地遼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">笠井 遥紀 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">土井 翔太郎 </t>
+  </si>
+  <si>
+    <t>早川柊</t>
+  </si>
+  <si>
+    <t>木村晴樹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">石田 迅 </t>
+  </si>
+  <si>
+    <t>伊藤 鴻甫</t>
+  </si>
+  <si>
+    <t>中野蒼司</t>
+  </si>
+  <si>
+    <t>野島大輝</t>
+  </si>
+  <si>
+    <t>鈎慈玖</t>
+  </si>
+  <si>
+    <t>障害物競走・赤団</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">ショウガイブツ </t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t xml:space="preserve">キョウソウ </t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">アカダン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>障害物競走・青団</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ショウガイブツキョウソウ </t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">アオダン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>障害物競走・黄団</t>
+    <rPh sb="0" eb="5">
+      <t xml:space="preserve">ショウガイブツキョウソウ </t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>障害物競走・黒団</t>
+    <rPh sb="0" eb="5">
+      <t>ショウガイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">クロダン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1343,6 +1942,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1352,7 +1974,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1493,13 +2115,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1557,19 +2194,37 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="21">
     <dxf>
       <font>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1581,6 +2236,17 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF0000FF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1603,6 +2269,127 @@
         <patternFill patternType="solid">
           <fgColor rgb="FF000000"/>
           <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF0000FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF0000FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF0000FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1988,7 +2775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E04C86-53A8-4C49-AB0F-61EBA36494D7}">
-  <dimension ref="A1:C365"/>
+  <dimension ref="A1:C553"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
     <row r="1" spans="1:3" ht="21" thickBot="1">
@@ -4953,37 +5740,1543 @@
         <v>378</v>
       </c>
     </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B366" s="19" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B367" s="19" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B368" s="19" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B369" s="19" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B370" s="19" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B371" s="19" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B372" s="19" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B373" s="19" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B374" s="19" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B375" s="19" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B376" s="19" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B377" s="19" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B378" s="19" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B379" s="19" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B380" s="19" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B381" s="19" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B382" s="19" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B383" s="19" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B384" s="19" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B385" s="19" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B386" s="19" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B387" s="19" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B388" s="19" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B389" s="19" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B390" s="19" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B391" s="20" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B392" s="20" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B393" s="20" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B394" s="20" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B395" s="20" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B396" s="20" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B397" s="20" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B398" s="20" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B399" s="20" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B400" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B401" s="21" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B402" s="21" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B403" s="21" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B404" s="21" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B405" s="21" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B406" s="21" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B407" s="21" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B408" s="21" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B409" s="21" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B410" s="21" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B411" s="21" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B412" s="21" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B413" s="21" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B414" s="21" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B415" s="21" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B416" s="21" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B417" s="21" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B418" s="21" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B419" s="21" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B420" s="21" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B421" s="21" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B422" s="21" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B423" s="21" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B424" s="21" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B425" s="21" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B426" s="22" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B427" s="22" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B428" s="22" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B429" s="22" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B430" s="22" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B431" s="22" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B432" s="20" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B433" s="22" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B434" s="22" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B435" s="22" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B436" s="22" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B437" s="22" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B438" s="22" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B439" s="22" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B440" s="22" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B441" s="21" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B442" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B443" s="21" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B444" s="21" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B445" s="21" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B446" s="21" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B447" s="21" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B448" s="21" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B449" s="21" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B450" s="21" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B451" s="21" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B452" s="21" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B453" s="21" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B454" s="21" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B455" s="21" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B456" s="21" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B457" s="21" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B458" s="21" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B459" s="21" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B460" s="21" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B461" s="21" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B462" s="21" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B463" s="21" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B464" s="21" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B465" s="21" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B466" s="21" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B467" s="21" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B468" s="21" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B469" s="21" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B470" s="21" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B471" s="21" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B472" s="21" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B473" s="21" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B474" s="21" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B475" s="21" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B476" s="21" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B477" s="21" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B478" s="21" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B479" s="21" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B480" s="21" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B481" s="21" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B482" s="21" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B483" s="21" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B484" s="21" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B485" s="21" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B486" s="21" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B487" s="21" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B488" s="21" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B489" s="21" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B490" s="21" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B491" s="21" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B492" s="21" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B493" s="21" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B494" s="21" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B495" s="21" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B496" s="21" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B497" s="21" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B498" s="21" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B499" s="21" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B500" s="21" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B501" s="21" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B502" s="21" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B503" s="21" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B504" s="21" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B505" s="21" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B506" s="21" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B507" s="21" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B508" s="21" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B509" s="21" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B510" s="21" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B511" s="21" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B512" s="21" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B513" s="21" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B514" s="21" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B515" s="21" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B516" s="22" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B517" s="22" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B518" s="22" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B519" s="22" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B520" s="22" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B521" s="22" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B522" s="22" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B523" s="22" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B524" s="22" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B525" s="22" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B526" s="21" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B527" s="21" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B528" s="21" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B529" s="21" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B530" s="21" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B531" s="21" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B532" s="21" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B533" s="21" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B534" s="21" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B535" s="21" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B536" s="21" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B537" s="21" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B538" s="21" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B539" s="21" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B540" s="21" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B541" s="21" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B542" s="21" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B543" s="21" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B544" s="21" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B545" s="21" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="B546" s="23"/>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="B547" s="23"/>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="B548" s="23"/>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="B549" s="23"/>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="B550" s="23"/>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="B551" s="23"/>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="B552" s="23"/>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="B553" s="23"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="B2:B344">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="38" operator="equal">
       <formula>"赤団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="39" operator="equal">
       <formula>"青団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="40" operator="equal">
       <formula>"黄団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="41" operator="equal">
       <formula>"黒団"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="16" priority="42">
       <formula>COUNTIF(INDIRECT("綱引き!A:Z"),B2)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C21 C43:C63">
-    <cfRule type="cellIs" dxfId="3" priority="67" operator="equal">
+  <conditionalFormatting sqref="B401:B425">
+    <cfRule type="cellIs" dxfId="15" priority="9" operator="equal">
+      <formula>"赤団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
+      <formula>"青団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
+      <formula>"黄団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
       <formula>"黒団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="64" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B441:B515">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
       <formula>"赤団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
+      <formula>"青団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
       <formula>"黄団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="65" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+      <formula>"黒団"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B526:B545">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+      <formula>"赤団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"青団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+      <formula>"黄団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+      <formula>"黒団"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C21 C43:C63">
+    <cfRule type="cellIs" dxfId="3" priority="101" operator="equal">
+      <formula>"赤団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="102" operator="equal">
+      <formula>"青団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="103" operator="equal">
+      <formula>"黄団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="104" operator="equal">
+      <formula>"黒団"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m2610025/Desktop/チェックイン/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEF8E3EC-9B56-4045-8306-1A6C80F6428B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8535496E-A28E-2D45-A9CB-BED2D612FD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{348E8972-E72E-5A4B-9183-B2C2B4112549}"/>
+    <workbookView xWindow="14680" yWindow="660" windowWidth="14720" windowHeight="18460" xr2:uid="{348E8972-E72E-5A4B-9183-B2C2B4112549}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="921">
   <si>
     <t>澤田七聖</t>
   </si>
@@ -1875,12 +1875,1151 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>団選抜リレー・赤団</t>
+  </si>
+  <si>
+    <t>岡田 理瑚</t>
+  </si>
+  <si>
+    <t>向井瑠海</t>
+  </si>
+  <si>
+    <t>中村滉志</t>
+  </si>
+  <si>
+    <t>岩本雪愛</t>
+  </si>
+  <si>
+    <t>岡本夏凛</t>
+  </si>
+  <si>
+    <t>中川結葵</t>
+  </si>
+  <si>
+    <t>根岸璃衣</t>
+  </si>
+  <si>
+    <t>井上栞那</t>
+  </si>
+  <si>
+    <t>堀川琉快</t>
+  </si>
+  <si>
+    <t>久保快翔</t>
+  </si>
+  <si>
+    <t>谷口楓</t>
+  </si>
+  <si>
+    <t>田内莉琴</t>
+  </si>
+  <si>
+    <t>村嶋彩日</t>
+  </si>
+  <si>
+    <t>三品遼音</t>
+  </si>
+  <si>
+    <t>神谷 幸輝</t>
+  </si>
+  <si>
+    <t>大西功都</t>
+  </si>
+  <si>
+    <t>辻柚香</t>
+  </si>
+  <si>
+    <t>西村太一</t>
+  </si>
+  <si>
+    <t>岸本大暉</t>
+  </si>
+  <si>
+    <t>由井陽斗</t>
+  </si>
+  <si>
+    <t>小薗宗一郎</t>
+  </si>
+  <si>
+    <t>岡本伊織</t>
+  </si>
+  <si>
+    <t>福永舞衣</t>
+  </si>
+  <si>
+    <t>中村謙吾</t>
+  </si>
+  <si>
+    <t>皆川蒼斗</t>
+  </si>
+  <si>
+    <t>熊谷 莉有</t>
+  </si>
+  <si>
+    <t>谷本真子</t>
+  </si>
+  <si>
+    <t>上之薗香帆</t>
+  </si>
+  <si>
+    <t>中林嶺佳</t>
+  </si>
+  <si>
+    <t>熊田結彩</t>
+  </si>
+  <si>
+    <t>奥村紗代</t>
+  </si>
+  <si>
+    <t>北川颯章</t>
+  </si>
+  <si>
+    <t>廣政孝太郎</t>
+  </si>
+  <si>
+    <t>中山萌衣</t>
+  </si>
+  <si>
+    <t>常峰祗園</t>
+  </si>
+  <si>
+    <t>片山陽</t>
+  </si>
+  <si>
+    <t>宇野宏紀</t>
+  </si>
+  <si>
+    <t>廣瀬 宗成</t>
+  </si>
+  <si>
+    <t>木村陸</t>
+  </si>
+  <si>
+    <t>永原拓真</t>
+  </si>
+  <si>
+    <t>濱田陸駆</t>
+  </si>
+  <si>
+    <t>吉岡将斗</t>
+  </si>
+  <si>
+    <t>松田一求</t>
+  </si>
+  <si>
+    <t>安原仁隆</t>
+  </si>
+  <si>
+    <t>石岡春蔵</t>
+  </si>
+  <si>
+    <t>栄口結愛</t>
+  </si>
+  <si>
+    <t>秦愛咲</t>
+  </si>
+  <si>
+    <t>小笠原啓太</t>
+  </si>
+  <si>
+    <t>足立晴太</t>
+  </si>
+  <si>
+    <t>団選抜リレー・青団</t>
+  </si>
+  <si>
+    <t>徳井凌太</t>
+  </si>
+  <si>
+    <t>日下由菜</t>
+  </si>
+  <si>
+    <t>片本真佳</t>
+  </si>
+  <si>
+    <t>奥野陽葵</t>
+  </si>
+  <si>
+    <t>林桃叶</t>
+  </si>
+  <si>
+    <t>渡邉煌士</t>
+  </si>
+  <si>
+    <t>山村王</t>
+  </si>
+  <si>
+    <t>川岡熙平</t>
+  </si>
+  <si>
+    <t>浅見陽香</t>
+  </si>
+  <si>
+    <t>井用あかり</t>
+  </si>
+  <si>
+    <t>藤井 彩友佳</t>
+  </si>
+  <si>
+    <t>中谷颯真</t>
+  </si>
+  <si>
+    <t>福嶋隼都</t>
+  </si>
+  <si>
+    <t>杉本陽</t>
+  </si>
+  <si>
+    <t>青木悠純</t>
+  </si>
+  <si>
+    <t>小島惟愛</t>
+  </si>
+  <si>
+    <t>Miki Schwarz</t>
+  </si>
+  <si>
+    <t>中嶋健登</t>
+  </si>
+  <si>
+    <t>橋本花凛</t>
+  </si>
+  <si>
+    <t>福井駿斗</t>
+  </si>
+  <si>
+    <t>谷本瑛汰</t>
+  </si>
+  <si>
+    <t>朝日千尋</t>
+  </si>
+  <si>
+    <t>丹野 凛緒</t>
+  </si>
+  <si>
+    <t>福田明里</t>
+  </si>
+  <si>
+    <t>岩永星南</t>
+  </si>
+  <si>
+    <t>田中健琉</t>
+  </si>
+  <si>
+    <t>木村真結奈</t>
+  </si>
+  <si>
+    <t>堀出駿</t>
+  </si>
+  <si>
+    <t>石田克季</t>
+  </si>
+  <si>
+    <t>上妻笑之祐</t>
+  </si>
+  <si>
+    <t>中田裕衣可</t>
+  </si>
+  <si>
+    <t>中前琴葉</t>
+  </si>
+  <si>
+    <t>安田悠乃</t>
+  </si>
+  <si>
+    <t>本郷隆太</t>
+  </si>
+  <si>
+    <t>岡田莉央</t>
+  </si>
+  <si>
+    <t>フースティング杏奈</t>
+  </si>
+  <si>
+    <t>木山凌汰</t>
+  </si>
+  <si>
+    <t>門田悠希</t>
+  </si>
+  <si>
+    <t>比木思結</t>
+  </si>
+  <si>
+    <t>兼平和季</t>
+  </si>
+  <si>
+    <t>岩崎航大</t>
+  </si>
+  <si>
+    <t>角田優斗</t>
+  </si>
+  <si>
+    <t>大林孝太朗</t>
+  </si>
+  <si>
+    <t>滝川康大</t>
+  </si>
+  <si>
+    <t>籔内梨琴</t>
+  </si>
+  <si>
+    <t>青木陽翔</t>
+  </si>
+  <si>
+    <t>大前 耀太郎</t>
+  </si>
+  <si>
+    <t>団選抜リレー・黄団</t>
+  </si>
+  <si>
+    <t>服部慶大</t>
+  </si>
+  <si>
+    <t>岡本菜優</t>
+  </si>
+  <si>
+    <t>田畑颯吾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">森口侑大 </t>
+  </si>
+  <si>
+    <t>竹中菜都希</t>
+  </si>
+  <si>
+    <t>宇野吏蘭</t>
+  </si>
+  <si>
+    <t>水口果音</t>
+  </si>
+  <si>
+    <t>村上尚哉</t>
+  </si>
+  <si>
+    <t>小川瑛太郎</t>
+  </si>
+  <si>
+    <t>下堂真緒</t>
+  </si>
+  <si>
+    <t>鳥居幹太</t>
+  </si>
+  <si>
+    <t>齋藤夢</t>
+  </si>
+  <si>
+    <t>門野澪良</t>
+  </si>
+  <si>
+    <t>長岡克興</t>
+  </si>
+  <si>
+    <t>倉橋一葉</t>
+  </si>
+  <si>
+    <t>土渕海</t>
+  </si>
+  <si>
+    <t>手塚愛結</t>
+  </si>
+  <si>
+    <t>杉山拓也</t>
+  </si>
+  <si>
+    <t>松井簾太朗</t>
+  </si>
+  <si>
+    <t>小笠原羚斗</t>
+  </si>
+  <si>
+    <t>小早川珀瑛</t>
+  </si>
+  <si>
+    <t>森永徳真</t>
+  </si>
+  <si>
+    <t>上野今日香</t>
+  </si>
+  <si>
+    <t>山崎聖流</t>
+  </si>
+  <si>
+    <t>森杉優輝</t>
+  </si>
+  <si>
+    <t>佐々木菜那</t>
+  </si>
+  <si>
+    <t>髙橋暖</t>
+  </si>
+  <si>
+    <t>河上桜輔</t>
+  </si>
+  <si>
+    <t>山中七海</t>
+  </si>
+  <si>
+    <t>石崎脩也</t>
+  </si>
+  <si>
+    <t>木村啓士朗</t>
+  </si>
+  <si>
+    <t>西村大輔</t>
+  </si>
+  <si>
+    <t>岡野志栞</t>
+  </si>
+  <si>
+    <t>坂上美依</t>
+  </si>
+  <si>
+    <t>西龍生</t>
+  </si>
+  <si>
+    <t>福島莉子</t>
+  </si>
+  <si>
+    <t>長谷川結子</t>
+  </si>
+  <si>
+    <t>木村彩夢</t>
+  </si>
+  <si>
+    <t>三村真由</t>
+  </si>
+  <si>
+    <t>長谷川大雅</t>
+  </si>
+  <si>
+    <t>宮本あん</t>
+  </si>
+  <si>
+    <t>西崎蓮</t>
+  </si>
+  <si>
+    <t>川西陽翔</t>
+  </si>
+  <si>
+    <t>元好拓真</t>
+  </si>
+  <si>
+    <t>山森 幹太</t>
+  </si>
+  <si>
+    <t>梶郁斗</t>
+  </si>
+  <si>
+    <t>辻陽菜</t>
+  </si>
+  <si>
+    <t>乾莉央</t>
+  </si>
+  <si>
+    <t>松原幸輝</t>
+  </si>
+  <si>
+    <t>増田遥哉</t>
+  </si>
+  <si>
+    <t>団選抜リレー・黒団</t>
+  </si>
+  <si>
+    <t>山西瑛人</t>
+  </si>
+  <si>
+    <t>島津柚花</t>
+  </si>
+  <si>
+    <t>薬師蓮</t>
+  </si>
+  <si>
+    <t>瀬戸口桜</t>
+  </si>
+  <si>
+    <t>下村圭吾</t>
+  </si>
+  <si>
+    <t>小森蓮生</t>
+  </si>
+  <si>
+    <t>上田芽愛</t>
+  </si>
+  <si>
+    <t>小山明日香</t>
+  </si>
+  <si>
+    <t>茶木陽良里</t>
+  </si>
+  <si>
+    <t>藤原拓海</t>
+  </si>
+  <si>
+    <t>本田胡桃</t>
+  </si>
+  <si>
+    <t>森玄親</t>
+  </si>
+  <si>
+    <t>前川綾音</t>
+  </si>
+  <si>
+    <t>稲ヶ部心夢</t>
+  </si>
+  <si>
+    <t xml:space="preserve">野中悠翔 </t>
+  </si>
+  <si>
+    <t>松井駿典</t>
+  </si>
+  <si>
+    <t>金岡大輔</t>
+  </si>
+  <si>
+    <t>原田唯菜</t>
+  </si>
+  <si>
+    <t>今井寛太</t>
+  </si>
+  <si>
+    <t>大崎真之介</t>
+  </si>
+  <si>
+    <t>藤原梨津</t>
+  </si>
+  <si>
+    <t>西川湊太</t>
+  </si>
+  <si>
+    <t>土屋遼人</t>
+  </si>
+  <si>
+    <t>松本寧々</t>
+  </si>
+  <si>
+    <t>小川二葉</t>
+  </si>
+  <si>
+    <t>駒井絵理奈</t>
+  </si>
+  <si>
+    <t xml:space="preserve">角恵里奈 </t>
+  </si>
+  <si>
+    <t>安澤秀哉</t>
+  </si>
+  <si>
+    <t>辻陽香</t>
+  </si>
+  <si>
+    <t>谷陽依</t>
+  </si>
+  <si>
+    <t>青木一悟</t>
+  </si>
+  <si>
+    <t>松尾亮佑</t>
+  </si>
+  <si>
+    <t>龍華天花</t>
+  </si>
+  <si>
+    <t>二村沙紀</t>
+  </si>
+  <si>
+    <t>門田悠佑</t>
+  </si>
+  <si>
+    <t>西山瑚々</t>
+  </si>
+  <si>
+    <t xml:space="preserve">丸山大海 </t>
+  </si>
+  <si>
+    <t>河村羽桜</t>
+  </si>
+  <si>
+    <t>中村海音</t>
+  </si>
+  <si>
+    <t>堀池梨央</t>
+  </si>
+  <si>
+    <t>高西真聖</t>
+  </si>
+  <si>
+    <t>夢田翔正</t>
+  </si>
+  <si>
+    <t>鈴木陽也</t>
+  </si>
+  <si>
+    <t>男子棒取り・赤団</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ダンシ </t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">ボウ </t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>🪿</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">アカダン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>川橋巧</t>
+  </si>
+  <si>
+    <t>豊島詢大</t>
+  </si>
+  <si>
+    <t>森戸鳳紀</t>
+  </si>
+  <si>
+    <t>谷龍風</t>
+  </si>
+  <si>
+    <t>木村悠希</t>
+  </si>
+  <si>
+    <t>小西由人</t>
+  </si>
+  <si>
+    <t>曽田佑亮</t>
+  </si>
+  <si>
+    <t>亀井勇杜</t>
+  </si>
+  <si>
+    <t>後藤大登</t>
+  </si>
+  <si>
+    <t>坂下登大</t>
+  </si>
+  <si>
+    <t>藤堂正輝</t>
+  </si>
+  <si>
+    <t>川尻悠生</t>
+  </si>
+  <si>
+    <t>前田大輔</t>
+  </si>
+  <si>
+    <t>的場駿士</t>
+  </si>
+  <si>
+    <t>林涼太</t>
+  </si>
+  <si>
+    <t>本田大翔</t>
+  </si>
+  <si>
+    <t>速水竣悟</t>
+  </si>
+  <si>
+    <t>植木蒼馬</t>
+  </si>
+  <si>
+    <t>三崎陽太</t>
+  </si>
+  <si>
+    <t>中村仁太朗</t>
+  </si>
+  <si>
+    <t>橋本竜成</t>
+  </si>
+  <si>
+    <t>男子棒取り・青団</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ダンシ </t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">ボウ </t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>🪿</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">アオダン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>太田亮ノ佑</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>万代悠羽</t>
+  </si>
+  <si>
+    <t>岩切音和</t>
+  </si>
+  <si>
+    <t>山田航大</t>
+  </si>
+  <si>
+    <t>山田晃誠</t>
+  </si>
+  <si>
+    <t>森健悟</t>
+  </si>
+  <si>
+    <t>山林心太朗</t>
+  </si>
+  <si>
+    <t>鳥本瑛斗</t>
+  </si>
+  <si>
+    <t>岩井翔大</t>
+  </si>
+  <si>
+    <t>前田真甫</t>
+  </si>
+  <si>
+    <t>中西巧実</t>
+  </si>
+  <si>
+    <t>青柴生</t>
+  </si>
+  <si>
+    <t>浦野亘輝</t>
+  </si>
+  <si>
+    <t>大川寛輔</t>
+  </si>
+  <si>
+    <t>飯田統維</t>
+  </si>
+  <si>
+    <t>細井瑛仁</t>
+  </si>
+  <si>
+    <t>島田光祐</t>
+  </si>
+  <si>
+    <t>帯刀亮真</t>
+  </si>
+  <si>
+    <t>山手悠生</t>
+  </si>
+  <si>
+    <t>竹田和貴</t>
+  </si>
+  <si>
+    <t>中川一輝</t>
+  </si>
+  <si>
+    <t>松田太志</t>
+  </si>
+  <si>
+    <t>杉本龍之祐</t>
+  </si>
+  <si>
+    <t>村上煌明</t>
+  </si>
+  <si>
+    <t>男子棒取り・黄団</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ダンシ </t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">ボウ </t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>🪿</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>🌲</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t xml:space="preserve">アオダン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>國定龍</t>
+  </si>
+  <si>
+    <t>奥村 航平</t>
+  </si>
+  <si>
+    <t>上城戸翔太</t>
+  </si>
+  <si>
+    <t>谷口善夕</t>
+  </si>
+  <si>
+    <t>小倉聡介</t>
+  </si>
+  <si>
+    <t>北村理</t>
+  </si>
+  <si>
+    <t>北川陸</t>
+  </si>
+  <si>
+    <t xml:space="preserve">辻健士朗 </t>
+  </si>
+  <si>
+    <t>矢谷太智</t>
+  </si>
+  <si>
+    <t>福澤蒼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">西崎蓮 </t>
+  </si>
+  <si>
+    <t>藤澤久眞</t>
+  </si>
+  <si>
+    <t>大堤永翔</t>
+  </si>
+  <si>
+    <t>本持諒也</t>
+  </si>
+  <si>
+    <t>穴見幸樹</t>
+  </si>
+  <si>
+    <t>伊藤隼一郎</t>
+  </si>
+  <si>
+    <t>森雄聖</t>
+  </si>
+  <si>
+    <t>男子棒取り・黒団</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ダンシ </t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">ボウ </t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>🪿</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t xml:space="preserve">クロ </t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t xml:space="preserve">アオダン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>児島遼哉</t>
+  </si>
+  <si>
+    <t>浅井健壱</t>
+  </si>
+  <si>
+    <t>山本開智</t>
+  </si>
+  <si>
+    <t>秋山吏乃翔</t>
+  </si>
+  <si>
+    <t>藤田大輝</t>
+  </si>
+  <si>
+    <t>佐野亮太郎</t>
+  </si>
+  <si>
+    <t>須田樹</t>
+  </si>
+  <si>
+    <t>前川聖成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">立石吏玖 </t>
+  </si>
+  <si>
+    <t>虎井蓮</t>
+  </si>
+  <si>
+    <t>藤原聡士</t>
+  </si>
+  <si>
+    <t>梶田琥太郎</t>
+  </si>
+  <si>
+    <t>水口日嵩</t>
+  </si>
+  <si>
+    <t>杉山彰吾</t>
+  </si>
+  <si>
+    <t>北垣十磨</t>
+  </si>
+  <si>
+    <t>高木龍之介</t>
+  </si>
+  <si>
+    <t>山田創太郎</t>
+  </si>
+  <si>
+    <t>芦谷泰芽</t>
+  </si>
+  <si>
+    <t>金山勢大</t>
+  </si>
+  <si>
+    <t>三宅航士朗</t>
+  </si>
+  <si>
+    <t>棒取り女子・青団</t>
+  </si>
+  <si>
+    <t>石井紗愛</t>
+  </si>
+  <si>
+    <t>井上優里</t>
+  </si>
+  <si>
+    <t>田中愛夕</t>
+  </si>
+  <si>
+    <t>中尾脩愛</t>
+  </si>
+  <si>
+    <t>高畠佐菜</t>
+  </si>
+  <si>
+    <t>高橋里奈</t>
+  </si>
+  <si>
+    <t>京明香里</t>
+  </si>
+  <si>
+    <t>岡本ひなた</t>
+  </si>
+  <si>
+    <t>西本愛衣</t>
+  </si>
+  <si>
+    <t>長谷川綾</t>
+  </si>
+  <si>
+    <t>長尾知夏</t>
+  </si>
+  <si>
+    <t>田中夏希</t>
+  </si>
+  <si>
+    <t>山田心愛</t>
+  </si>
+  <si>
+    <t>越野紗良</t>
+  </si>
+  <si>
+    <t>下里美侑</t>
+  </si>
+  <si>
+    <t>竹内友凛乃</t>
+  </si>
+  <si>
+    <t>安倍真花</t>
+  </si>
+  <si>
+    <t>棒取り女子・赤団</t>
+  </si>
+  <si>
+    <t>寺田亜梨沙</t>
+  </si>
+  <si>
+    <t>鈴木真帆</t>
+  </si>
+  <si>
+    <t>杉浦瑠南</t>
+  </si>
+  <si>
+    <t>大野光莉</t>
+  </si>
+  <si>
+    <t>松村杏詩</t>
+  </si>
+  <si>
+    <t>中山萌依</t>
+  </si>
+  <si>
+    <t>小川悠</t>
+  </si>
+  <si>
+    <t>末成佑愛</t>
+  </si>
+  <si>
+    <t>島津心温</t>
+  </si>
+  <si>
+    <t>久保田悠月</t>
+  </si>
+  <si>
+    <t>丸山萌々</t>
+  </si>
+  <si>
+    <t>深尾彩夏</t>
+  </si>
+  <si>
+    <t>中村純</t>
+  </si>
+  <si>
+    <t>加藤梓</t>
+  </si>
+  <si>
+    <t>小寺幸音</t>
+  </si>
+  <si>
+    <t>藤本莉璃</t>
+  </si>
+  <si>
+    <t>本城青凛</t>
+  </si>
+  <si>
+    <t>談恵佳</t>
+  </si>
+  <si>
+    <t>濱野輝</t>
+  </si>
+  <si>
+    <t>山田美樹</t>
+  </si>
+  <si>
+    <t>今田凛</t>
+  </si>
+  <si>
+    <t>棒取り女子・黄団</t>
+  </si>
+  <si>
+    <t>コリア愛羚奈</t>
+  </si>
+  <si>
+    <t>佐伯莉央</t>
+  </si>
+  <si>
+    <t>Corina</t>
+  </si>
+  <si>
+    <t>池添心菜</t>
+  </si>
+  <si>
+    <t>高橋暖</t>
+  </si>
+  <si>
+    <t>竹内彩音</t>
+  </si>
+  <si>
+    <t>田中貴沙子</t>
+  </si>
+  <si>
+    <t>安部真凜</t>
+  </si>
+  <si>
+    <t>加藤涼菜</t>
+  </si>
+  <si>
+    <t>三永真桜</t>
+  </si>
+  <si>
+    <t>吉田晴香</t>
+  </si>
+  <si>
+    <t>福田茉央</t>
+  </si>
+  <si>
+    <t xml:space="preserve">浄慶咲 </t>
+  </si>
+  <si>
+    <t>杉山真祐佳</t>
+  </si>
+  <si>
+    <t>崗崎瑞月</t>
+  </si>
+  <si>
+    <t>西田結子</t>
+  </si>
+  <si>
+    <t>谷野雫月</t>
+  </si>
+  <si>
+    <t>堤内晴香</t>
+  </si>
+  <si>
+    <t xml:space="preserve">岡野志栞 </t>
+  </si>
+  <si>
+    <t>石田陽彩</t>
+  </si>
+  <si>
+    <t>窪田莉子</t>
+  </si>
+  <si>
+    <t>斎藤夢</t>
+  </si>
+  <si>
+    <t>棒取り女子・黒団</t>
+  </si>
+  <si>
+    <t>伊藤結悠</t>
+  </si>
+  <si>
+    <t>山田真那</t>
+  </si>
+  <si>
+    <t xml:space="preserve">辻花奏 </t>
+  </si>
+  <si>
+    <t>神谷萌衣</t>
+  </si>
+  <si>
+    <t>斎田陽愛</t>
+  </si>
+  <si>
+    <t>川端柚璃</t>
+  </si>
+  <si>
+    <t>堀愛香</t>
+  </si>
+  <si>
+    <t>杣友愛依</t>
+  </si>
+  <si>
+    <t>岡田小夏</t>
+  </si>
+  <si>
+    <t>岸谷美桜</t>
+  </si>
+  <si>
+    <t>秋田珠里</t>
+  </si>
+  <si>
+    <t>大久保圭萌</t>
+  </si>
+  <si>
+    <t>小林由莉乃</t>
+  </si>
+  <si>
+    <t>エヴァ</t>
+  </si>
+  <si>
+    <t>筈井洛凪</t>
+  </si>
+  <si>
+    <t>中原椛梨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">湊萌花 </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="17">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1965,6 +3104,43 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="MS Mincho"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1974,7 +3150,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -2130,13 +3306,155 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2206,17 +3524,74 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="26">
     <dxf>
       <font>
         <color rgb="FFFFFFFF"/>
@@ -2247,6 +3622,58 @@
         <patternFill patternType="solid">
           <fgColor rgb="FF0000FF"/>
           <bgColor rgb="FF0000FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF0000FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="8"/>
+          <bgColor theme="8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2394,21 +3821,13 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="8"/>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
+          <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF0000FF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2429,8 +3848,16 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="8"/>
+          <bgColor theme="8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2775,7 +4202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E04C86-53A8-4C49-AB0F-61EBA36494D7}">
-  <dimension ref="A1:C553"/>
+  <dimension ref="A1:C1009"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
     <row r="1" spans="1:3" ht="21" thickBot="1">
@@ -5741,7 +7168,7 @@
       </c>
     </row>
     <row r="366" spans="1:2">
-      <c r="A366" s="24" t="s">
+      <c r="A366" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B366" s="19" t="s">
@@ -5749,7 +7176,7 @@
       </c>
     </row>
     <row r="367" spans="1:2">
-      <c r="A367" s="24" t="s">
+      <c r="A367" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B367" s="19" t="s">
@@ -5757,7 +7184,7 @@
       </c>
     </row>
     <row r="368" spans="1:2">
-      <c r="A368" s="24" t="s">
+      <c r="A368" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B368" s="19" t="s">
@@ -5765,7 +7192,7 @@
       </c>
     </row>
     <row r="369" spans="1:2">
-      <c r="A369" s="24" t="s">
+      <c r="A369" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B369" s="19" t="s">
@@ -5773,7 +7200,7 @@
       </c>
     </row>
     <row r="370" spans="1:2">
-      <c r="A370" s="24" t="s">
+      <c r="A370" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B370" s="19" t="s">
@@ -5781,7 +7208,7 @@
       </c>
     </row>
     <row r="371" spans="1:2">
-      <c r="A371" s="24" t="s">
+      <c r="A371" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B371" s="19" t="s">
@@ -5789,7 +7216,7 @@
       </c>
     </row>
     <row r="372" spans="1:2">
-      <c r="A372" s="24" t="s">
+      <c r="A372" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B372" s="19" t="s">
@@ -5797,7 +7224,7 @@
       </c>
     </row>
     <row r="373" spans="1:2">
-      <c r="A373" s="24" t="s">
+      <c r="A373" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B373" s="19" t="s">
@@ -5805,7 +7232,7 @@
       </c>
     </row>
     <row r="374" spans="1:2">
-      <c r="A374" s="24" t="s">
+      <c r="A374" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B374" s="19" t="s">
@@ -5813,7 +7240,7 @@
       </c>
     </row>
     <row r="375" spans="1:2">
-      <c r="A375" s="24" t="s">
+      <c r="A375" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B375" s="19" t="s">
@@ -5821,7 +7248,7 @@
       </c>
     </row>
     <row r="376" spans="1:2">
-      <c r="A376" s="24" t="s">
+      <c r="A376" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B376" s="19" t="s">
@@ -5829,7 +7256,7 @@
       </c>
     </row>
     <row r="377" spans="1:2">
-      <c r="A377" s="24" t="s">
+      <c r="A377" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B377" s="19" t="s">
@@ -5837,7 +7264,7 @@
       </c>
     </row>
     <row r="378" spans="1:2">
-      <c r="A378" s="24" t="s">
+      <c r="A378" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B378" s="19" t="s">
@@ -5845,7 +7272,7 @@
       </c>
     </row>
     <row r="379" spans="1:2">
-      <c r="A379" s="24" t="s">
+      <c r="A379" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B379" s="19" t="s">
@@ -5853,7 +7280,7 @@
       </c>
     </row>
     <row r="380" spans="1:2">
-      <c r="A380" s="24" t="s">
+      <c r="A380" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B380" s="19" t="s">
@@ -5861,7 +7288,7 @@
       </c>
     </row>
     <row r="381" spans="1:2">
-      <c r="A381" s="24" t="s">
+      <c r="A381" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B381" s="19" t="s">
@@ -5869,7 +7296,7 @@
       </c>
     </row>
     <row r="382" spans="1:2">
-      <c r="A382" s="24" t="s">
+      <c r="A382" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B382" s="19" t="s">
@@ -5877,7 +7304,7 @@
       </c>
     </row>
     <row r="383" spans="1:2">
-      <c r="A383" s="24" t="s">
+      <c r="A383" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B383" s="19" t="s">
@@ -5885,7 +7312,7 @@
       </c>
     </row>
     <row r="384" spans="1:2">
-      <c r="A384" s="24" t="s">
+      <c r="A384" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B384" s="19" t="s">
@@ -5893,7 +7320,7 @@
       </c>
     </row>
     <row r="385" spans="1:2">
-      <c r="A385" s="24" t="s">
+      <c r="A385" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B385" s="19" t="s">
@@ -5901,7 +7328,7 @@
       </c>
     </row>
     <row r="386" spans="1:2">
-      <c r="A386" s="24" t="s">
+      <c r="A386" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B386" s="19" t="s">
@@ -5909,7 +7336,7 @@
       </c>
     </row>
     <row r="387" spans="1:2">
-      <c r="A387" s="24" t="s">
+      <c r="A387" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B387" s="19" t="s">
@@ -5917,7 +7344,7 @@
       </c>
     </row>
     <row r="388" spans="1:2">
-      <c r="A388" s="24" t="s">
+      <c r="A388" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B388" s="19" t="s">
@@ -5925,7 +7352,7 @@
       </c>
     </row>
     <row r="389" spans="1:2">
-      <c r="A389" s="24" t="s">
+      <c r="A389" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B389" s="19" t="s">
@@ -5933,7 +7360,7 @@
       </c>
     </row>
     <row r="390" spans="1:2">
-      <c r="A390" s="24" t="s">
+      <c r="A390" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B390" s="19" t="s">
@@ -5941,7 +7368,7 @@
       </c>
     </row>
     <row r="391" spans="1:2">
-      <c r="A391" s="24" t="s">
+      <c r="A391" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B391" s="20" t="s">
@@ -5949,7 +7376,7 @@
       </c>
     </row>
     <row r="392" spans="1:2">
-      <c r="A392" s="24" t="s">
+      <c r="A392" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B392" s="20" t="s">
@@ -5957,7 +7384,7 @@
       </c>
     </row>
     <row r="393" spans="1:2">
-      <c r="A393" s="24" t="s">
+      <c r="A393" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B393" s="20" t="s">
@@ -5965,7 +7392,7 @@
       </c>
     </row>
     <row r="394" spans="1:2">
-      <c r="A394" s="24" t="s">
+      <c r="A394" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B394" s="20" t="s">
@@ -5973,7 +7400,7 @@
       </c>
     </row>
     <row r="395" spans="1:2">
-      <c r="A395" s="24" t="s">
+      <c r="A395" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B395" s="20" t="s">
@@ -5981,7 +7408,7 @@
       </c>
     </row>
     <row r="396" spans="1:2">
-      <c r="A396" s="24" t="s">
+      <c r="A396" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B396" s="20" t="s">
@@ -5989,7 +7416,7 @@
       </c>
     </row>
     <row r="397" spans="1:2">
-      <c r="A397" s="24" t="s">
+      <c r="A397" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B397" s="20" t="s">
@@ -5997,7 +7424,7 @@
       </c>
     </row>
     <row r="398" spans="1:2">
-      <c r="A398" s="24" t="s">
+      <c r="A398" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B398" s="20" t="s">
@@ -6005,7 +7432,7 @@
       </c>
     </row>
     <row r="399" spans="1:2">
-      <c r="A399" s="24" t="s">
+      <c r="A399" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B399" s="20" t="s">
@@ -6013,7 +7440,7 @@
       </c>
     </row>
     <row r="400" spans="1:2">
-      <c r="A400" s="24" t="s">
+      <c r="A400" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B400" s="20" t="s">
@@ -6021,7 +7448,7 @@
       </c>
     </row>
     <row r="401" spans="1:2">
-      <c r="A401" s="24" t="s">
+      <c r="A401" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B401" s="21" t="s">
@@ -6029,7 +7456,7 @@
       </c>
     </row>
     <row r="402" spans="1:2">
-      <c r="A402" s="24" t="s">
+      <c r="A402" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B402" s="21" t="s">
@@ -6037,7 +7464,7 @@
       </c>
     </row>
     <row r="403" spans="1:2">
-      <c r="A403" s="24" t="s">
+      <c r="A403" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B403" s="21" t="s">
@@ -6045,7 +7472,7 @@
       </c>
     </row>
     <row r="404" spans="1:2">
-      <c r="A404" s="24" t="s">
+      <c r="A404" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B404" s="21" t="s">
@@ -6053,7 +7480,7 @@
       </c>
     </row>
     <row r="405" spans="1:2">
-      <c r="A405" s="24" t="s">
+      <c r="A405" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B405" s="21" t="s">
@@ -6061,7 +7488,7 @@
       </c>
     </row>
     <row r="406" spans="1:2">
-      <c r="A406" s="24" t="s">
+      <c r="A406" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B406" s="21" t="s">
@@ -6069,7 +7496,7 @@
       </c>
     </row>
     <row r="407" spans="1:2">
-      <c r="A407" s="24" t="s">
+      <c r="A407" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B407" s="21" t="s">
@@ -6077,7 +7504,7 @@
       </c>
     </row>
     <row r="408" spans="1:2">
-      <c r="A408" s="24" t="s">
+      <c r="A408" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B408" s="21" t="s">
@@ -6085,7 +7512,7 @@
       </c>
     </row>
     <row r="409" spans="1:2">
-      <c r="A409" s="24" t="s">
+      <c r="A409" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B409" s="21" t="s">
@@ -6093,7 +7520,7 @@
       </c>
     </row>
     <row r="410" spans="1:2">
-      <c r="A410" s="24" t="s">
+      <c r="A410" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B410" s="21" t="s">
@@ -6101,7 +7528,7 @@
       </c>
     </row>
     <row r="411" spans="1:2">
-      <c r="A411" s="24" t="s">
+      <c r="A411" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B411" s="21" t="s">
@@ -6109,7 +7536,7 @@
       </c>
     </row>
     <row r="412" spans="1:2">
-      <c r="A412" s="24" t="s">
+      <c r="A412" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B412" s="21" t="s">
@@ -6117,7 +7544,7 @@
       </c>
     </row>
     <row r="413" spans="1:2">
-      <c r="A413" s="24" t="s">
+      <c r="A413" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B413" s="21" t="s">
@@ -6125,7 +7552,7 @@
       </c>
     </row>
     <row r="414" spans="1:2">
-      <c r="A414" s="24" t="s">
+      <c r="A414" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B414" s="21" t="s">
@@ -6133,7 +7560,7 @@
       </c>
     </row>
     <row r="415" spans="1:2">
-      <c r="A415" s="24" t="s">
+      <c r="A415" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B415" s="21" t="s">
@@ -6141,7 +7568,7 @@
       </c>
     </row>
     <row r="416" spans="1:2">
-      <c r="A416" s="24" t="s">
+      <c r="A416" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B416" s="21" t="s">
@@ -6149,7 +7576,7 @@
       </c>
     </row>
     <row r="417" spans="1:2">
-      <c r="A417" s="24" t="s">
+      <c r="A417" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B417" s="21" t="s">
@@ -6157,7 +7584,7 @@
       </c>
     </row>
     <row r="418" spans="1:2">
-      <c r="A418" s="24" t="s">
+      <c r="A418" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B418" s="21" t="s">
@@ -6165,7 +7592,7 @@
       </c>
     </row>
     <row r="419" spans="1:2">
-      <c r="A419" s="24" t="s">
+      <c r="A419" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B419" s="21" t="s">
@@ -6173,7 +7600,7 @@
       </c>
     </row>
     <row r="420" spans="1:2">
-      <c r="A420" s="24" t="s">
+      <c r="A420" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B420" s="21" t="s">
@@ -6181,7 +7608,7 @@
       </c>
     </row>
     <row r="421" spans="1:2">
-      <c r="A421" s="24" t="s">
+      <c r="A421" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B421" s="21" t="s">
@@ -6189,7 +7616,7 @@
       </c>
     </row>
     <row r="422" spans="1:2">
-      <c r="A422" s="24" t="s">
+      <c r="A422" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B422" s="21" t="s">
@@ -6197,7 +7624,7 @@
       </c>
     </row>
     <row r="423" spans="1:2">
-      <c r="A423" s="24" t="s">
+      <c r="A423" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B423" s="21" t="s">
@@ -6205,7 +7632,7 @@
       </c>
     </row>
     <row r="424" spans="1:2">
-      <c r="A424" s="24" t="s">
+      <c r="A424" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B424" s="21" t="s">
@@ -6213,7 +7640,7 @@
       </c>
     </row>
     <row r="425" spans="1:2">
-      <c r="A425" s="24" t="s">
+      <c r="A425" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B425" s="21" t="s">
@@ -6221,7 +7648,7 @@
       </c>
     </row>
     <row r="426" spans="1:2">
-      <c r="A426" s="24" t="s">
+      <c r="A426" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B426" s="22" t="s">
@@ -6229,7 +7656,7 @@
       </c>
     </row>
     <row r="427" spans="1:2">
-      <c r="A427" s="24" t="s">
+      <c r="A427" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B427" s="22" t="s">
@@ -6237,7 +7664,7 @@
       </c>
     </row>
     <row r="428" spans="1:2">
-      <c r="A428" s="24" t="s">
+      <c r="A428" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B428" s="22" t="s">
@@ -6245,7 +7672,7 @@
       </c>
     </row>
     <row r="429" spans="1:2">
-      <c r="A429" s="24" t="s">
+      <c r="A429" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B429" s="22" t="s">
@@ -6253,7 +7680,7 @@
       </c>
     </row>
     <row r="430" spans="1:2">
-      <c r="A430" s="24" t="s">
+      <c r="A430" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B430" s="22" t="s">
@@ -6261,7 +7688,7 @@
       </c>
     </row>
     <row r="431" spans="1:2">
-      <c r="A431" s="24" t="s">
+      <c r="A431" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B431" s="22" t="s">
@@ -6269,7 +7696,7 @@
       </c>
     </row>
     <row r="432" spans="1:2">
-      <c r="A432" s="24" t="s">
+      <c r="A432" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B432" s="20" t="s">
@@ -6277,7 +7704,7 @@
       </c>
     </row>
     <row r="433" spans="1:2">
-      <c r="A433" s="24" t="s">
+      <c r="A433" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B433" s="22" t="s">
@@ -6285,7 +7712,7 @@
       </c>
     </row>
     <row r="434" spans="1:2">
-      <c r="A434" s="24" t="s">
+      <c r="A434" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B434" s="22" t="s">
@@ -6293,7 +7720,7 @@
       </c>
     </row>
     <row r="435" spans="1:2">
-      <c r="A435" s="24" t="s">
+      <c r="A435" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B435" s="22" t="s">
@@ -6301,7 +7728,7 @@
       </c>
     </row>
     <row r="436" spans="1:2">
-      <c r="A436" s="24" t="s">
+      <c r="A436" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B436" s="22" t="s">
@@ -6309,7 +7736,7 @@
       </c>
     </row>
     <row r="437" spans="1:2">
-      <c r="A437" s="24" t="s">
+      <c r="A437" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B437" s="22" t="s">
@@ -6317,7 +7744,7 @@
       </c>
     </row>
     <row r="438" spans="1:2">
-      <c r="A438" s="24" t="s">
+      <c r="A438" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B438" s="22" t="s">
@@ -6325,7 +7752,7 @@
       </c>
     </row>
     <row r="439" spans="1:2">
-      <c r="A439" s="24" t="s">
+      <c r="A439" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B439" s="22" t="s">
@@ -6333,7 +7760,7 @@
       </c>
     </row>
     <row r="440" spans="1:2">
-      <c r="A440" s="24" t="s">
+      <c r="A440" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B440" s="22" t="s">
@@ -6341,7 +7768,7 @@
       </c>
     </row>
     <row r="441" spans="1:2">
-      <c r="A441" s="24" t="s">
+      <c r="A441" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B441" s="21" t="s">
@@ -6349,7 +7776,7 @@
       </c>
     </row>
     <row r="442" spans="1:2">
-      <c r="A442" s="24" t="s">
+      <c r="A442" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B442" s="21" t="s">
@@ -6357,7 +7784,7 @@
       </c>
     </row>
     <row r="443" spans="1:2">
-      <c r="A443" s="24" t="s">
+      <c r="A443" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B443" s="21" t="s">
@@ -6365,7 +7792,7 @@
       </c>
     </row>
     <row r="444" spans="1:2">
-      <c r="A444" s="24" t="s">
+      <c r="A444" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B444" s="21" t="s">
@@ -6373,7 +7800,7 @@
       </c>
     </row>
     <row r="445" spans="1:2">
-      <c r="A445" s="24" t="s">
+      <c r="A445" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B445" s="21" t="s">
@@ -6381,7 +7808,7 @@
       </c>
     </row>
     <row r="446" spans="1:2">
-      <c r="A446" s="24" t="s">
+      <c r="A446" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B446" s="21" t="s">
@@ -6389,7 +7816,7 @@
       </c>
     </row>
     <row r="447" spans="1:2">
-      <c r="A447" s="24" t="s">
+      <c r="A447" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B447" s="21" t="s">
@@ -6397,7 +7824,7 @@
       </c>
     </row>
     <row r="448" spans="1:2">
-      <c r="A448" s="24" t="s">
+      <c r="A448" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B448" s="21" t="s">
@@ -6405,7 +7832,7 @@
       </c>
     </row>
     <row r="449" spans="1:2">
-      <c r="A449" s="24" t="s">
+      <c r="A449" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B449" s="21" t="s">
@@ -6413,7 +7840,7 @@
       </c>
     </row>
     <row r="450" spans="1:2">
-      <c r="A450" s="24" t="s">
+      <c r="A450" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B450" s="21" t="s">
@@ -6421,7 +7848,7 @@
       </c>
     </row>
     <row r="451" spans="1:2">
-      <c r="A451" s="24" t="s">
+      <c r="A451" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B451" s="21" t="s">
@@ -6429,7 +7856,7 @@
       </c>
     </row>
     <row r="452" spans="1:2">
-      <c r="A452" s="24" t="s">
+      <c r="A452" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B452" s="21" t="s">
@@ -6437,7 +7864,7 @@
       </c>
     </row>
     <row r="453" spans="1:2">
-      <c r="A453" s="24" t="s">
+      <c r="A453" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B453" s="21" t="s">
@@ -6445,7 +7872,7 @@
       </c>
     </row>
     <row r="454" spans="1:2">
-      <c r="A454" s="24" t="s">
+      <c r="A454" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B454" s="21" t="s">
@@ -6453,7 +7880,7 @@
       </c>
     </row>
     <row r="455" spans="1:2">
-      <c r="A455" s="24" t="s">
+      <c r="A455" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B455" s="21" t="s">
@@ -6461,7 +7888,7 @@
       </c>
     </row>
     <row r="456" spans="1:2">
-      <c r="A456" s="24" t="s">
+      <c r="A456" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B456" s="21" t="s">
@@ -6469,7 +7896,7 @@
       </c>
     </row>
     <row r="457" spans="1:2">
-      <c r="A457" s="24" t="s">
+      <c r="A457" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B457" s="21" t="s">
@@ -6477,7 +7904,7 @@
       </c>
     </row>
     <row r="458" spans="1:2">
-      <c r="A458" s="24" t="s">
+      <c r="A458" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B458" s="21" t="s">
@@ -6485,7 +7912,7 @@
       </c>
     </row>
     <row r="459" spans="1:2">
-      <c r="A459" s="24" t="s">
+      <c r="A459" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B459" s="21" t="s">
@@ -6493,7 +7920,7 @@
       </c>
     </row>
     <row r="460" spans="1:2">
-      <c r="A460" s="24" t="s">
+      <c r="A460" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B460" s="21" t="s">
@@ -6501,7 +7928,7 @@
       </c>
     </row>
     <row r="461" spans="1:2">
-      <c r="A461" s="24" t="s">
+      <c r="A461" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B461" s="21" t="s">
@@ -6509,7 +7936,7 @@
       </c>
     </row>
     <row r="462" spans="1:2">
-      <c r="A462" s="24" t="s">
+      <c r="A462" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B462" s="21" t="s">
@@ -6517,7 +7944,7 @@
       </c>
     </row>
     <row r="463" spans="1:2">
-      <c r="A463" s="24" t="s">
+      <c r="A463" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B463" s="21" t="s">
@@ -6525,7 +7952,7 @@
       </c>
     </row>
     <row r="464" spans="1:2">
-      <c r="A464" s="24" t="s">
+      <c r="A464" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B464" s="21" t="s">
@@ -6533,7 +7960,7 @@
       </c>
     </row>
     <row r="465" spans="1:2">
-      <c r="A465" s="24" t="s">
+      <c r="A465" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B465" s="21" t="s">
@@ -6541,7 +7968,7 @@
       </c>
     </row>
     <row r="466" spans="1:2">
-      <c r="A466" s="24" t="s">
+      <c r="A466" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B466" s="21" t="s">
@@ -6549,7 +7976,7 @@
       </c>
     </row>
     <row r="467" spans="1:2">
-      <c r="A467" s="24" t="s">
+      <c r="A467" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B467" s="21" t="s">
@@ -6557,7 +7984,7 @@
       </c>
     </row>
     <row r="468" spans="1:2">
-      <c r="A468" s="24" t="s">
+      <c r="A468" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B468" s="21" t="s">
@@ -6565,7 +7992,7 @@
       </c>
     </row>
     <row r="469" spans="1:2">
-      <c r="A469" s="24" t="s">
+      <c r="A469" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B469" s="21" t="s">
@@ -6573,7 +8000,7 @@
       </c>
     </row>
     <row r="470" spans="1:2">
-      <c r="A470" s="24" t="s">
+      <c r="A470" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B470" s="21" t="s">
@@ -6581,7 +8008,7 @@
       </c>
     </row>
     <row r="471" spans="1:2">
-      <c r="A471" s="24" t="s">
+      <c r="A471" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B471" s="21" t="s">
@@ -6589,7 +8016,7 @@
       </c>
     </row>
     <row r="472" spans="1:2">
-      <c r="A472" s="24" t="s">
+      <c r="A472" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B472" s="21" t="s">
@@ -6597,7 +8024,7 @@
       </c>
     </row>
     <row r="473" spans="1:2">
-      <c r="A473" s="24" t="s">
+      <c r="A473" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B473" s="21" t="s">
@@ -6605,7 +8032,7 @@
       </c>
     </row>
     <row r="474" spans="1:2">
-      <c r="A474" s="24" t="s">
+      <c r="A474" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B474" s="21" t="s">
@@ -6613,7 +8040,7 @@
       </c>
     </row>
     <row r="475" spans="1:2">
-      <c r="A475" s="24" t="s">
+      <c r="A475" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B475" s="21" t="s">
@@ -6621,7 +8048,7 @@
       </c>
     </row>
     <row r="476" spans="1:2">
-      <c r="A476" s="24" t="s">
+      <c r="A476" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B476" s="21" t="s">
@@ -6629,7 +8056,7 @@
       </c>
     </row>
     <row r="477" spans="1:2">
-      <c r="A477" s="24" t="s">
+      <c r="A477" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B477" s="21" t="s">
@@ -6637,7 +8064,7 @@
       </c>
     </row>
     <row r="478" spans="1:2">
-      <c r="A478" s="24" t="s">
+      <c r="A478" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B478" s="21" t="s">
@@ -6645,7 +8072,7 @@
       </c>
     </row>
     <row r="479" spans="1:2">
-      <c r="A479" s="24" t="s">
+      <c r="A479" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B479" s="21" t="s">
@@ -6653,7 +8080,7 @@
       </c>
     </row>
     <row r="480" spans="1:2">
-      <c r="A480" s="24" t="s">
+      <c r="A480" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B480" s="21" t="s">
@@ -6661,7 +8088,7 @@
       </c>
     </row>
     <row r="481" spans="1:2">
-      <c r="A481" s="24" t="s">
+      <c r="A481" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B481" s="21" t="s">
@@ -6669,7 +8096,7 @@
       </c>
     </row>
     <row r="482" spans="1:2">
-      <c r="A482" s="24" t="s">
+      <c r="A482" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B482" s="21" t="s">
@@ -6677,7 +8104,7 @@
       </c>
     </row>
     <row r="483" spans="1:2">
-      <c r="A483" s="24" t="s">
+      <c r="A483" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B483" s="21" t="s">
@@ -6685,7 +8112,7 @@
       </c>
     </row>
     <row r="484" spans="1:2">
-      <c r="A484" s="24" t="s">
+      <c r="A484" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B484" s="21" t="s">
@@ -6693,7 +8120,7 @@
       </c>
     </row>
     <row r="485" spans="1:2">
-      <c r="A485" s="24" t="s">
+      <c r="A485" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B485" s="21" t="s">
@@ -6701,7 +8128,7 @@
       </c>
     </row>
     <row r="486" spans="1:2">
-      <c r="A486" s="24" t="s">
+      <c r="A486" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B486" s="21" t="s">
@@ -6709,7 +8136,7 @@
       </c>
     </row>
     <row r="487" spans="1:2">
-      <c r="A487" s="24" t="s">
+      <c r="A487" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B487" s="21" t="s">
@@ -6717,7 +8144,7 @@
       </c>
     </row>
     <row r="488" spans="1:2">
-      <c r="A488" s="24" t="s">
+      <c r="A488" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B488" s="21" t="s">
@@ -6725,7 +8152,7 @@
       </c>
     </row>
     <row r="489" spans="1:2">
-      <c r="A489" s="24" t="s">
+      <c r="A489" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B489" s="21" t="s">
@@ -6733,7 +8160,7 @@
       </c>
     </row>
     <row r="490" spans="1:2">
-      <c r="A490" s="24" t="s">
+      <c r="A490" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B490" s="21" t="s">
@@ -6741,7 +8168,7 @@
       </c>
     </row>
     <row r="491" spans="1:2">
-      <c r="A491" s="24" t="s">
+      <c r="A491" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B491" s="21" t="s">
@@ -6749,7 +8176,7 @@
       </c>
     </row>
     <row r="492" spans="1:2">
-      <c r="A492" s="24" t="s">
+      <c r="A492" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B492" s="21" t="s">
@@ -6757,7 +8184,7 @@
       </c>
     </row>
     <row r="493" spans="1:2">
-      <c r="A493" s="24" t="s">
+      <c r="A493" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B493" s="21" t="s">
@@ -6765,7 +8192,7 @@
       </c>
     </row>
     <row r="494" spans="1:2">
-      <c r="A494" s="24" t="s">
+      <c r="A494" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B494" s="21" t="s">
@@ -6773,7 +8200,7 @@
       </c>
     </row>
     <row r="495" spans="1:2">
-      <c r="A495" s="24" t="s">
+      <c r="A495" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B495" s="21" t="s">
@@ -6781,7 +8208,7 @@
       </c>
     </row>
     <row r="496" spans="1:2">
-      <c r="A496" s="24" t="s">
+      <c r="A496" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B496" s="21" t="s">
@@ -6789,7 +8216,7 @@
       </c>
     </row>
     <row r="497" spans="1:2">
-      <c r="A497" s="24" t="s">
+      <c r="A497" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B497" s="21" t="s">
@@ -6797,7 +8224,7 @@
       </c>
     </row>
     <row r="498" spans="1:2">
-      <c r="A498" s="24" t="s">
+      <c r="A498" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B498" s="21" t="s">
@@ -6805,7 +8232,7 @@
       </c>
     </row>
     <row r="499" spans="1:2">
-      <c r="A499" s="24" t="s">
+      <c r="A499" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B499" s="21" t="s">
@@ -6813,7 +8240,7 @@
       </c>
     </row>
     <row r="500" spans="1:2">
-      <c r="A500" s="24" t="s">
+      <c r="A500" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B500" s="21" t="s">
@@ -6821,7 +8248,7 @@
       </c>
     </row>
     <row r="501" spans="1:2">
-      <c r="A501" s="24" t="s">
+      <c r="A501" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B501" s="21" t="s">
@@ -6829,7 +8256,7 @@
       </c>
     </row>
     <row r="502" spans="1:2">
-      <c r="A502" s="24" t="s">
+      <c r="A502" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B502" s="21" t="s">
@@ -6837,7 +8264,7 @@
       </c>
     </row>
     <row r="503" spans="1:2">
-      <c r="A503" s="24" t="s">
+      <c r="A503" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B503" s="21" t="s">
@@ -6845,7 +8272,7 @@
       </c>
     </row>
     <row r="504" spans="1:2">
-      <c r="A504" s="24" t="s">
+      <c r="A504" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B504" s="21" t="s">
@@ -6853,7 +8280,7 @@
       </c>
     </row>
     <row r="505" spans="1:2">
-      <c r="A505" s="24" t="s">
+      <c r="A505" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B505" s="21" t="s">
@@ -6861,7 +8288,7 @@
       </c>
     </row>
     <row r="506" spans="1:2">
-      <c r="A506" s="24" t="s">
+      <c r="A506" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B506" s="21" t="s">
@@ -6869,7 +8296,7 @@
       </c>
     </row>
     <row r="507" spans="1:2">
-      <c r="A507" s="24" t="s">
+      <c r="A507" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B507" s="21" t="s">
@@ -6877,7 +8304,7 @@
       </c>
     </row>
     <row r="508" spans="1:2">
-      <c r="A508" s="24" t="s">
+      <c r="A508" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B508" s="21" t="s">
@@ -6885,7 +8312,7 @@
       </c>
     </row>
     <row r="509" spans="1:2">
-      <c r="A509" s="24" t="s">
+      <c r="A509" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B509" s="21" t="s">
@@ -6893,7 +8320,7 @@
       </c>
     </row>
     <row r="510" spans="1:2">
-      <c r="A510" s="24" t="s">
+      <c r="A510" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B510" s="21" t="s">
@@ -6901,7 +8328,7 @@
       </c>
     </row>
     <row r="511" spans="1:2">
-      <c r="A511" s="24" t="s">
+      <c r="A511" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B511" s="21" t="s">
@@ -6909,7 +8336,7 @@
       </c>
     </row>
     <row r="512" spans="1:2">
-      <c r="A512" s="24" t="s">
+      <c r="A512" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B512" s="21" t="s">
@@ -6917,7 +8344,7 @@
       </c>
     </row>
     <row r="513" spans="1:2">
-      <c r="A513" s="24" t="s">
+      <c r="A513" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B513" s="21" t="s">
@@ -6925,7 +8352,7 @@
       </c>
     </row>
     <row r="514" spans="1:2">
-      <c r="A514" s="24" t="s">
+      <c r="A514" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B514" s="21" t="s">
@@ -6933,7 +8360,7 @@
       </c>
     </row>
     <row r="515" spans="1:2">
-      <c r="A515" s="24" t="s">
+      <c r="A515" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B515" s="21" t="s">
@@ -6941,7 +8368,7 @@
       </c>
     </row>
     <row r="516" spans="1:2">
-      <c r="A516" s="24" t="s">
+      <c r="A516" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B516" s="22" t="s">
@@ -6949,7 +8376,7 @@
       </c>
     </row>
     <row r="517" spans="1:2">
-      <c r="A517" s="24" t="s">
+      <c r="A517" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B517" s="22" t="s">
@@ -6957,7 +8384,7 @@
       </c>
     </row>
     <row r="518" spans="1:2">
-      <c r="A518" s="24" t="s">
+      <c r="A518" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B518" s="22" t="s">
@@ -6965,7 +8392,7 @@
       </c>
     </row>
     <row r="519" spans="1:2">
-      <c r="A519" s="24" t="s">
+      <c r="A519" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B519" s="22" t="s">
@@ -6973,7 +8400,7 @@
       </c>
     </row>
     <row r="520" spans="1:2">
-      <c r="A520" s="24" t="s">
+      <c r="A520" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B520" s="22" t="s">
@@ -6981,7 +8408,7 @@
       </c>
     </row>
     <row r="521" spans="1:2">
-      <c r="A521" s="24" t="s">
+      <c r="A521" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B521" s="22" t="s">
@@ -6989,7 +8416,7 @@
       </c>
     </row>
     <row r="522" spans="1:2">
-      <c r="A522" s="24" t="s">
+      <c r="A522" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B522" s="22" t="s">
@@ -6997,7 +8424,7 @@
       </c>
     </row>
     <row r="523" spans="1:2">
-      <c r="A523" s="24" t="s">
+      <c r="A523" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B523" s="22" t="s">
@@ -7005,7 +8432,7 @@
       </c>
     </row>
     <row r="524" spans="1:2">
-      <c r="A524" s="24" t="s">
+      <c r="A524" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B524" s="22" t="s">
@@ -7013,7 +8440,7 @@
       </c>
     </row>
     <row r="525" spans="1:2">
-      <c r="A525" s="24" t="s">
+      <c r="A525" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B525" s="22" t="s">
@@ -7021,7 +8448,7 @@
       </c>
     </row>
     <row r="526" spans="1:2">
-      <c r="A526" s="24" t="s">
+      <c r="A526" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B526" s="21" t="s">
@@ -7029,7 +8456,7 @@
       </c>
     </row>
     <row r="527" spans="1:2">
-      <c r="A527" s="24" t="s">
+      <c r="A527" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B527" s="21" t="s">
@@ -7037,7 +8464,7 @@
       </c>
     </row>
     <row r="528" spans="1:2">
-      <c r="A528" s="24" t="s">
+      <c r="A528" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B528" s="21" t="s">
@@ -7045,7 +8472,7 @@
       </c>
     </row>
     <row r="529" spans="1:2">
-      <c r="A529" s="24" t="s">
+      <c r="A529" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B529" s="21" t="s">
@@ -7053,7 +8480,7 @@
       </c>
     </row>
     <row r="530" spans="1:2">
-      <c r="A530" s="24" t="s">
+      <c r="A530" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B530" s="21" t="s">
@@ -7061,7 +8488,7 @@
       </c>
     </row>
     <row r="531" spans="1:2">
-      <c r="A531" s="24" t="s">
+      <c r="A531" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B531" s="21" t="s">
@@ -7069,7 +8496,7 @@
       </c>
     </row>
     <row r="532" spans="1:2">
-      <c r="A532" s="24" t="s">
+      <c r="A532" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B532" s="21" t="s">
@@ -7077,7 +8504,7 @@
       </c>
     </row>
     <row r="533" spans="1:2">
-      <c r="A533" s="24" t="s">
+      <c r="A533" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B533" s="21" t="s">
@@ -7085,7 +8512,7 @@
       </c>
     </row>
     <row r="534" spans="1:2">
-      <c r="A534" s="24" t="s">
+      <c r="A534" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B534" s="21" t="s">
@@ -7093,7 +8520,7 @@
       </c>
     </row>
     <row r="535" spans="1:2">
-      <c r="A535" s="24" t="s">
+      <c r="A535" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B535" s="21" t="s">
@@ -7101,7 +8528,7 @@
       </c>
     </row>
     <row r="536" spans="1:2">
-      <c r="A536" s="24" t="s">
+      <c r="A536" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B536" s="21" t="s">
@@ -7109,7 +8536,7 @@
       </c>
     </row>
     <row r="537" spans="1:2">
-      <c r="A537" s="24" t="s">
+      <c r="A537" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B537" s="21" t="s">
@@ -7117,7 +8544,7 @@
       </c>
     </row>
     <row r="538" spans="1:2">
-      <c r="A538" s="24" t="s">
+      <c r="A538" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B538" s="21" t="s">
@@ -7125,7 +8552,7 @@
       </c>
     </row>
     <row r="539" spans="1:2">
-      <c r="A539" s="24" t="s">
+      <c r="A539" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B539" s="21" t="s">
@@ -7133,7 +8560,7 @@
       </c>
     </row>
     <row r="540" spans="1:2">
-      <c r="A540" s="24" t="s">
+      <c r="A540" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B540" s="21" t="s">
@@ -7141,7 +8568,7 @@
       </c>
     </row>
     <row r="541" spans="1:2">
-      <c r="A541" s="24" t="s">
+      <c r="A541" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B541" s="21" t="s">
@@ -7149,7 +8576,7 @@
       </c>
     </row>
     <row r="542" spans="1:2">
-      <c r="A542" s="24" t="s">
+      <c r="A542" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B542" s="21" t="s">
@@ -7157,7 +8584,7 @@
       </c>
     </row>
     <row r="543" spans="1:2">
-      <c r="A543" s="24" t="s">
+      <c r="A543" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B543" s="21" t="s">
@@ -7165,7 +8592,7 @@
       </c>
     </row>
     <row r="544" spans="1:2">
-      <c r="A544" s="24" t="s">
+      <c r="A544" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B544" s="21" t="s">
@@ -7173,7 +8600,7 @@
       </c>
     </row>
     <row r="545" spans="1:2">
-      <c r="A545" s="24" t="s">
+      <c r="A545" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B545" s="21" t="s">
@@ -7181,101 +8608,3806 @@
       </c>
     </row>
     <row r="546" spans="1:2">
-      <c r="B546" s="23"/>
+      <c r="A546" s="24" t="s">
+        <v>561</v>
+      </c>
+      <c r="B546" s="25" t="s">
+        <v>562</v>
+      </c>
     </row>
     <row r="547" spans="1:2">
-      <c r="B547" s="23"/>
+      <c r="A547" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B547" s="27" t="s">
+        <v>563</v>
+      </c>
     </row>
     <row r="548" spans="1:2">
-      <c r="B548" s="23"/>
+      <c r="A548" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B548" s="27" t="s">
+        <v>564</v>
+      </c>
     </row>
     <row r="549" spans="1:2">
-      <c r="B549" s="23"/>
+      <c r="A549" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B549" s="27" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="550" spans="1:2">
-      <c r="B550" s="23"/>
+      <c r="A550" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B550" s="27" t="s">
+        <v>566</v>
+      </c>
     </row>
     <row r="551" spans="1:2">
-      <c r="B551" s="23"/>
+      <c r="A551" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B551" s="27" t="s">
+        <v>567</v>
+      </c>
     </row>
     <row r="552" spans="1:2">
-      <c r="B552" s="23"/>
+      <c r="A552" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B552" s="27" t="s">
+        <v>568</v>
+      </c>
     </row>
     <row r="553" spans="1:2">
-      <c r="B553" s="23"/>
+      <c r="A553" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B553" s="27" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B554" s="27" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B555" s="27" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B556" s="27" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B557" s="27" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B558" s="27" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B559" s="27" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B560" s="27" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B561" s="27" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B562" s="27" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B563" s="27" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B564" s="27" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B565" s="27" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B566" s="27" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B567" s="27" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B568" s="27" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B569" s="27" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B570" s="27" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B571" s="27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B572" s="27" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B573" s="27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B574" s="27" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B575" s="27" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B576" s="27" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B577" s="27" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B578" s="27" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B579" s="27" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B580" s="27" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B581" s="27" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B582" s="27" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B583" s="27" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B584" s="27" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B585" s="27" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B586" s="27" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B587" s="27" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2">
+      <c r="A588" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B588" s="27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2">
+      <c r="A589" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B589" s="27" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2">
+      <c r="A590" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B590" s="27" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2">
+      <c r="A591" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B591" s="27" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2">
+      <c r="A592" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B592" s="27" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B593" s="27" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B594" s="27" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B595" s="27" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B596" s="27" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B597" s="27" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B598" s="27" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B599" s="27" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B600" s="27" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B601" s="27" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B602" s="27" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B603" s="27" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B604" s="27" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B605" s="27" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B606" s="28" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B607" s="28" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B608" s="28" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B609" s="28" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B610" s="28" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B611" s="28" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B612" s="28" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B613" s="28" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B614" s="28" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B615" s="28" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B616" s="28" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B617" s="28" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B618" s="28" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B619" s="28" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2">
+      <c r="A620" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B620" s="28" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2">
+      <c r="A621" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B621" s="28" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2">
+      <c r="A622" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B622" s="28" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2">
+      <c r="A623" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B623" s="28" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2">
+      <c r="A624" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B624" s="28" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2">
+      <c r="A625" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B625" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2">
+      <c r="A626" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B626" s="28" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2">
+      <c r="A627" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B627" s="28" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2">
+      <c r="A628" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B628" s="28" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2">
+      <c r="A629" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B629" s="28" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2">
+      <c r="A630" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B630" s="28" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2">
+      <c r="A631" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B631" s="28" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2">
+      <c r="A632" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B632" s="28" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2">
+      <c r="A633" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B633" s="28" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2">
+      <c r="A634" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B634" s="28" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2">
+      <c r="A635" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B635" s="28" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2">
+      <c r="A636" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B636" s="28" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2">
+      <c r="A637" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B637" s="28" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2">
+      <c r="A638" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B638" s="28" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2">
+      <c r="A639" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B639" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2">
+      <c r="A640" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B640" s="28" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2">
+      <c r="A641" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B641" s="28" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2">
+      <c r="A642" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B642" s="28" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2">
+      <c r="A643" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B643" s="28" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2">
+      <c r="A644" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B644" s="28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2">
+      <c r="A645" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B645" s="28" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2">
+      <c r="A646" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B646" s="28" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2">
+      <c r="A647" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B647" s="28" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2">
+      <c r="A648" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B648" s="28" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2">
+      <c r="A649" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B649" s="28" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2">
+      <c r="A650" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B650" s="28" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2">
+      <c r="A651" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B651" s="28" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2">
+      <c r="A652" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B652" s="28" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2">
+      <c r="A653" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B653" s="28" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2">
+      <c r="A654" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B654" s="28" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2">
+      <c r="A655" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B655" s="28" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B656" s="28" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2">
+      <c r="A657" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B657" s="28" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2">
+      <c r="A658" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B658" s="28" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2">
+      <c r="A659" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B659" s="28" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2">
+      <c r="A660" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B660" s="28" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2">
+      <c r="A661" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B661" s="28" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2">
+      <c r="A662" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B662" s="28" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2">
+      <c r="A663" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B663" s="28" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2">
+      <c r="A664" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B664" s="28" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2">
+      <c r="A665" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B665" s="28" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2">
+      <c r="A666" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B666" s="28" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2">
+      <c r="A667" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B667" s="28" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2">
+      <c r="A668" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B668" s="28" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2">
+      <c r="A669" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B669" s="28" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2">
+      <c r="A670" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B670" s="28" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2">
+      <c r="A671" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B671" s="28" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2">
+      <c r="A672" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B672" s="28" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2">
+      <c r="A673" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B673" s="28" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2">
+      <c r="A674" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B674" s="28" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2">
+      <c r="A675" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B675" s="28" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2">
+      <c r="A676" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B676" s="28" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2">
+      <c r="A677" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B677" s="28" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2">
+      <c r="A678" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B678" s="28" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2">
+      <c r="A679" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B679" s="28" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2">
+      <c r="A680" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B680" s="28" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2">
+      <c r="A681" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B681" s="28" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2">
+      <c r="A682" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B682" s="28" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2">
+      <c r="A683" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B683" s="28" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2">
+      <c r="A684" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B684" s="28" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2">
+      <c r="A685" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B685" s="28" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2">
+      <c r="A686" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B686" s="28" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2">
+      <c r="A687" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B687" s="28" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2">
+      <c r="A688" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B688" s="28" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2">
+      <c r="A689" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B689" s="28" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2">
+      <c r="A690" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B690" s="28" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2">
+      <c r="A691" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B691" s="28" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2">
+      <c r="A692" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B692" s="28" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2">
+      <c r="A693" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B693" s="28" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2">
+      <c r="A694" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B694" s="28" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2">
+      <c r="A695" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B695" s="28" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2">
+      <c r="A696" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B696" s="28" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2">
+      <c r="A697" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B697" s="28" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2">
+      <c r="A698" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B698" s="28" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2">
+      <c r="A699" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B699" s="28" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2">
+      <c r="A700" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B700" s="28" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2">
+      <c r="A701" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B701" s="28" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2">
+      <c r="A702" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B702" s="28" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2">
+      <c r="A703" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B703" s="28" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2">
+      <c r="A704" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B704" s="28" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2">
+      <c r="A705" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B705" s="28" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2">
+      <c r="A706" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B706" s="28" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2">
+      <c r="A707" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B707" s="28" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2">
+      <c r="A708" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B708" s="28" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2">
+      <c r="A709" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B709" s="28" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2">
+      <c r="A710" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B710" s="28" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2">
+      <c r="A711" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B711" s="28" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2">
+      <c r="A712" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B712" s="28" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2">
+      <c r="A713" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B713" s="28" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2">
+      <c r="A714" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B714" s="28" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2">
+      <c r="A715" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B715" s="28" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2">
+      <c r="A716" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B716" s="28" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2">
+      <c r="A717" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B717" s="28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2">
+      <c r="A718" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B718" s="28" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2">
+      <c r="A719" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B719" s="28" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2">
+      <c r="A720" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B720" s="28" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2">
+      <c r="A721" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B721" s="28" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2">
+      <c r="A722" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B722" s="28" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2">
+      <c r="A723" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B723" s="28" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2">
+      <c r="A724" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B724" s="28" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2">
+      <c r="A725" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B725" s="28" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2">
+      <c r="A726" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B726" s="27" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2">
+      <c r="A727" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B727" s="27" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2">
+      <c r="A728" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B728" s="27" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2">
+      <c r="A729" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B729" s="27" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2">
+      <c r="A730" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B730" s="27" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2">
+      <c r="A731" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B731" s="27" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2">
+      <c r="A732" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B732" s="27" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2">
+      <c r="A733" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B733" s="27" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2">
+      <c r="A734" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B734" s="27" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2">
+      <c r="A735" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B735" s="27" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2">
+      <c r="A736" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B736" s="27" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2">
+      <c r="A737" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B737" s="27" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2">
+      <c r="A738" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B738" s="27" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2">
+      <c r="A739" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B739" s="27" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2">
+      <c r="A740" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B740" s="27" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2">
+      <c r="A741" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B741" s="27" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2">
+      <c r="A742" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B742" s="27" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2">
+      <c r="A743" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B743" s="27" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2">
+      <c r="A744" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B744" s="27" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2">
+      <c r="A745" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B745" s="27" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2">
+      <c r="A746" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B746" s="27" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2">
+      <c r="A747" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B747" s="27" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2">
+      <c r="A748" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B748" s="27" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2">
+      <c r="A749" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B749" s="27" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2">
+      <c r="A750" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B750" s="27" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2">
+      <c r="A751" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B751" s="27" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2">
+      <c r="A752" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B752" s="27" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2">
+      <c r="A753" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B753" s="27" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2">
+      <c r="A754" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B754" s="27" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2">
+      <c r="A755" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B755" s="27" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2">
+      <c r="A756" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B756" s="27" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2">
+      <c r="A757" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B757" s="27" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2">
+      <c r="A758" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B758" s="27" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2">
+      <c r="A759" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B759" s="27" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2">
+      <c r="A760" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B760" s="27" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2">
+      <c r="A761" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B761" s="27" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2">
+      <c r="A762" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B762" s="27" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2">
+      <c r="A763" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B763" s="27" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2">
+      <c r="A764" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B764" s="27" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2">
+      <c r="A765" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B765" s="27" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2">
+      <c r="A766" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B766" s="27" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2">
+      <c r="A767" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B767" s="27" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2">
+      <c r="A768" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B768" s="27" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2">
+      <c r="A769" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B769" s="27" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2">
+      <c r="A770" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B770" s="27" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2">
+      <c r="A771" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B771" s="27" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2">
+      <c r="A772" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B772" s="27" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2">
+      <c r="A773" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B773" s="27" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2">
+      <c r="A774" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B774" s="27" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2">
+      <c r="A775" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B775" s="27" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2">
+      <c r="A776" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B776" s="27" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2">
+      <c r="A777" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B777" s="27" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2">
+      <c r="A778" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B778" s="27" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2">
+      <c r="A779" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B779" s="27" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2">
+      <c r="A780" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B780" s="27" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2">
+      <c r="A781" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B781" s="27" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2">
+      <c r="A782" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B782" s="27" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2">
+      <c r="A783" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B783" s="27" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2">
+      <c r="A784" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B784" s="27" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2">
+      <c r="A785" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B785" s="27" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2">
+      <c r="A786" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B786" s="19" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2">
+      <c r="A787" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B787" s="19" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2">
+      <c r="A788" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B788" s="19" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2">
+      <c r="A789" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B789" s="19" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2">
+      <c r="A790" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B790" s="19" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2">
+      <c r="A791" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B791" s="19" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2">
+      <c r="A792" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B792" s="19" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2">
+      <c r="A793" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B793" s="19" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2">
+      <c r="A794" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B794" s="19" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2">
+      <c r="A795" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B795" s="19" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2">
+      <c r="A796" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B796" s="19" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2">
+      <c r="A797" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B797" s="19" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2">
+      <c r="A798" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B798" s="19" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2">
+      <c r="A799" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B799" s="19" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2">
+      <c r="A800" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B800" s="19" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2">
+      <c r="A801" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B801" s="19" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2">
+      <c r="A802" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B802" s="19" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2">
+      <c r="A803" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B803" s="19" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2">
+      <c r="A804" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B804" s="19" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2">
+      <c r="A805" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B805" s="19" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2">
+      <c r="A806" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B806" s="19" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2">
+      <c r="A807" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B807" s="19" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2">
+      <c r="A808" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B808" s="19" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2">
+      <c r="A809" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B809" s="19" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2">
+      <c r="A810" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B810" s="19" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2">
+      <c r="A811" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B811" s="19" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2">
+      <c r="A812" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B812" s="19" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2">
+      <c r="A813" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B813" s="19" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2">
+      <c r="A814" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B814" s="21" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2">
+      <c r="A815" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B815" s="21" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2">
+      <c r="A816" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B816" s="21" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2">
+      <c r="A817" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B817" s="21" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2">
+      <c r="A818" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B818" s="21" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2">
+      <c r="A819" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B819" s="21" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="820" spans="1:2">
+      <c r="A820" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B820" s="21" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="821" spans="1:2">
+      <c r="A821" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B821" s="21" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="822" spans="1:2">
+      <c r="A822" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B822" s="21" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="823" spans="1:2">
+      <c r="A823" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B823" s="21" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="824" spans="1:2">
+      <c r="A824" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B824" s="21" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="825" spans="1:2">
+      <c r="A825" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B825" s="21" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="826" spans="1:2">
+      <c r="A826" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B826" s="21" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="827" spans="1:2">
+      <c r="A827" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B827" s="21" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="828" spans="1:2">
+      <c r="A828" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B828" s="21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="829" spans="1:2">
+      <c r="A829" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B829" s="21" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="830" spans="1:2">
+      <c r="A830" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B830" s="21" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="831" spans="1:2">
+      <c r="A831" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B831" s="21" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="832" spans="1:2">
+      <c r="A832" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B832" s="21" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="833" spans="1:2">
+      <c r="A833" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B833" s="21" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="834" spans="1:2">
+      <c r="A834" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B834" s="21" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="835" spans="1:2">
+      <c r="A835" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B835" s="21" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="836" spans="1:2">
+      <c r="A836" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B836" s="21" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="837" spans="1:2">
+      <c r="A837" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B837" s="21" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="838" spans="1:2">
+      <c r="A838" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B838" s="21" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="839" spans="1:2">
+      <c r="A839" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B839" s="21" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="840" spans="1:2">
+      <c r="A840" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B840" s="21" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="841" spans="1:2">
+      <c r="A841" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B841" s="21" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="842" spans="1:2">
+      <c r="A842" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B842" s="20" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="843" spans="1:2">
+      <c r="A843" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B843" s="20" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="844" spans="1:2">
+      <c r="A844" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B844" s="20" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="845" spans="1:2">
+      <c r="A845" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B845" s="20" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="846" spans="1:2">
+      <c r="A846" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B846" s="20" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="847" spans="1:2">
+      <c r="A847" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B847" s="20" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="848" spans="1:2">
+      <c r="A848" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B848" s="20" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="849" spans="1:2">
+      <c r="A849" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B849" s="20" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="850" spans="1:2">
+      <c r="A850" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B850" s="20" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="851" spans="1:2">
+      <c r="A851" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B851" s="20" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="852" spans="1:2">
+      <c r="A852" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B852" s="20" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="853" spans="1:2">
+      <c r="A853" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B853" s="20" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="854" spans="1:2">
+      <c r="A854" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B854" s="20" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="855" spans="1:2">
+      <c r="A855" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B855" s="20" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="856" spans="1:2">
+      <c r="A856" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B856" s="20" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="857" spans="1:2">
+      <c r="A857" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B857" s="20" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="858" spans="1:2">
+      <c r="A858" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B858" s="20" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="859" spans="1:2">
+      <c r="A859" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B859" s="20" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="860" spans="1:2">
+      <c r="A860" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B860" s="20" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="861" spans="1:2">
+      <c r="A861" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B861" s="20" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="862" spans="1:2">
+      <c r="A862" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B862" s="20" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="863" spans="1:2">
+      <c r="A863" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B863" s="20" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="864" spans="1:2">
+      <c r="A864" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B864" s="20" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="865" spans="1:2">
+      <c r="A865" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B865" s="20" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="866" spans="1:2">
+      <c r="A866" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B866" s="20" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="867" spans="1:2">
+      <c r="A867" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B867" s="20" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="868" spans="1:2">
+      <c r="A868" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B868" s="20" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="869" spans="1:2">
+      <c r="A869" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B869" s="20" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="870" spans="1:2">
+      <c r="A870" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B870" s="19" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="871" spans="1:2">
+      <c r="A871" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B871" s="19" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="872" spans="1:2">
+      <c r="A872" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B872" s="19" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="873" spans="1:2">
+      <c r="A873" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B873" s="19" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="874" spans="1:2">
+      <c r="A874" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B874" s="19" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="875" spans="1:2">
+      <c r="A875" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B875" s="19" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="876" spans="1:2">
+      <c r="A876" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B876" s="19" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="877" spans="1:2">
+      <c r="A877" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B877" s="19" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="878" spans="1:2">
+      <c r="A878" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B878" s="19" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="879" spans="1:2">
+      <c r="A879" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B879" s="19" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="880" spans="1:2">
+      <c r="A880" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B880" s="19" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="881" spans="1:2">
+      <c r="A881" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B881" s="19" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="882" spans="1:2">
+      <c r="A882" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B882" s="19" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="883" spans="1:2">
+      <c r="A883" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B883" s="19" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="884" spans="1:2">
+      <c r="A884" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B884" s="19" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="885" spans="1:2">
+      <c r="A885" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B885" s="19" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="886" spans="1:2">
+      <c r="A886" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B886" s="19" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="887" spans="1:2">
+      <c r="A887" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B887" s="19" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="888" spans="1:2">
+      <c r="A888" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B888" s="19" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="889" spans="1:2">
+      <c r="A889" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B889" s="19" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="890" spans="1:2">
+      <c r="A890" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B890" s="21" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="891" spans="1:2">
+      <c r="A891" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B891" s="19" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="892" spans="1:2">
+      <c r="A892" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B892" s="19" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="893" spans="1:2">
+      <c r="A893" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B893" s="19" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="894" spans="1:2">
+      <c r="A894" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B894" s="19" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="895" spans="1:2">
+      <c r="A895" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B895" s="19" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="896" spans="1:2">
+      <c r="A896" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B896" s="19" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="897" spans="1:2">
+      <c r="A897" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B897" s="19" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="898" spans="1:2">
+      <c r="A898" s="29" t="s">
+        <v>840</v>
+      </c>
+      <c r="B898" s="30" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="899" spans="1:2">
+      <c r="A899" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B899" s="32" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="900" spans="1:2">
+      <c r="A900" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B900" s="32" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="901" spans="1:2">
+      <c r="A901" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B901" s="32" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="902" spans="1:2">
+      <c r="A902" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B902" s="32" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="903" spans="1:2">
+      <c r="A903" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B903" s="32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="904" spans="1:2">
+      <c r="A904" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B904" s="32" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="905" spans="1:2">
+      <c r="A905" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B905" s="33" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="906" spans="1:2">
+      <c r="A906" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B906" s="32" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="907" spans="1:2">
+      <c r="A907" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B907" s="32" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="908" spans="1:2">
+      <c r="A908" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B908" s="32" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="909" spans="1:2">
+      <c r="A909" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B909" s="32" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="910" spans="1:2">
+      <c r="A910" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B910" s="32" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="911" spans="1:2">
+      <c r="A911" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B911" s="32" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="912" spans="1:2">
+      <c r="A912" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B912" s="32" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="913" spans="1:2">
+      <c r="A913" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B913" s="32" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="914" spans="1:2">
+      <c r="A914" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B914" s="32" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="915" spans="1:2">
+      <c r="A915" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B915" s="32" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="916" spans="1:2">
+      <c r="A916" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B916" s="32" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="917" spans="1:2">
+      <c r="A917" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B917" s="32" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="918" spans="1:2">
+      <c r="A918" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B918" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="919" spans="1:2">
+      <c r="A919" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B919" s="32" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="920" spans="1:2">
+      <c r="A920" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B920" s="32" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="921" spans="1:2">
+      <c r="A921" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B921" s="32" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="922" spans="1:2">
+      <c r="A922" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B922" s="32" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="923" spans="1:2">
+      <c r="A923" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B923" s="32" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="924" spans="1:2">
+      <c r="A924" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B924" s="32" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="925" spans="1:2">
+      <c r="A925" s="31" t="s">
+        <v>840</v>
+      </c>
+      <c r="B925" s="32" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="926" spans="1:2">
+      <c r="A926" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B926" s="35" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="927" spans="1:2">
+      <c r="A927" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B927" s="35" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="928" spans="1:2">
+      <c r="A928" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B928" s="35" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="929" spans="1:2">
+      <c r="A929" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B929" s="35" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="930" spans="1:2">
+      <c r="A930" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B930" s="35" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="931" spans="1:2">
+      <c r="A931" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B931" s="35" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="932" spans="1:2">
+      <c r="A932" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B932" s="35" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="933" spans="1:2">
+      <c r="A933" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B933" s="35" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="934" spans="1:2">
+      <c r="A934" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B934" s="35" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="935" spans="1:2">
+      <c r="A935" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B935" s="35" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="936" spans="1:2">
+      <c r="A936" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B936" s="35" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="937" spans="1:2">
+      <c r="A937" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B937" s="35" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="938" spans="1:2">
+      <c r="A938" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B938" s="35" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="939" spans="1:2">
+      <c r="A939" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B939" s="35" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="940" spans="1:2">
+      <c r="A940" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B940" s="35" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="941" spans="1:2">
+      <c r="A941" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B941" s="35" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="942" spans="1:2">
+      <c r="A942" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B942" s="35" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="943" spans="1:2">
+      <c r="A943" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B943" s="35" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="944" spans="1:2">
+      <c r="A944" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B944" s="35" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="945" spans="1:2">
+      <c r="A945" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B945" s="35" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="946" spans="1:2">
+      <c r="A946" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B946" s="35" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="947" spans="1:2">
+      <c r="A947" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B947" s="35" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="948" spans="1:2">
+      <c r="A948" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B948" s="35" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="949" spans="1:2">
+      <c r="A949" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B949" s="35" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="950" spans="1:2">
+      <c r="A950" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B950" s="35" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="951" spans="1:2">
+      <c r="A951" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B951" s="35" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="952" spans="1:2">
+      <c r="A952" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B952" s="35" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="953" spans="1:2">
+      <c r="A953" s="36" t="s">
+        <v>858</v>
+      </c>
+      <c r="B953" s="35" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="954" spans="1:2">
+      <c r="A954" s="37" t="s">
+        <v>880</v>
+      </c>
+      <c r="B954" s="38" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="955" spans="1:2">
+      <c r="A955" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B955" s="38" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="956" spans="1:2">
+      <c r="A956" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B956" s="38" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="957" spans="1:2">
+      <c r="A957" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B957" s="38" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="958" spans="1:2">
+      <c r="A958" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B958" s="38" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="959" spans="1:2">
+      <c r="A959" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B959" s="38" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="960" spans="1:2">
+      <c r="A960" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B960" s="38" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="961" spans="1:2">
+      <c r="A961" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B961" s="38" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="962" spans="1:2">
+      <c r="A962" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B962" s="38" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="963" spans="1:2">
+      <c r="A963" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B963" s="38" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="964" spans="1:2">
+      <c r="A964" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B964" s="38" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="965" spans="1:2">
+      <c r="A965" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B965" s="38" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="966" spans="1:2">
+      <c r="A966" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B966" s="38" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="967" spans="1:2">
+      <c r="A967" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B967" s="38" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="968" spans="1:2">
+      <c r="A968" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B968" s="38" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="969" spans="1:2">
+      <c r="A969" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B969" s="38" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="970" spans="1:2">
+      <c r="A970" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B970" s="38" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="971" spans="1:2">
+      <c r="A971" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B971" s="38" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="972" spans="1:2">
+      <c r="A972" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B972" s="38" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="973" spans="1:2">
+      <c r="A973" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B973" s="38" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="974" spans="1:2">
+      <c r="A974" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B974" s="38" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="975" spans="1:2">
+      <c r="A975" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B975" s="38" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="976" spans="1:2">
+      <c r="A976" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B976" s="38" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="977" spans="1:2">
+      <c r="A977" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B977" s="38" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="978" spans="1:2">
+      <c r="A978" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B978" s="38" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="979" spans="1:2">
+      <c r="A979" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B979" s="38" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="980" spans="1:2">
+      <c r="A980" s="39" t="s">
+        <v>880</v>
+      </c>
+      <c r="B980" s="38" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="981" spans="1:2">
+      <c r="A981" s="40" t="s">
+        <v>880</v>
+      </c>
+      <c r="B981" s="38" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="982" spans="1:2">
+      <c r="A982" s="41" t="s">
+        <v>903</v>
+      </c>
+      <c r="B982" s="42" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="983" spans="1:2">
+      <c r="A983" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B983" s="42" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="984" spans="1:2">
+      <c r="A984" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B984" s="42" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="985" spans="1:2">
+      <c r="A985" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B985" s="42" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="986" spans="1:2">
+      <c r="A986" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B986" s="42" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="987" spans="1:2">
+      <c r="A987" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B987" s="42" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="988" spans="1:2">
+      <c r="A988" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B988" s="42" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="989" spans="1:2">
+      <c r="A989" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B989" s="42" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="990" spans="1:2">
+      <c r="A990" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B990" s="42" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="991" spans="1:2">
+      <c r="A991" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B991" s="42" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="992" spans="1:2">
+      <c r="A992" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B992" s="42" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="993" spans="1:2">
+      <c r="A993" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B993" s="42" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="994" spans="1:2">
+      <c r="A994" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B994" s="42" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="995" spans="1:2">
+      <c r="A995" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B995" s="42" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="996" spans="1:2">
+      <c r="A996" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B996" s="42" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="997" spans="1:2">
+      <c r="A997" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B997" s="42" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="998" spans="1:2">
+      <c r="A998" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B998" s="42" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="999" spans="1:2">
+      <c r="A999" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B999" s="42" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:2">
+      <c r="A1000" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B1000" s="42" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:2">
+      <c r="A1001" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B1001" s="42" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:2">
+      <c r="A1002" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B1002" s="42" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:2">
+      <c r="A1003" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B1003" s="42" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:2">
+      <c r="A1004" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B1004" s="42" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:2">
+      <c r="A1005" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B1005" s="42" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:2">
+      <c r="A1006" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B1006" s="42" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:2">
+      <c r="A1007" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B1007" s="42" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:2">
+      <c r="A1008" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B1008" s="42" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:2">
+      <c r="A1009" s="43" t="s">
+        <v>903</v>
+      </c>
+      <c r="B1009" s="42" t="s">
+        <v>377</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="B2:B344">
-    <cfRule type="cellIs" dxfId="20" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="43" operator="equal">
       <formula>"赤団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="39" operator="equal">
-      <formula>"青団"</formula>
+    <cfRule type="expression" dxfId="24" priority="47">
+      <formula>COUNTIF(INDIRECT("綱引き!A:Z"),B2)&gt;0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="46" operator="equal">
+      <formula>"黒団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="45" operator="equal">
       <formula>"黄団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="41" operator="equal">
-      <formula>"黒団"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="42">
-      <formula>COUNTIF(INDIRECT("綱引き!A:Z"),B2)&gt;0</formula>
+    <cfRule type="cellIs" dxfId="21" priority="44" operator="equal">
+      <formula>"青団"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B401:B425">
-    <cfRule type="cellIs" dxfId="15" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="14" operator="equal">
       <formula>"赤団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="15" operator="equal">
       <formula>"青団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="16" operator="equal">
       <formula>"黄団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="17" operator="equal">
       <formula>"黒団"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441:B515">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="10" operator="equal">
       <formula>"赤団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="11" operator="equal">
       <formula>"青団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="12" operator="equal">
       <formula>"黄団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="13" operator="equal">
       <formula>"黒団"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526:B545">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
       <formula>"赤団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
       <formula>"青団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
+      <formula>"黄団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
+      <formula>"黒団"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B786:B841 B870:B897">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+      <formula>"赤団"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="5">
+      <formula>COUNTIF(INDIRECT("女子棒取り!A:Z"),B786)&gt;0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+      <formula>"黒団"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"黄団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
-      <formula>"黒団"</formula>
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+      <formula>"青団"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C21 C43:C63">
-    <cfRule type="cellIs" dxfId="3" priority="101" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="106" operator="equal">
       <formula>"赤団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="102" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="107" operator="equal">
       <formula>"青団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="103" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="108" operator="equal">
       <formula>"黄団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="104" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="109" operator="equal">
       <formula>"黒団"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m2610025/Desktop/チェックイン/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3406BEA7-4F74-4B40-8023-2E399E5AFA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F97AB49E-17F9-4945-AB22-B4EDA734B9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{348E8972-E72E-5A4B-9183-B2C2B4112549}"/>
   </bookViews>
@@ -70,9 +70,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>佐久間琥太郎</t>
-  </si>
-  <si>
     <t>西祥一朗</t>
   </si>
   <si>
@@ -2721,15 +2718,19 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>佐久間琥太郎</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="179" formatCode="@&quot;(1)&quot;"/>
-    <numFmt numFmtId="180" formatCode="@&quot;(2)&quot;"/>
-    <numFmt numFmtId="181" formatCode="@&quot;(3)&quot;"/>
+    <numFmt numFmtId="176" formatCode="@&quot;(1)&quot;"/>
+    <numFmt numFmtId="177" formatCode="@&quot;(2)&quot;"/>
+    <numFmt numFmtId="178" formatCode="@&quot;(3)&quot;"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -3076,82 +3077,82 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3783,4616 +3784,4616 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>827</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>7</v>
+        <v>826</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>834</v>
       </c>
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>827</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>8</v>
+        <v>826</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>7</v>
       </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>827</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>9</v>
+        <v>826</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>8</v>
       </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>827</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>10</v>
+        <v>826</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>9</v>
       </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>827</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>11</v>
+        <v>826</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>10</v>
       </c>
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>827</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>12</v>
+        <v>826</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>11</v>
       </c>
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>827</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>13</v>
+        <v>826</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>827</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>14</v>
+        <v>826</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>13</v>
       </c>
       <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>827</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>15</v>
+        <v>826</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>14</v>
       </c>
       <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>827</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>16</v>
+        <v>826</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>15</v>
       </c>
       <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>827</v>
-      </c>
-      <c r="B12" s="18" t="s">
+        <v>826</v>
+      </c>
+      <c r="B12" s="17" t="s">
         <v>0</v>
       </c>
       <c r="C12" s="1"/>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>827</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>17</v>
+        <v>826</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>16</v>
       </c>
       <c r="C13" s="1"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>827</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>18</v>
+        <v>826</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>17</v>
       </c>
       <c r="C14" s="1"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>827</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>19</v>
+        <v>826</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>18</v>
       </c>
       <c r="C15" s="1"/>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>827</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>20</v>
+        <v>826</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>19</v>
       </c>
       <c r="C16" s="1"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>827</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>21</v>
+        <v>826</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>20</v>
       </c>
       <c r="C17" s="1"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>827</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>22</v>
+        <v>826</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>21</v>
       </c>
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>827</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>23</v>
+        <v>826</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>22</v>
       </c>
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>827</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>24</v>
+        <v>826</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>23</v>
       </c>
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3" ht="21" thickBot="1">
       <c r="A21" t="s">
-        <v>827</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>25</v>
+        <v>826</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>827</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>26</v>
+        <v>826</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>827</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>27</v>
+        <v>826</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>827</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>28</v>
+        <v>826</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>827</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>29</v>
+        <v>826</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>827</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>30</v>
+        <v>826</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>827</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>31</v>
+        <v>826</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>827</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>32</v>
+        <v>826</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>827</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>33</v>
+        <v>826</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>827</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>34</v>
+        <v>826</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>827</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>35</v>
+        <v>826</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>827</v>
-      </c>
-      <c r="B32" s="18" t="s">
-        <v>36</v>
+        <v>826</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>827</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>37</v>
+        <v>826</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>827</v>
-      </c>
-      <c r="B34" s="18" t="s">
-        <v>38</v>
+        <v>826</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>827</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>39</v>
+        <v>826</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="21" thickBot="1">
       <c r="A36" t="s">
-        <v>827</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>40</v>
+        <v>826</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>828</v>
-      </c>
-      <c r="B37" s="21" t="s">
-        <v>41</v>
+        <v>827</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>828</v>
-      </c>
-      <c r="B38" s="21" t="s">
-        <v>42</v>
+        <v>827</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>828</v>
-      </c>
-      <c r="B39" s="21" t="s">
-        <v>43</v>
+        <v>827</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>828</v>
-      </c>
-      <c r="B40" s="21" t="s">
-        <v>44</v>
+        <v>827</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>828</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>45</v>
+        <v>827</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>828</v>
-      </c>
-      <c r="B42" s="21" t="s">
-        <v>46</v>
+        <v>827</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>828</v>
-      </c>
-      <c r="B43" s="21" t="s">
+        <v>827</v>
+      </c>
+      <c r="B43" s="20" t="s">
         <v>4</v>
       </c>
       <c r="C43" s="5"/>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>828</v>
-      </c>
-      <c r="B44" s="21" t="s">
-        <v>47</v>
+        <v>827</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="C44" s="5"/>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>828</v>
-      </c>
-      <c r="B45" s="21" t="s">
-        <v>48</v>
+        <v>827</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>47</v>
       </c>
       <c r="C45" s="5"/>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>828</v>
-      </c>
-      <c r="B46" s="21" t="s">
-        <v>49</v>
+        <v>827</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>48</v>
       </c>
       <c r="C46" s="5"/>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>828</v>
-      </c>
-      <c r="B47" s="21" t="s">
-        <v>50</v>
+        <v>827</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>49</v>
       </c>
       <c r="C47" s="5"/>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>828</v>
-      </c>
-      <c r="B48" s="21" t="s">
-        <v>51</v>
+        <v>827</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>50</v>
       </c>
       <c r="C48" s="5"/>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>828</v>
-      </c>
-      <c r="B49" s="21" t="s">
-        <v>52</v>
+        <v>827</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>51</v>
       </c>
       <c r="C49" s="5"/>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>828</v>
-      </c>
-      <c r="B50" s="21" t="s">
-        <v>53</v>
+        <v>827</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>52</v>
       </c>
       <c r="C50" s="5"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>828</v>
-      </c>
-      <c r="B51" s="21" t="s">
-        <v>54</v>
+        <v>827</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>53</v>
       </c>
       <c r="C51" s="5"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>828</v>
-      </c>
-      <c r="B52" s="21" t="s">
-        <v>55</v>
+        <v>827</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>54</v>
       </c>
       <c r="C52" s="5"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>828</v>
-      </c>
-      <c r="B53" s="21" t="s">
-        <v>56</v>
+        <v>827</v>
+      </c>
+      <c r="B53" s="20" t="s">
+        <v>55</v>
       </c>
       <c r="C53" s="5"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>828</v>
-      </c>
-      <c r="B54" s="21" t="s">
-        <v>57</v>
+        <v>827</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>56</v>
       </c>
       <c r="C54" s="5"/>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>828</v>
-      </c>
-      <c r="B55" s="21" t="s">
-        <v>58</v>
+        <v>827</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>57</v>
       </c>
       <c r="C55" s="5"/>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>828</v>
-      </c>
-      <c r="B56" s="21" t="s">
-        <v>59</v>
+        <v>827</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>58</v>
       </c>
       <c r="C56" s="5"/>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>828</v>
-      </c>
-      <c r="B57" s="21" t="s">
-        <v>60</v>
+        <v>827</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>59</v>
       </c>
       <c r="C57" s="5"/>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>828</v>
-      </c>
-      <c r="B58" s="21" t="s">
+        <v>827</v>
+      </c>
+      <c r="B58" s="20" t="s">
         <v>1</v>
       </c>
       <c r="C58" s="5"/>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>828</v>
-      </c>
-      <c r="B59" s="21" t="s">
-        <v>61</v>
+        <v>827</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>60</v>
       </c>
       <c r="C59" s="5"/>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>828</v>
-      </c>
-      <c r="B60" s="21" t="s">
-        <v>62</v>
+        <v>827</v>
+      </c>
+      <c r="B60" s="20" t="s">
+        <v>61</v>
       </c>
       <c r="C60" s="5"/>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>828</v>
-      </c>
-      <c r="B61" s="21" t="s">
-        <v>63</v>
+        <v>827</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>62</v>
       </c>
       <c r="C61" s="5"/>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>828</v>
-      </c>
-      <c r="B62" s="21" t="s">
-        <v>64</v>
+        <v>827</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>63</v>
       </c>
       <c r="C62" s="5"/>
     </row>
     <row r="63" spans="1:3" ht="21" thickBot="1">
       <c r="A63" t="s">
-        <v>828</v>
-      </c>
-      <c r="B63" s="21" t="s">
-        <v>65</v>
+        <v>827</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="C63" s="6"/>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>828</v>
-      </c>
-      <c r="B64" s="21" t="s">
-        <v>66</v>
+        <v>827</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>828</v>
-      </c>
-      <c r="B65" s="21" t="s">
-        <v>67</v>
+        <v>827</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>828</v>
-      </c>
-      <c r="B66" s="21" t="s">
-        <v>68</v>
+        <v>827</v>
+      </c>
+      <c r="B66" s="20" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>828</v>
-      </c>
-      <c r="B67" s="21" t="s">
-        <v>69</v>
+        <v>827</v>
+      </c>
+      <c r="B67" s="20" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>828</v>
-      </c>
-      <c r="B68" s="21" t="s">
-        <v>70</v>
+        <v>827</v>
+      </c>
+      <c r="B68" s="20" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>828</v>
-      </c>
-      <c r="B69" s="21" t="s">
-        <v>71</v>
+        <v>827</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>828</v>
-      </c>
-      <c r="B70" s="21" t="s">
-        <v>72</v>
+        <v>827</v>
+      </c>
+      <c r="B70" s="20" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="21" thickBot="1">
       <c r="A71" t="s">
-        <v>828</v>
-      </c>
-      <c r="B71" s="22" t="s">
-        <v>73</v>
+        <v>827</v>
+      </c>
+      <c r="B71" s="21" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>829</v>
-      </c>
-      <c r="B72" s="23" t="s">
-        <v>74</v>
+        <v>828</v>
+      </c>
+      <c r="B72" s="22" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>829</v>
-      </c>
-      <c r="B73" s="23" t="s">
-        <v>75</v>
+        <v>828</v>
+      </c>
+      <c r="B73" s="22" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>829</v>
-      </c>
-      <c r="B74" s="23" t="s">
-        <v>76</v>
+        <v>828</v>
+      </c>
+      <c r="B74" s="22" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>829</v>
-      </c>
-      <c r="B75" s="23" t="s">
-        <v>77</v>
+        <v>828</v>
+      </c>
+      <c r="B75" s="22" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>829</v>
-      </c>
-      <c r="B76" s="23" t="s">
-        <v>78</v>
+        <v>828</v>
+      </c>
+      <c r="B76" s="22" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>829</v>
-      </c>
-      <c r="B77" s="23" t="s">
-        <v>79</v>
+        <v>828</v>
+      </c>
+      <c r="B77" s="22" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>829</v>
-      </c>
-      <c r="B78" s="23" t="s">
-        <v>80</v>
+        <v>828</v>
+      </c>
+      <c r="B78" s="22" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>829</v>
-      </c>
-      <c r="B79" s="23" t="s">
-        <v>81</v>
+        <v>828</v>
+      </c>
+      <c r="B79" s="22" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>829</v>
-      </c>
-      <c r="B80" s="23" t="s">
-        <v>82</v>
+        <v>828</v>
+      </c>
+      <c r="B80" s="22" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>829</v>
-      </c>
-      <c r="B81" s="23" t="s">
-        <v>83</v>
+        <v>828</v>
+      </c>
+      <c r="B81" s="22" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>829</v>
-      </c>
-      <c r="B82" s="23" t="s">
-        <v>84</v>
+        <v>828</v>
+      </c>
+      <c r="B82" s="22" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>829</v>
-      </c>
-      <c r="B83" s="23" t="s">
-        <v>85</v>
+        <v>828</v>
+      </c>
+      <c r="B83" s="22" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>829</v>
-      </c>
-      <c r="B84" s="23" t="s">
-        <v>86</v>
+        <v>828</v>
+      </c>
+      <c r="B84" s="22" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>829</v>
-      </c>
-      <c r="B85" s="23" t="s">
-        <v>87</v>
+        <v>828</v>
+      </c>
+      <c r="B85" s="22" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>829</v>
-      </c>
-      <c r="B86" s="23" t="s">
-        <v>88</v>
+        <v>828</v>
+      </c>
+      <c r="B86" s="22" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>829</v>
-      </c>
-      <c r="B87" s="23" t="s">
-        <v>89</v>
+        <v>828</v>
+      </c>
+      <c r="B87" s="22" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>829</v>
-      </c>
-      <c r="B88" s="23" t="s">
-        <v>90</v>
+        <v>828</v>
+      </c>
+      <c r="B88" s="22" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>829</v>
-      </c>
-      <c r="B89" s="23" t="s">
-        <v>91</v>
+        <v>828</v>
+      </c>
+      <c r="B89" s="22" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>829</v>
-      </c>
-      <c r="B90" s="23" t="s">
-        <v>92</v>
+        <v>828</v>
+      </c>
+      <c r="B90" s="22" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>829</v>
-      </c>
-      <c r="B91" s="23" t="s">
-        <v>93</v>
+        <v>828</v>
+      </c>
+      <c r="B91" s="22" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>829</v>
-      </c>
-      <c r="B92" s="23" t="s">
-        <v>94</v>
+        <v>828</v>
+      </c>
+      <c r="B92" s="22" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>829</v>
-      </c>
-      <c r="B93" s="23" t="s">
-        <v>95</v>
+        <v>828</v>
+      </c>
+      <c r="B93" s="22" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>829</v>
-      </c>
-      <c r="B94" s="23" t="s">
-        <v>96</v>
+        <v>828</v>
+      </c>
+      <c r="B94" s="22" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>829</v>
-      </c>
-      <c r="B95" s="23" t="s">
-        <v>97</v>
+        <v>828</v>
+      </c>
+      <c r="B95" s="22" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>829</v>
-      </c>
-      <c r="B96" s="23" t="s">
-        <v>98</v>
+        <v>828</v>
+      </c>
+      <c r="B96" s="22" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>829</v>
-      </c>
-      <c r="B97" s="23" t="s">
-        <v>99</v>
+        <v>828</v>
+      </c>
+      <c r="B97" s="22" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>829</v>
-      </c>
-      <c r="B98" s="23" t="s">
-        <v>100</v>
+        <v>828</v>
+      </c>
+      <c r="B98" s="22" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>829</v>
-      </c>
-      <c r="B99" s="23" t="s">
-        <v>101</v>
+        <v>828</v>
+      </c>
+      <c r="B99" s="22" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>829</v>
-      </c>
-      <c r="B100" s="23" t="s">
-        <v>102</v>
+        <v>828</v>
+      </c>
+      <c r="B100" s="22" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>829</v>
-      </c>
-      <c r="B101" s="23" t="s">
-        <v>103</v>
+        <v>828</v>
+      </c>
+      <c r="B101" s="22" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>829</v>
-      </c>
-      <c r="B102" s="23" t="s">
-        <v>104</v>
+        <v>828</v>
+      </c>
+      <c r="B102" s="22" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>829</v>
-      </c>
-      <c r="B103" s="23" t="s">
-        <v>105</v>
+        <v>828</v>
+      </c>
+      <c r="B103" s="22" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>829</v>
-      </c>
-      <c r="B104" s="23" t="s">
-        <v>106</v>
+        <v>828</v>
+      </c>
+      <c r="B104" s="22" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>829</v>
-      </c>
-      <c r="B105" s="23" t="s">
-        <v>107</v>
+        <v>828</v>
+      </c>
+      <c r="B105" s="22" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="106" spans="1:2" ht="21" thickBot="1">
       <c r="A106" t="s">
-        <v>829</v>
-      </c>
-      <c r="B106" s="24" t="s">
-        <v>108</v>
+        <v>828</v>
+      </c>
+      <c r="B106" s="23" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>830</v>
-      </c>
-      <c r="B107" s="18" t="s">
-        <v>109</v>
+        <v>829</v>
+      </c>
+      <c r="B107" s="17" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>830</v>
-      </c>
-      <c r="B108" s="18" t="s">
-        <v>110</v>
+        <v>829</v>
+      </c>
+      <c r="B108" s="17" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>830</v>
-      </c>
-      <c r="B109" s="18" t="s">
-        <v>111</v>
+        <v>829</v>
+      </c>
+      <c r="B109" s="17" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>830</v>
-      </c>
-      <c r="B110" s="18" t="s">
-        <v>112</v>
+        <v>829</v>
+      </c>
+      <c r="B110" s="17" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>830</v>
-      </c>
-      <c r="B111" s="18" t="s">
-        <v>113</v>
+        <v>829</v>
+      </c>
+      <c r="B111" s="17" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>830</v>
-      </c>
-      <c r="B112" s="18" t="s">
-        <v>114</v>
+        <v>829</v>
+      </c>
+      <c r="B112" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>830</v>
-      </c>
-      <c r="B113" s="18" t="s">
-        <v>115</v>
+        <v>829</v>
+      </c>
+      <c r="B113" s="17" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>830</v>
-      </c>
-      <c r="B114" s="18" t="s">
-        <v>116</v>
+        <v>829</v>
+      </c>
+      <c r="B114" s="17" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>830</v>
-      </c>
-      <c r="B115" s="18" t="s">
-        <v>117</v>
+        <v>829</v>
+      </c>
+      <c r="B115" s="17" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>830</v>
-      </c>
-      <c r="B116" s="18" t="s">
-        <v>118</v>
+        <v>829</v>
+      </c>
+      <c r="B116" s="17" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>830</v>
-      </c>
-      <c r="B117" s="18" t="s">
-        <v>119</v>
+        <v>829</v>
+      </c>
+      <c r="B117" s="17" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>830</v>
-      </c>
-      <c r="B118" s="18" t="s">
-        <v>120</v>
+        <v>829</v>
+      </c>
+      <c r="B118" s="17" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>830</v>
-      </c>
-      <c r="B119" s="18" t="s">
-        <v>121</v>
+        <v>829</v>
+      </c>
+      <c r="B119" s="17" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>830</v>
-      </c>
-      <c r="B120" s="18" t="s">
-        <v>122</v>
+        <v>829</v>
+      </c>
+      <c r="B120" s="17" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>830</v>
-      </c>
-      <c r="B121" s="18" t="s">
-        <v>123</v>
+        <v>829</v>
+      </c>
+      <c r="B121" s="17" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>830</v>
-      </c>
-      <c r="B122" s="18" t="s">
-        <v>124</v>
+        <v>829</v>
+      </c>
+      <c r="B122" s="17" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>830</v>
-      </c>
-      <c r="B123" s="18" t="s">
-        <v>125</v>
+        <v>829</v>
+      </c>
+      <c r="B123" s="17" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>830</v>
-      </c>
-      <c r="B124" s="18" t="s">
-        <v>126</v>
+        <v>829</v>
+      </c>
+      <c r="B124" s="17" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>830</v>
-      </c>
-      <c r="B125" s="18" t="s">
-        <v>127</v>
+        <v>829</v>
+      </c>
+      <c r="B125" s="17" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>830</v>
-      </c>
-      <c r="B126" s="18" t="s">
-        <v>128</v>
+        <v>829</v>
+      </c>
+      <c r="B126" s="17" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>830</v>
-      </c>
-      <c r="B127" s="18" t="s">
-        <v>129</v>
+        <v>829</v>
+      </c>
+      <c r="B127" s="17" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>830</v>
-      </c>
-      <c r="B128" s="18" t="s">
-        <v>130</v>
+        <v>829</v>
+      </c>
+      <c r="B128" s="17" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>830</v>
-      </c>
-      <c r="B129" s="18" t="s">
-        <v>131</v>
+        <v>829</v>
+      </c>
+      <c r="B129" s="17" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>830</v>
-      </c>
-      <c r="B130" s="18" t="s">
-        <v>132</v>
+        <v>829</v>
+      </c>
+      <c r="B130" s="17" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>830</v>
-      </c>
-      <c r="B131" s="18" t="s">
-        <v>133</v>
+        <v>829</v>
+      </c>
+      <c r="B131" s="17" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>830</v>
-      </c>
-      <c r="B132" s="18" t="s">
-        <v>134</v>
+        <v>829</v>
+      </c>
+      <c r="B132" s="17" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>830</v>
-      </c>
-      <c r="B133" s="18" t="s">
-        <v>135</v>
+        <v>829</v>
+      </c>
+      <c r="B133" s="17" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>830</v>
-      </c>
-      <c r="B134" s="18" t="s">
-        <v>136</v>
+        <v>829</v>
+      </c>
+      <c r="B134" s="17" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>830</v>
-      </c>
-      <c r="B135" s="18" t="s">
-        <v>137</v>
+        <v>829</v>
+      </c>
+      <c r="B135" s="17" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>830</v>
-      </c>
-      <c r="B136" s="18" t="s">
-        <v>138</v>
+        <v>829</v>
+      </c>
+      <c r="B136" s="17" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>830</v>
-      </c>
-      <c r="B137" s="18" t="s">
-        <v>139</v>
+        <v>829</v>
+      </c>
+      <c r="B137" s="17" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>830</v>
-      </c>
-      <c r="B138" s="18" t="s">
-        <v>140</v>
+        <v>829</v>
+      </c>
+      <c r="B138" s="17" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>830</v>
-      </c>
-      <c r="B139" s="18" t="s">
-        <v>141</v>
+        <v>829</v>
+      </c>
+      <c r="B139" s="17" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>830</v>
-      </c>
-      <c r="B140" s="18" t="s">
-        <v>142</v>
+        <v>829</v>
+      </c>
+      <c r="B140" s="17" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="141" spans="1:2" ht="21" thickBot="1">
       <c r="A141" t="s">
-        <v>830</v>
-      </c>
-      <c r="B141" s="20" t="s">
-        <v>143</v>
+        <v>829</v>
+      </c>
+      <c r="B141" s="19" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>827</v>
-      </c>
-      <c r="B142" s="25" t="s">
-        <v>144</v>
+        <v>826</v>
+      </c>
+      <c r="B142" s="24" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>827</v>
-      </c>
-      <c r="B143" s="26" t="s">
-        <v>145</v>
+        <v>826</v>
+      </c>
+      <c r="B143" s="25" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>827</v>
-      </c>
-      <c r="B144" s="26" t="s">
-        <v>146</v>
+        <v>826</v>
+      </c>
+      <c r="B144" s="25" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>827</v>
-      </c>
-      <c r="B145" s="26" t="s">
-        <v>147</v>
+        <v>826</v>
+      </c>
+      <c r="B145" s="25" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>827</v>
-      </c>
-      <c r="B146" s="26" t="s">
-        <v>148</v>
+        <v>826</v>
+      </c>
+      <c r="B146" s="25" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>827</v>
-      </c>
-      <c r="B147" s="26" t="s">
-        <v>149</v>
+        <v>826</v>
+      </c>
+      <c r="B147" s="25" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>827</v>
-      </c>
-      <c r="B148" s="26" t="s">
-        <v>150</v>
+        <v>826</v>
+      </c>
+      <c r="B148" s="25" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>827</v>
-      </c>
-      <c r="B149" s="26" t="s">
-        <v>151</v>
+        <v>826</v>
+      </c>
+      <c r="B149" s="25" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>827</v>
-      </c>
-      <c r="B150" s="26" t="s">
-        <v>152</v>
+        <v>826</v>
+      </c>
+      <c r="B150" s="25" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>827</v>
-      </c>
-      <c r="B151" s="26" t="s">
-        <v>153</v>
+        <v>826</v>
+      </c>
+      <c r="B151" s="25" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>827</v>
-      </c>
-      <c r="B152" s="26" t="s">
-        <v>154</v>
+        <v>826</v>
+      </c>
+      <c r="B152" s="25" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>827</v>
-      </c>
-      <c r="B153" s="26" t="s">
-        <v>155</v>
+        <v>826</v>
+      </c>
+      <c r="B153" s="25" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>827</v>
-      </c>
-      <c r="B154" s="26" t="s">
-        <v>156</v>
+        <v>826</v>
+      </c>
+      <c r="B154" s="25" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>827</v>
-      </c>
-      <c r="B155" s="26" t="s">
-        <v>157</v>
+        <v>826</v>
+      </c>
+      <c r="B155" s="25" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>827</v>
-      </c>
-      <c r="B156" s="26" t="s">
-        <v>158</v>
+        <v>826</v>
+      </c>
+      <c r="B156" s="25" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>827</v>
-      </c>
-      <c r="B157" s="26" t="s">
-        <v>159</v>
+        <v>826</v>
+      </c>
+      <c r="B157" s="25" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>827</v>
-      </c>
-      <c r="B158" s="26" t="s">
-        <v>160</v>
+        <v>826</v>
+      </c>
+      <c r="B158" s="25" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>827</v>
-      </c>
-      <c r="B159" s="26" t="s">
-        <v>161</v>
+        <v>826</v>
+      </c>
+      <c r="B159" s="25" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>827</v>
-      </c>
-      <c r="B160" s="26" t="s">
-        <v>162</v>
+        <v>826</v>
+      </c>
+      <c r="B160" s="25" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>827</v>
-      </c>
-      <c r="B161" s="26" t="s">
-        <v>163</v>
+        <v>826</v>
+      </c>
+      <c r="B161" s="25" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>827</v>
-      </c>
-      <c r="B162" s="26" t="s">
-        <v>164</v>
+        <v>826</v>
+      </c>
+      <c r="B162" s="25" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>827</v>
-      </c>
-      <c r="B163" s="26" t="s">
-        <v>165</v>
+        <v>826</v>
+      </c>
+      <c r="B163" s="25" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>827</v>
-      </c>
-      <c r="B164" s="26" t="s">
-        <v>166</v>
+        <v>826</v>
+      </c>
+      <c r="B164" s="25" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>827</v>
-      </c>
-      <c r="B165" s="26" t="s">
-        <v>167</v>
+        <v>826</v>
+      </c>
+      <c r="B165" s="25" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>827</v>
-      </c>
-      <c r="B166" s="26" t="s">
-        <v>168</v>
+        <v>826</v>
+      </c>
+      <c r="B166" s="25" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>827</v>
-      </c>
-      <c r="B167" s="26" t="s">
-        <v>169</v>
+        <v>826</v>
+      </c>
+      <c r="B167" s="25" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>827</v>
-      </c>
-      <c r="B168" s="26" t="s">
-        <v>170</v>
+        <v>826</v>
+      </c>
+      <c r="B168" s="25" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>827</v>
-      </c>
-      <c r="B169" s="26" t="s">
-        <v>171</v>
+        <v>826</v>
+      </c>
+      <c r="B169" s="25" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>827</v>
-      </c>
-      <c r="B170" s="26" t="s">
-        <v>172</v>
+        <v>826</v>
+      </c>
+      <c r="B170" s="25" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>827</v>
-      </c>
-      <c r="B171" s="26" t="s">
-        <v>173</v>
+        <v>826</v>
+      </c>
+      <c r="B171" s="25" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>827</v>
-      </c>
-      <c r="B172" s="26" t="s">
-        <v>174</v>
+        <v>826</v>
+      </c>
+      <c r="B172" s="25" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>827</v>
-      </c>
-      <c r="B173" s="26" t="s">
-        <v>175</v>
+        <v>826</v>
+      </c>
+      <c r="B173" s="25" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>827</v>
-      </c>
-      <c r="B174" s="26" t="s">
-        <v>176</v>
+        <v>826</v>
+      </c>
+      <c r="B174" s="25" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>827</v>
-      </c>
-      <c r="B175" s="26" t="s">
-        <v>177</v>
+        <v>826</v>
+      </c>
+      <c r="B175" s="25" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="176" spans="1:2" ht="21" thickBot="1">
       <c r="A176" t="s">
-        <v>827</v>
-      </c>
-      <c r="B176" s="27" t="s">
-        <v>178</v>
+        <v>826</v>
+      </c>
+      <c r="B176" s="26" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>831</v>
-      </c>
-      <c r="B177" s="28" t="s">
-        <v>179</v>
+        <v>830</v>
+      </c>
+      <c r="B177" s="27" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>831</v>
-      </c>
-      <c r="B178" s="28" t="s">
-        <v>180</v>
+        <v>830</v>
+      </c>
+      <c r="B178" s="27" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>831</v>
-      </c>
-      <c r="B179" s="28" t="s">
-        <v>181</v>
+        <v>830</v>
+      </c>
+      <c r="B179" s="27" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>831</v>
-      </c>
-      <c r="B180" s="28" t="s">
-        <v>182</v>
+        <v>830</v>
+      </c>
+      <c r="B180" s="27" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>831</v>
-      </c>
-      <c r="B181" s="28" t="s">
-        <v>183</v>
+        <v>830</v>
+      </c>
+      <c r="B181" s="27" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>831</v>
-      </c>
-      <c r="B182" s="28" t="s">
-        <v>184</v>
+        <v>830</v>
+      </c>
+      <c r="B182" s="27" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
-        <v>831</v>
-      </c>
-      <c r="B183" s="28" t="s">
-        <v>185</v>
+        <v>830</v>
+      </c>
+      <c r="B183" s="27" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" t="s">
-        <v>831</v>
-      </c>
-      <c r="B184" s="28" t="s">
-        <v>186</v>
+        <v>830</v>
+      </c>
+      <c r="B184" s="27" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" t="s">
-        <v>831</v>
-      </c>
-      <c r="B185" s="28" t="s">
-        <v>187</v>
+        <v>830</v>
+      </c>
+      <c r="B185" s="27" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" t="s">
-        <v>831</v>
-      </c>
-      <c r="B186" s="28" t="s">
-        <v>188</v>
+        <v>830</v>
+      </c>
+      <c r="B186" s="27" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" t="s">
-        <v>831</v>
-      </c>
-      <c r="B187" s="28" t="s">
-        <v>189</v>
+        <v>830</v>
+      </c>
+      <c r="B187" s="27" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
-        <v>831</v>
-      </c>
-      <c r="B188" s="28" t="s">
-        <v>190</v>
+        <v>830</v>
+      </c>
+      <c r="B188" s="27" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" t="s">
-        <v>831</v>
-      </c>
-      <c r="B189" s="28" t="s">
-        <v>191</v>
+        <v>830</v>
+      </c>
+      <c r="B189" s="27" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>831</v>
-      </c>
-      <c r="B190" s="28" t="s">
-        <v>192</v>
+        <v>830</v>
+      </c>
+      <c r="B190" s="27" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
-        <v>831</v>
-      </c>
-      <c r="B191" s="28" t="s">
-        <v>193</v>
+        <v>830</v>
+      </c>
+      <c r="B191" s="27" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" t="s">
-        <v>831</v>
-      </c>
-      <c r="B192" s="28" t="s">
-        <v>194</v>
+        <v>830</v>
+      </c>
+      <c r="B192" s="27" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" t="s">
-        <v>831</v>
-      </c>
-      <c r="B193" s="28" t="s">
-        <v>195</v>
+        <v>830</v>
+      </c>
+      <c r="B193" s="27" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>831</v>
-      </c>
-      <c r="B194" s="28" t="s">
-        <v>196</v>
+        <v>830</v>
+      </c>
+      <c r="B194" s="27" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" t="s">
-        <v>831</v>
-      </c>
-      <c r="B195" s="28" t="s">
-        <v>197</v>
+        <v>830</v>
+      </c>
+      <c r="B195" s="27" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
-        <v>831</v>
-      </c>
-      <c r="B196" s="28" t="s">
-        <v>198</v>
+        <v>830</v>
+      </c>
+      <c r="B196" s="27" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
-        <v>831</v>
-      </c>
-      <c r="B197" s="28" t="s">
+        <v>830</v>
+      </c>
+      <c r="B197" s="27" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" t="s">
-        <v>831</v>
-      </c>
-      <c r="B198" s="28" t="s">
-        <v>199</v>
+        <v>830</v>
+      </c>
+      <c r="B198" s="27" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
-        <v>831</v>
-      </c>
-      <c r="B199" s="28" t="s">
-        <v>200</v>
+        <v>830</v>
+      </c>
+      <c r="B199" s="27" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" t="s">
-        <v>831</v>
-      </c>
-      <c r="B200" s="28" t="s">
-        <v>201</v>
+        <v>830</v>
+      </c>
+      <c r="B200" s="27" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
-        <v>831</v>
-      </c>
-      <c r="B201" s="28" t="s">
-        <v>202</v>
+        <v>830</v>
+      </c>
+      <c r="B201" s="27" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>831</v>
-      </c>
-      <c r="B202" s="28" t="s">
-        <v>203</v>
+        <v>830</v>
+      </c>
+      <c r="B202" s="27" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
-        <v>831</v>
-      </c>
-      <c r="B203" s="28" t="s">
-        <v>204</v>
+        <v>830</v>
+      </c>
+      <c r="B203" s="27" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
-        <v>831</v>
-      </c>
-      <c r="B204" s="28" t="s">
-        <v>205</v>
+        <v>830</v>
+      </c>
+      <c r="B204" s="27" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" t="s">
-        <v>831</v>
-      </c>
-      <c r="B205" s="28" t="s">
-        <v>206</v>
+        <v>830</v>
+      </c>
+      <c r="B205" s="27" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" t="s">
-        <v>831</v>
-      </c>
-      <c r="B206" s="28" t="s">
-        <v>207</v>
+        <v>830</v>
+      </c>
+      <c r="B206" s="27" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
-        <v>831</v>
-      </c>
-      <c r="B207" s="28" t="s">
-        <v>208</v>
+        <v>830</v>
+      </c>
+      <c r="B207" s="27" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>831</v>
-      </c>
-      <c r="B208" s="28" t="s">
-        <v>209</v>
+        <v>830</v>
+      </c>
+      <c r="B208" s="27" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" t="s">
-        <v>831</v>
-      </c>
-      <c r="B209" s="28" t="s">
-        <v>210</v>
+        <v>830</v>
+      </c>
+      <c r="B209" s="27" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" t="s">
-        <v>831</v>
-      </c>
-      <c r="B210" s="28" t="s">
-        <v>211</v>
+        <v>830</v>
+      </c>
+      <c r="B210" s="27" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="211" spans="1:2" ht="21" thickBot="1">
       <c r="A211" t="s">
-        <v>831</v>
-      </c>
-      <c r="B211" s="29" t="s">
-        <v>212</v>
+        <v>830</v>
+      </c>
+      <c r="B211" s="28" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
-        <v>832</v>
-      </c>
-      <c r="B212" s="30" t="s">
-        <v>213</v>
+        <v>831</v>
+      </c>
+      <c r="B212" s="29" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="213" spans="1:2">
       <c r="A213" t="s">
-        <v>832</v>
-      </c>
-      <c r="B213" s="30" t="s">
-        <v>214</v>
+        <v>831</v>
+      </c>
+      <c r="B213" s="29" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
-        <v>832</v>
-      </c>
-      <c r="B214" s="30" t="s">
-        <v>215</v>
+        <v>831</v>
+      </c>
+      <c r="B214" s="29" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
-        <v>832</v>
-      </c>
-      <c r="B215" s="30" t="s">
-        <v>216</v>
+        <v>831</v>
+      </c>
+      <c r="B215" s="29" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="216" spans="1:2">
       <c r="A216" t="s">
-        <v>832</v>
-      </c>
-      <c r="B216" s="30" t="s">
-        <v>217</v>
+        <v>831</v>
+      </c>
+      <c r="B216" s="29" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>832</v>
-      </c>
-      <c r="B217" s="30" t="s">
-        <v>218</v>
+        <v>831</v>
+      </c>
+      <c r="B217" s="29" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>832</v>
-      </c>
-      <c r="B218" s="30" t="s">
-        <v>219</v>
+        <v>831</v>
+      </c>
+      <c r="B218" s="29" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="219" spans="1:2">
       <c r="A219" t="s">
-        <v>832</v>
-      </c>
-      <c r="B219" s="30" t="s">
-        <v>220</v>
+        <v>831</v>
+      </c>
+      <c r="B219" s="29" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>832</v>
-      </c>
-      <c r="B220" s="30" t="s">
-        <v>221</v>
+        <v>831</v>
+      </c>
+      <c r="B220" s="29" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="221" spans="1:2">
       <c r="A221" t="s">
-        <v>832</v>
-      </c>
-      <c r="B221" s="30" t="s">
-        <v>222</v>
+        <v>831</v>
+      </c>
+      <c r="B221" s="29" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>832</v>
-      </c>
-      <c r="B222" s="30" t="s">
-        <v>223</v>
+        <v>831</v>
+      </c>
+      <c r="B222" s="29" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>832</v>
-      </c>
-      <c r="B223" s="30" t="s">
-        <v>224</v>
+        <v>831</v>
+      </c>
+      <c r="B223" s="29" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" t="s">
-        <v>832</v>
-      </c>
-      <c r="B224" s="30" t="s">
-        <v>225</v>
+        <v>831</v>
+      </c>
+      <c r="B224" s="29" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>832</v>
-      </c>
-      <c r="B225" s="30" t="s">
-        <v>226</v>
+        <v>831</v>
+      </c>
+      <c r="B225" s="29" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226" t="s">
-        <v>832</v>
-      </c>
-      <c r="B226" s="30" t="s">
-        <v>227</v>
+        <v>831</v>
+      </c>
+      <c r="B226" s="29" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>832</v>
-      </c>
-      <c r="B227" s="30" t="s">
-        <v>228</v>
+        <v>831</v>
+      </c>
+      <c r="B227" s="29" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>832</v>
-      </c>
-      <c r="B228" s="30" t="s">
-        <v>229</v>
+        <v>831</v>
+      </c>
+      <c r="B228" s="29" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
-        <v>832</v>
-      </c>
-      <c r="B229" s="30" t="s">
-        <v>230</v>
+        <v>831</v>
+      </c>
+      <c r="B229" s="29" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>832</v>
-      </c>
-      <c r="B230" s="30" t="s">
-        <v>231</v>
+        <v>831</v>
+      </c>
+      <c r="B230" s="29" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>832</v>
-      </c>
-      <c r="B231" s="30" t="s">
-        <v>232</v>
+        <v>831</v>
+      </c>
+      <c r="B231" s="29" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="232" spans="1:2">
       <c r="A232" t="s">
-        <v>832</v>
-      </c>
-      <c r="B232" s="30" t="s">
-        <v>233</v>
+        <v>831</v>
+      </c>
+      <c r="B232" s="29" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>832</v>
-      </c>
-      <c r="B233" s="30" t="s">
-        <v>234</v>
+        <v>831</v>
+      </c>
+      <c r="B233" s="29" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
-        <v>832</v>
-      </c>
-      <c r="B234" s="30" t="s">
-        <v>235</v>
+        <v>831</v>
+      </c>
+      <c r="B234" s="29" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>832</v>
-      </c>
-      <c r="B235" s="30" t="s">
-        <v>236</v>
+        <v>831</v>
+      </c>
+      <c r="B235" s="29" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" t="s">
-        <v>832</v>
-      </c>
-      <c r="B236" s="30" t="s">
-        <v>237</v>
+        <v>831</v>
+      </c>
+      <c r="B236" s="29" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>832</v>
-      </c>
-      <c r="B237" s="30" t="s">
-        <v>238</v>
+        <v>831</v>
+      </c>
+      <c r="B237" s="29" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
-        <v>832</v>
-      </c>
-      <c r="B238" s="30" t="s">
-        <v>239</v>
+        <v>831</v>
+      </c>
+      <c r="B238" s="29" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
-        <v>832</v>
-      </c>
-      <c r="B239" s="30" t="s">
-        <v>240</v>
+        <v>831</v>
+      </c>
+      <c r="B239" s="29" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
-        <v>832</v>
-      </c>
-      <c r="B240" s="30" t="s">
-        <v>241</v>
+        <v>831</v>
+      </c>
+      <c r="B240" s="29" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
-        <v>832</v>
-      </c>
-      <c r="B241" s="30" t="s">
-        <v>242</v>
+        <v>831</v>
+      </c>
+      <c r="B241" s="29" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" t="s">
-        <v>832</v>
-      </c>
-      <c r="B242" s="30" t="s">
-        <v>243</v>
+        <v>831</v>
+      </c>
+      <c r="B242" s="29" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="243" spans="1:2">
       <c r="A243" t="s">
-        <v>832</v>
-      </c>
-      <c r="B243" s="30" t="s">
-        <v>244</v>
+        <v>831</v>
+      </c>
+      <c r="B243" s="29" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>832</v>
-      </c>
-      <c r="B244" s="30" t="s">
-        <v>245</v>
+        <v>831</v>
+      </c>
+      <c r="B244" s="29" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>832</v>
-      </c>
-      <c r="B245" s="30" t="s">
-        <v>246</v>
+        <v>831</v>
+      </c>
+      <c r="B245" s="29" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="246" spans="1:2" ht="21" thickBot="1">
       <c r="A246" t="s">
-        <v>832</v>
-      </c>
-      <c r="B246" s="31" t="s">
-        <v>247</v>
+        <v>831</v>
+      </c>
+      <c r="B246" s="30" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
-        <v>830</v>
-      </c>
-      <c r="B247" s="26" t="s">
-        <v>248</v>
+        <v>829</v>
+      </c>
+      <c r="B247" s="25" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
-        <v>830</v>
-      </c>
-      <c r="B248" s="26" t="s">
-        <v>249</v>
+        <v>829</v>
+      </c>
+      <c r="B248" s="25" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
-        <v>830</v>
-      </c>
-      <c r="B249" s="26" t="s">
-        <v>250</v>
+        <v>829</v>
+      </c>
+      <c r="B249" s="25" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>830</v>
-      </c>
-      <c r="B250" s="26" t="s">
-        <v>251</v>
+        <v>829</v>
+      </c>
+      <c r="B250" s="25" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>830</v>
-      </c>
-      <c r="B251" s="26" t="s">
-        <v>252</v>
+        <v>829</v>
+      </c>
+      <c r="B251" s="25" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="252" spans="1:2">
       <c r="A252" t="s">
-        <v>830</v>
-      </c>
-      <c r="B252" s="26" t="s">
-        <v>253</v>
+        <v>829</v>
+      </c>
+      <c r="B252" s="25" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>830</v>
-      </c>
-      <c r="B253" s="26" t="s">
-        <v>254</v>
+        <v>829</v>
+      </c>
+      <c r="B253" s="25" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>830</v>
-      </c>
-      <c r="B254" s="32" t="s">
-        <v>255</v>
+        <v>829</v>
+      </c>
+      <c r="B254" s="31" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>830</v>
-      </c>
-      <c r="B255" s="26" t="s">
-        <v>256</v>
+        <v>829</v>
+      </c>
+      <c r="B255" s="25" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>830</v>
-      </c>
-      <c r="B256" s="26" t="s">
-        <v>257</v>
+        <v>829</v>
+      </c>
+      <c r="B256" s="25" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>830</v>
-      </c>
-      <c r="B257" s="26" t="s">
-        <v>258</v>
+        <v>829</v>
+      </c>
+      <c r="B257" s="25" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>830</v>
-      </c>
-      <c r="B258" s="26" t="s">
-        <v>259</v>
+        <v>829</v>
+      </c>
+      <c r="B258" s="25" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>830</v>
-      </c>
-      <c r="B259" s="26" t="s">
-        <v>260</v>
+        <v>829</v>
+      </c>
+      <c r="B259" s="25" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" t="s">
-        <v>830</v>
-      </c>
-      <c r="B260" s="26" t="s">
-        <v>261</v>
+        <v>829</v>
+      </c>
+      <c r="B260" s="25" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" t="s">
-        <v>830</v>
-      </c>
-      <c r="B261" s="26" t="s">
-        <v>262</v>
+        <v>829</v>
+      </c>
+      <c r="B261" s="25" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="262" spans="1:2">
       <c r="A262" t="s">
-        <v>830</v>
-      </c>
-      <c r="B262" s="26" t="s">
-        <v>263</v>
+        <v>829</v>
+      </c>
+      <c r="B262" s="25" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="263" spans="1:2">
       <c r="A263" t="s">
-        <v>830</v>
-      </c>
-      <c r="B263" s="26" t="s">
-        <v>264</v>
+        <v>829</v>
+      </c>
+      <c r="B263" s="25" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="264" spans="1:2">
       <c r="A264" t="s">
-        <v>830</v>
-      </c>
-      <c r="B264" s="26" t="s">
-        <v>265</v>
+        <v>829</v>
+      </c>
+      <c r="B264" s="25" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="265" spans="1:2">
       <c r="A265" t="s">
-        <v>830</v>
-      </c>
-      <c r="B265" s="26" t="s">
-        <v>266</v>
+        <v>829</v>
+      </c>
+      <c r="B265" s="25" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="266" spans="1:2">
       <c r="A266" t="s">
-        <v>830</v>
-      </c>
-      <c r="B266" s="26" t="s">
-        <v>267</v>
+        <v>829</v>
+      </c>
+      <c r="B266" s="25" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="267" spans="1:2">
       <c r="A267" t="s">
-        <v>830</v>
-      </c>
-      <c r="B267" s="26" t="s">
-        <v>268</v>
+        <v>829</v>
+      </c>
+      <c r="B267" s="25" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>830</v>
-      </c>
-      <c r="B268" s="26" t="s">
-        <v>269</v>
+        <v>829</v>
+      </c>
+      <c r="B268" s="25" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>830</v>
-      </c>
-      <c r="B269" s="26" t="s">
-        <v>270</v>
+        <v>829</v>
+      </c>
+      <c r="B269" s="25" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="270" spans="1:2">
       <c r="A270" t="s">
-        <v>830</v>
-      </c>
-      <c r="B270" s="26" t="s">
-        <v>271</v>
+        <v>829</v>
+      </c>
+      <c r="B270" s="25" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>830</v>
-      </c>
-      <c r="B271" s="26" t="s">
-        <v>272</v>
+        <v>829</v>
+      </c>
+      <c r="B271" s="25" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>830</v>
-      </c>
-      <c r="B272" s="26" t="s">
-        <v>273</v>
+        <v>829</v>
+      </c>
+      <c r="B272" s="25" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>830</v>
-      </c>
-      <c r="B273" s="26" t="s">
-        <v>274</v>
+        <v>829</v>
+      </c>
+      <c r="B273" s="25" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>830</v>
-      </c>
-      <c r="B274" s="26" t="s">
-        <v>275</v>
+        <v>829</v>
+      </c>
+      <c r="B274" s="25" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>830</v>
-      </c>
-      <c r="B275" s="26" t="s">
-        <v>276</v>
+        <v>829</v>
+      </c>
+      <c r="B275" s="25" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" t="s">
-        <v>830</v>
-      </c>
-      <c r="B276" s="26" t="s">
-        <v>277</v>
+        <v>829</v>
+      </c>
+      <c r="B276" s="25" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" t="s">
-        <v>830</v>
-      </c>
-      <c r="B277" s="26" t="s">
-        <v>278</v>
+        <v>829</v>
+      </c>
+      <c r="B277" s="25" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>830</v>
-      </c>
-      <c r="B278" s="26" t="s">
-        <v>279</v>
+        <v>829</v>
+      </c>
+      <c r="B278" s="25" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="279" spans="1:2">
       <c r="A279" t="s">
-        <v>830</v>
-      </c>
-      <c r="B279" s="26" t="s">
-        <v>280</v>
+        <v>829</v>
+      </c>
+      <c r="B279" s="25" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" t="s">
-        <v>830</v>
-      </c>
-      <c r="B280" s="26" t="s">
-        <v>281</v>
+        <v>829</v>
+      </c>
+      <c r="B280" s="25" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="281" spans="1:2" ht="21" thickBot="1">
       <c r="A281" t="s">
-        <v>830</v>
-      </c>
-      <c r="B281" s="27" t="s">
-        <v>282</v>
+        <v>829</v>
+      </c>
+      <c r="B281" s="26" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="282" spans="1:2">
       <c r="A282" t="s">
-        <v>827</v>
-      </c>
-      <c r="B282" s="33" t="s">
-        <v>283</v>
+        <v>826</v>
+      </c>
+      <c r="B282" s="32" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="283" spans="1:2">
       <c r="A283" t="s">
-        <v>827</v>
-      </c>
-      <c r="B283" s="34" t="s">
-        <v>284</v>
+        <v>826</v>
+      </c>
+      <c r="B283" s="33" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>827</v>
-      </c>
-      <c r="B284" s="34" t="s">
-        <v>285</v>
+        <v>826</v>
+      </c>
+      <c r="B284" s="33" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>827</v>
-      </c>
-      <c r="B285" s="34" t="s">
-        <v>286</v>
+        <v>826</v>
+      </c>
+      <c r="B285" s="33" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>827</v>
-      </c>
-      <c r="B286" s="34" t="s">
-        <v>287</v>
+        <v>826</v>
+      </c>
+      <c r="B286" s="33" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="287" spans="1:2">
       <c r="A287" t="s">
-        <v>827</v>
-      </c>
-      <c r="B287" s="34" t="s">
-        <v>288</v>
+        <v>826</v>
+      </c>
+      <c r="B287" s="33" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
-        <v>827</v>
-      </c>
-      <c r="B288" s="34" t="s">
-        <v>289</v>
+        <v>826</v>
+      </c>
+      <c r="B288" s="33" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" t="s">
-        <v>827</v>
-      </c>
-      <c r="B289" s="34" t="s">
-        <v>290</v>
+        <v>826</v>
+      </c>
+      <c r="B289" s="33" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" t="s">
-        <v>827</v>
-      </c>
-      <c r="B290" s="34" t="s">
-        <v>291</v>
+        <v>826</v>
+      </c>
+      <c r="B290" s="33" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="291" spans="1:2">
       <c r="A291" t="s">
-        <v>827</v>
-      </c>
-      <c r="B291" s="34" t="s">
-        <v>292</v>
+        <v>826</v>
+      </c>
+      <c r="B291" s="33" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
-        <v>827</v>
-      </c>
-      <c r="B292" s="34" t="s">
-        <v>293</v>
+        <v>826</v>
+      </c>
+      <c r="B292" s="33" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="293" spans="1:2">
       <c r="A293" t="s">
-        <v>827</v>
-      </c>
-      <c r="B293" s="34" t="s">
-        <v>294</v>
+        <v>826</v>
+      </c>
+      <c r="B293" s="33" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="294" spans="1:2">
       <c r="A294" t="s">
-        <v>827</v>
-      </c>
-      <c r="B294" s="34" t="s">
-        <v>295</v>
+        <v>826</v>
+      </c>
+      <c r="B294" s="33" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="295" spans="1:2">
       <c r="A295" t="s">
-        <v>827</v>
-      </c>
-      <c r="B295" s="34" t="s">
-        <v>296</v>
+        <v>826</v>
+      </c>
+      <c r="B295" s="33" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="296" spans="1:2">
       <c r="A296" t="s">
-        <v>827</v>
-      </c>
-      <c r="B296" s="34" t="s">
-        <v>297</v>
+        <v>826</v>
+      </c>
+      <c r="B296" s="33" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" t="s">
-        <v>827</v>
-      </c>
-      <c r="B297" s="34" t="s">
-        <v>298</v>
+        <v>826</v>
+      </c>
+      <c r="B297" s="33" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>827</v>
-      </c>
-      <c r="B298" s="34" t="s">
-        <v>299</v>
+        <v>826</v>
+      </c>
+      <c r="B298" s="33" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
-        <v>827</v>
-      </c>
-      <c r="B299" s="34" t="s">
-        <v>300</v>
+        <v>826</v>
+      </c>
+      <c r="B299" s="33" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="300" spans="1:2">
       <c r="A300" t="s">
-        <v>827</v>
-      </c>
-      <c r="B300" s="34" t="s">
-        <v>301</v>
+        <v>826</v>
+      </c>
+      <c r="B300" s="33" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="301" spans="1:2">
       <c r="A301" t="s">
-        <v>827</v>
-      </c>
-      <c r="B301" s="34" t="s">
-        <v>302</v>
+        <v>826</v>
+      </c>
+      <c r="B301" s="33" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="302" spans="1:2" ht="21" thickBot="1">
       <c r="A302" t="s">
-        <v>827</v>
-      </c>
-      <c r="B302" s="35" t="s">
-        <v>303</v>
+        <v>826</v>
+      </c>
+      <c r="B302" s="34" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>833</v>
-      </c>
-      <c r="B303" s="36" t="s">
-        <v>304</v>
+        <v>832</v>
+      </c>
+      <c r="B303" s="35" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="304" spans="1:2">
       <c r="A304" t="s">
-        <v>833</v>
-      </c>
-      <c r="B304" s="36" t="s">
-        <v>305</v>
+        <v>832</v>
+      </c>
+      <c r="B304" s="35" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
-        <v>833</v>
-      </c>
-      <c r="B305" s="36" t="s">
-        <v>306</v>
+        <v>832</v>
+      </c>
+      <c r="B305" s="35" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
-        <v>833</v>
-      </c>
-      <c r="B306" s="36" t="s">
-        <v>307</v>
+        <v>832</v>
+      </c>
+      <c r="B306" s="35" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="307" spans="1:2">
       <c r="A307" t="s">
-        <v>833</v>
-      </c>
-      <c r="B307" s="36" t="s">
-        <v>308</v>
+        <v>832</v>
+      </c>
+      <c r="B307" s="35" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="308" spans="1:2">
       <c r="A308" t="s">
-        <v>833</v>
-      </c>
-      <c r="B308" s="36" t="s">
-        <v>309</v>
+        <v>832</v>
+      </c>
+      <c r="B308" s="35" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="309" spans="1:2">
       <c r="A309" t="s">
-        <v>833</v>
-      </c>
-      <c r="B309" s="36" t="s">
-        <v>310</v>
+        <v>832</v>
+      </c>
+      <c r="B309" s="35" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="310" spans="1:2">
       <c r="A310" t="s">
-        <v>833</v>
-      </c>
-      <c r="B310" s="36" t="s">
-        <v>311</v>
+        <v>832</v>
+      </c>
+      <c r="B310" s="35" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="311" spans="1:2">
       <c r="A311" t="s">
-        <v>833</v>
-      </c>
-      <c r="B311" s="36" t="s">
-        <v>312</v>
+        <v>832</v>
+      </c>
+      <c r="B311" s="35" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>833</v>
-      </c>
-      <c r="B312" s="36" t="s">
+        <v>832</v>
+      </c>
+      <c r="B312" s="35" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>833</v>
-      </c>
-      <c r="B313" s="36" t="s">
-        <v>313</v>
+        <v>832</v>
+      </c>
+      <c r="B313" s="35" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="314" spans="1:2">
       <c r="A314" t="s">
-        <v>833</v>
-      </c>
-      <c r="B314" s="36" t="s">
-        <v>314</v>
+        <v>832</v>
+      </c>
+      <c r="B314" s="35" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="315" spans="1:2">
       <c r="A315" t="s">
-        <v>833</v>
-      </c>
-      <c r="B315" s="36" t="s">
-        <v>315</v>
+        <v>832</v>
+      </c>
+      <c r="B315" s="35" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>833</v>
-      </c>
-      <c r="B316" s="36" t="s">
-        <v>316</v>
+        <v>832</v>
+      </c>
+      <c r="B316" s="35" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="317" spans="1:2">
       <c r="A317" t="s">
-        <v>833</v>
-      </c>
-      <c r="B317" s="36" t="s">
-        <v>317</v>
+        <v>832</v>
+      </c>
+      <c r="B317" s="35" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="318" spans="1:2">
       <c r="A318" t="s">
-        <v>833</v>
-      </c>
-      <c r="B318" s="36" t="s">
-        <v>318</v>
+        <v>832</v>
+      </c>
+      <c r="B318" s="35" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>833</v>
-      </c>
-      <c r="B319" s="36" t="s">
-        <v>319</v>
+        <v>832</v>
+      </c>
+      <c r="B319" s="35" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>833</v>
-      </c>
-      <c r="B320" s="36" t="s">
-        <v>320</v>
+        <v>832</v>
+      </c>
+      <c r="B320" s="35" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>833</v>
-      </c>
-      <c r="B321" s="36" t="s">
-        <v>321</v>
+        <v>832</v>
+      </c>
+      <c r="B321" s="35" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>833</v>
-      </c>
-      <c r="B322" s="36" t="s">
-        <v>322</v>
+        <v>832</v>
+      </c>
+      <c r="B322" s="35" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="323" spans="1:2" ht="21" thickBot="1">
       <c r="A323" t="s">
-        <v>833</v>
-      </c>
-      <c r="B323" s="37" t="s">
-        <v>323</v>
+        <v>832</v>
+      </c>
+      <c r="B323" s="36" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>834</v>
-      </c>
-      <c r="B324" s="38" t="s">
-        <v>324</v>
+        <v>833</v>
+      </c>
+      <c r="B324" s="37" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>834</v>
-      </c>
-      <c r="B325" s="38" t="s">
-        <v>325</v>
+        <v>833</v>
+      </c>
+      <c r="B325" s="37" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="326" spans="1:2">
       <c r="A326" t="s">
-        <v>834</v>
-      </c>
-      <c r="B326" s="38" t="s">
-        <v>326</v>
+        <v>833</v>
+      </c>
+      <c r="B326" s="37" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>834</v>
-      </c>
-      <c r="B327" s="38" t="s">
-        <v>327</v>
+        <v>833</v>
+      </c>
+      <c r="B327" s="37" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>834</v>
-      </c>
-      <c r="B328" s="38" t="s">
-        <v>328</v>
+        <v>833</v>
+      </c>
+      <c r="B328" s="37" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>834</v>
-      </c>
-      <c r="B329" s="38" t="s">
-        <v>329</v>
+        <v>833</v>
+      </c>
+      <c r="B329" s="37" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
-        <v>834</v>
-      </c>
-      <c r="B330" s="38" t="s">
-        <v>330</v>
+        <v>833</v>
+      </c>
+      <c r="B330" s="37" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>834</v>
-      </c>
-      <c r="B331" s="38" t="s">
-        <v>331</v>
+        <v>833</v>
+      </c>
+      <c r="B331" s="37" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="332" spans="1:2">
       <c r="A332" t="s">
-        <v>834</v>
-      </c>
-      <c r="B332" s="39" t="s">
-        <v>332</v>
+        <v>833</v>
+      </c>
+      <c r="B332" s="38" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>834</v>
-      </c>
-      <c r="B333" s="38" t="s">
-        <v>333</v>
+        <v>833</v>
+      </c>
+      <c r="B333" s="37" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>834</v>
-      </c>
-      <c r="B334" s="38" t="s">
-        <v>334</v>
+        <v>833</v>
+      </c>
+      <c r="B334" s="37" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
-        <v>834</v>
-      </c>
-      <c r="B335" s="38" t="s">
-        <v>335</v>
+        <v>833</v>
+      </c>
+      <c r="B335" s="37" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="336" spans="1:2">
       <c r="A336" t="s">
-        <v>834</v>
-      </c>
-      <c r="B336" s="38" t="s">
-        <v>336</v>
+        <v>833</v>
+      </c>
+      <c r="B336" s="37" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="A337" t="s">
-        <v>834</v>
-      </c>
-      <c r="B337" s="38" t="s">
-        <v>337</v>
+        <v>833</v>
+      </c>
+      <c r="B337" s="37" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="338" spans="1:2">
       <c r="A338" t="s">
-        <v>834</v>
-      </c>
-      <c r="B338" s="38" t="s">
-        <v>338</v>
+        <v>833</v>
+      </c>
+      <c r="B338" s="37" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="339" spans="1:2">
       <c r="A339" t="s">
-        <v>834</v>
-      </c>
-      <c r="B339" s="38" t="s">
-        <v>339</v>
+        <v>833</v>
+      </c>
+      <c r="B339" s="37" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" t="s">
-        <v>834</v>
-      </c>
-      <c r="B340" s="38" t="s">
-        <v>340</v>
+        <v>833</v>
+      </c>
+      <c r="B340" s="37" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="341" spans="1:2">
       <c r="A341" t="s">
-        <v>834</v>
-      </c>
-      <c r="B341" s="38" t="s">
-        <v>341</v>
+        <v>833</v>
+      </c>
+      <c r="B341" s="37" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="A342" t="s">
-        <v>834</v>
-      </c>
-      <c r="B342" s="38" t="s">
-        <v>342</v>
+        <v>833</v>
+      </c>
+      <c r="B342" s="37" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
-        <v>834</v>
-      </c>
-      <c r="B343" s="38" t="s">
-        <v>343</v>
+        <v>833</v>
+      </c>
+      <c r="B343" s="37" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="344" spans="1:2" ht="21" thickBot="1">
       <c r="A344" t="s">
-        <v>834</v>
-      </c>
-      <c r="B344" s="40" t="s">
-        <v>344</v>
+        <v>833</v>
+      </c>
+      <c r="B344" s="39" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="A345" t="s">
-        <v>830</v>
-      </c>
-      <c r="B345" s="41" t="s">
-        <v>345</v>
+        <v>829</v>
+      </c>
+      <c r="B345" s="40" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="A346" t="s">
-        <v>830</v>
-      </c>
-      <c r="B346" s="41" t="s">
-        <v>346</v>
+        <v>829</v>
+      </c>
+      <c r="B346" s="40" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="347" spans="1:2">
       <c r="A347" t="s">
-        <v>830</v>
-      </c>
-      <c r="B347" s="41" t="s">
-        <v>347</v>
+        <v>829</v>
+      </c>
+      <c r="B347" s="40" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="348" spans="1:2">
       <c r="A348" t="s">
-        <v>830</v>
-      </c>
-      <c r="B348" s="41" t="s">
-        <v>348</v>
+        <v>829</v>
+      </c>
+      <c r="B348" s="40" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="349" spans="1:2">
       <c r="A349" t="s">
-        <v>830</v>
-      </c>
-      <c r="B349" s="41" t="s">
-        <v>349</v>
+        <v>829</v>
+      </c>
+      <c r="B349" s="40" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="350" spans="1:2">
       <c r="A350" t="s">
-        <v>830</v>
-      </c>
-      <c r="B350" s="41" t="s">
-        <v>350</v>
+        <v>829</v>
+      </c>
+      <c r="B350" s="40" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="351" spans="1:2">
       <c r="A351" t="s">
-        <v>830</v>
-      </c>
-      <c r="B351" s="41" t="s">
-        <v>351</v>
+        <v>829</v>
+      </c>
+      <c r="B351" s="40" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="352" spans="1:2">
       <c r="A352" t="s">
-        <v>830</v>
-      </c>
-      <c r="B352" s="41" t="s">
-        <v>352</v>
+        <v>829</v>
+      </c>
+      <c r="B352" s="40" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="353" spans="1:2">
       <c r="A353" t="s">
-        <v>830</v>
-      </c>
-      <c r="B353" s="41" t="s">
-        <v>353</v>
+        <v>829</v>
+      </c>
+      <c r="B353" s="40" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="354" spans="1:2">
       <c r="A354" t="s">
-        <v>830</v>
-      </c>
-      <c r="B354" s="41" t="s">
-        <v>354</v>
+        <v>829</v>
+      </c>
+      <c r="B354" s="40" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="355" spans="1:2">
       <c r="A355" t="s">
-        <v>830</v>
-      </c>
-      <c r="B355" s="41" t="s">
-        <v>355</v>
+        <v>829</v>
+      </c>
+      <c r="B355" s="40" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="356" spans="1:2">
       <c r="A356" t="s">
-        <v>830</v>
-      </c>
-      <c r="B356" s="41" t="s">
-        <v>356</v>
+        <v>829</v>
+      </c>
+      <c r="B356" s="40" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="357" spans="1:2">
       <c r="A357" t="s">
-        <v>830</v>
-      </c>
-      <c r="B357" s="41" t="s">
-        <v>357</v>
+        <v>829</v>
+      </c>
+      <c r="B357" s="40" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="358" spans="1:2">
       <c r="A358" t="s">
-        <v>830</v>
-      </c>
-      <c r="B358" s="41" t="s">
-        <v>358</v>
+        <v>829</v>
+      </c>
+      <c r="B358" s="40" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" t="s">
-        <v>830</v>
-      </c>
-      <c r="B359" s="41" t="s">
-        <v>359</v>
+        <v>829</v>
+      </c>
+      <c r="B359" s="40" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
-        <v>830</v>
-      </c>
-      <c r="B360" s="41" t="s">
-        <v>360</v>
+        <v>829</v>
+      </c>
+      <c r="B360" s="40" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="361" spans="1:2">
       <c r="A361" t="s">
-        <v>830</v>
-      </c>
-      <c r="B361" s="41" t="s">
-        <v>361</v>
+        <v>829</v>
+      </c>
+      <c r="B361" s="40" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="362" spans="1:2">
       <c r="A362" t="s">
-        <v>830</v>
-      </c>
-      <c r="B362" s="41" t="s">
-        <v>362</v>
+        <v>829</v>
+      </c>
+      <c r="B362" s="40" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" t="s">
-        <v>830</v>
-      </c>
-      <c r="B363" s="41" t="s">
-        <v>363</v>
+        <v>829</v>
+      </c>
+      <c r="B363" s="40" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
-        <v>830</v>
-      </c>
-      <c r="B364" s="41" t="s">
-        <v>364</v>
+        <v>829</v>
+      </c>
+      <c r="B364" s="40" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="365" spans="1:2" ht="21" thickBot="1">
       <c r="A365" t="s">
-        <v>830</v>
-      </c>
-      <c r="B365" s="42" t="s">
-        <v>365</v>
+        <v>829</v>
+      </c>
+      <c r="B365" s="41" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="366" spans="1:2">
       <c r="A366" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B366" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B367" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="368" spans="1:2">
       <c r="A368" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B368" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="369" spans="1:2">
       <c r="A369" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B369" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="370" spans="1:2">
       <c r="A370" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B370" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="371" spans="1:2">
       <c r="A371" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B371" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="372" spans="1:2">
       <c r="A372" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B372" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="373" spans="1:2">
       <c r="A373" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B373" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="374" spans="1:2">
       <c r="A374" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B374" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="375" spans="1:2">
       <c r="A375" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B375" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="376" spans="1:2">
       <c r="A376" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B376" s="7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="377" spans="1:2">
       <c r="A377" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B377" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="378" spans="1:2">
       <c r="A378" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B378" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="379" spans="1:2">
       <c r="A379" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B379" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="380" spans="1:2">
       <c r="A380" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B380" s="7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="381" spans="1:2">
       <c r="A381" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B381" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="382" spans="1:2">
       <c r="A382" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B382" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="383" spans="1:2">
       <c r="A383" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B383" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="384" spans="1:2">
       <c r="A384" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B384" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="385" spans="1:2">
       <c r="A385" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B385" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="386" spans="1:2">
       <c r="A386" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B386" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="387" spans="1:2">
       <c r="A387" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B387" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="388" spans="1:2">
       <c r="A388" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B388" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="389" spans="1:2">
       <c r="A389" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B389" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="390" spans="1:2">
       <c r="A390" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B390" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="391" spans="1:2">
       <c r="A391" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B391" s="8" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="392" spans="1:2">
       <c r="A392" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B392" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="393" spans="1:2">
       <c r="A393" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B393" s="8" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="394" spans="1:2">
       <c r="A394" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B394" s="8" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B395" s="8" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="396" spans="1:2">
       <c r="A396" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B396" s="8" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="397" spans="1:2">
       <c r="A397" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B397" s="8" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="398" spans="1:2">
       <c r="A398" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B398" s="8" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="399" spans="1:2">
       <c r="A399" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B399" s="8" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="400" spans="1:2">
       <c r="A400" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B400" s="8" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="401" spans="1:2">
       <c r="A401" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B401" s="9" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B402" s="9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="403" spans="1:2">
       <c r="A403" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B403" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="404" spans="1:2">
       <c r="A404" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B404" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="405" spans="1:2">
       <c r="A405" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B405" s="9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="406" spans="1:2">
       <c r="A406" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B406" s="9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="407" spans="1:2">
       <c r="A407" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B407" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="408" spans="1:2">
       <c r="A408" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B408" s="9" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="409" spans="1:2">
       <c r="A409" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B409" s="9" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="410" spans="1:2">
       <c r="A410" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B410" s="9" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="411" spans="1:2">
       <c r="A411" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B411" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="412" spans="1:2">
       <c r="A412" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B412" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="413" spans="1:2">
       <c r="A413" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B413" s="9" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="414" spans="1:2">
       <c r="A414" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B414" s="9" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B415" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="416" spans="1:2">
       <c r="A416" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B416" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="417" spans="1:2">
       <c r="A417" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B417" s="9" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="418" spans="1:2">
       <c r="A418" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B418" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="419" spans="1:2">
       <c r="A419" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B419" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="420" spans="1:2">
       <c r="A420" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B420" s="9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="421" spans="1:2">
       <c r="A421" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B421" s="9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="422" spans="1:2">
       <c r="A422" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B422" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="423" spans="1:2">
       <c r="A423" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B423" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="424" spans="1:2">
       <c r="A424" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B424" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="425" spans="1:2">
       <c r="A425" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B425" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="426" spans="1:2">
       <c r="A426" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B426" s="10" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="427" spans="1:2">
       <c r="A427" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B427" s="10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="428" spans="1:2">
       <c r="A428" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B428" s="10" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="429" spans="1:2">
       <c r="A429" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B429" s="10" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="430" spans="1:2">
       <c r="A430" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B430" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="431" spans="1:2">
       <c r="A431" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B431" s="10" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="432" spans="1:2">
       <c r="A432" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B432" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="433" spans="1:2">
       <c r="A433" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B433" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="434" spans="1:2">
       <c r="A434" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B434" s="10" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="A435" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B435" s="10" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B436" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B437" s="10" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B438" s="10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B439" s="10" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B440" s="10" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="441" spans="1:2">
       <c r="A441" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B441" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="442" spans="1:2">
       <c r="A442" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B442" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="443" spans="1:2">
       <c r="A443" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B443" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="444" spans="1:2">
       <c r="A444" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B444" s="9" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="445" spans="1:2">
       <c r="A445" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B445" s="9" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="446" spans="1:2">
       <c r="A446" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B446" s="9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="447" spans="1:2">
       <c r="A447" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B447" s="9" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="448" spans="1:2">
       <c r="A448" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B448" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="449" spans="1:2">
       <c r="A449" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B449" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="450" spans="1:2">
       <c r="A450" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B450" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="451" spans="1:2">
       <c r="A451" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B451" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="452" spans="1:2">
       <c r="A452" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B452" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="453" spans="1:2">
       <c r="A453" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B453" s="9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B454" s="9" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="455" spans="1:2">
       <c r="A455" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B455" s="9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="456" spans="1:2">
       <c r="A456" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B456" s="9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="457" spans="1:2">
       <c r="A457" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B457" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="458" spans="1:2">
       <c r="A458" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B458" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="459" spans="1:2">
       <c r="A459" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B459" s="9" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="460" spans="1:2">
       <c r="A460" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B460" s="9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="461" spans="1:2">
       <c r="A461" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B461" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="462" spans="1:2">
       <c r="A462" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B462" s="9" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="463" spans="1:2">
       <c r="A463" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B463" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="464" spans="1:2">
       <c r="A464" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B464" s="9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="465" spans="1:2">
       <c r="A465" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B465" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="466" spans="1:2">
       <c r="A466" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B466" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B467" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B468" s="9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B469" s="9" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B470" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B471" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B472" s="9" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="473" spans="1:2">
       <c r="A473" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B473" s="9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="474" spans="1:2">
       <c r="A474" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B474" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B475" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="476" spans="1:2">
       <c r="A476" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B476" s="9" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B477" s="9" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B478" s="9" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B479" s="9" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B480" s="9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="481" spans="1:2">
       <c r="A481" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B481" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B482" s="9" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="483" spans="1:2">
       <c r="A483" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B483" s="9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B484" s="9" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B485" s="9" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B486" s="9" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B487" s="9" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B488" s="9" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B489" s="9" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B490" s="9" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B491" s="9" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B492" s="9" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B493" s="9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="494" spans="1:2">
       <c r="A494" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B494" s="9" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="495" spans="1:2">
       <c r="A495" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B495" s="9" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="496" spans="1:2">
       <c r="A496" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B496" s="9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="497" spans="1:2">
       <c r="A497" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B497" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="498" spans="1:2">
       <c r="A498" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B498" s="9" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="499" spans="1:2">
       <c r="A499" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B499" s="9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="500" spans="1:2">
       <c r="A500" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B500" s="9" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="501" spans="1:2">
       <c r="A501" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B501" s="9" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="502" spans="1:2">
       <c r="A502" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B502" s="9" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="503" spans="1:2">
       <c r="A503" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B503" s="9" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="504" spans="1:2">
       <c r="A504" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B504" s="9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="505" spans="1:2">
       <c r="A505" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B505" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="506" spans="1:2">
       <c r="A506" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B506" s="9" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="507" spans="1:2">
       <c r="A507" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B507" s="9" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="508" spans="1:2">
       <c r="A508" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B508" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="509" spans="1:2">
       <c r="A509" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B509" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="510" spans="1:2">
       <c r="A510" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B510" s="9" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="511" spans="1:2">
       <c r="A511" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B511" s="9" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="512" spans="1:2">
       <c r="A512" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B512" s="9" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="A513" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B513" s="9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="514" spans="1:2">
       <c r="A514" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B514" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B515" s="9" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="A516" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B516" s="10" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="A517" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B517" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B518" s="10" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="519" spans="1:2">
       <c r="A519" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B519" s="10" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="520" spans="1:2">
       <c r="A520" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B520" s="10" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="521" spans="1:2">
       <c r="A521" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B521" s="10" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="522" spans="1:2">
       <c r="A522" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B522" s="10" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="A523" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B523" s="10" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="A524" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B524" s="10" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="A525" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B525" s="10" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="526" spans="1:2">
       <c r="A526" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B526" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="527" spans="1:2">
       <c r="A527" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B527" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="528" spans="1:2">
       <c r="A528" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B528" s="9" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="529" spans="1:2">
       <c r="A529" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B529" s="9" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="530" spans="1:2">
       <c r="A530" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B530" s="9" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="531" spans="1:2">
       <c r="A531" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B531" s="9" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="532" spans="1:2">
       <c r="A532" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B532" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="533" spans="1:2">
       <c r="A533" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B533" s="9" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="534" spans="1:2">
       <c r="A534" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B534" s="9" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B535" s="9" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B536" s="9" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B537" s="9" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="538" spans="1:2">
       <c r="A538" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B538" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B539" s="9" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B540" s="9" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B541" s="9" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B542" s="9" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B543" s="9" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B544" s="9" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B545" s="9" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="B546" s="13" t="s">
         <v>548</v>
-      </c>
-      <c r="B546" s="13" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="547" spans="1:2">
       <c r="A547" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B547" s="15" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="548" spans="1:2">
       <c r="A548" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B548" s="15" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B549" s="15" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B550" s="15" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B551" s="15" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B552" s="15" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B553" s="15" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B554" s="15" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B555" s="15" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B556" s="15" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B557" s="15" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B558" s="15" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B559" s="15" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B560" s="15" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="561" spans="1:2">
       <c r="A561" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B561" s="15" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="562" spans="1:2">
       <c r="A562" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B562" s="15" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="563" spans="1:2">
       <c r="A563" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B563" s="15" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="564" spans="1:2">
       <c r="A564" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B564" s="15" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="565" spans="1:2">
       <c r="A565" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B565" s="15" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="566" spans="1:2">
       <c r="A566" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B566" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B567" s="15" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B568" s="15" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="569" spans="1:2">
       <c r="A569" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B569" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B570" s="15" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B571" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="572" spans="1:2">
       <c r="A572" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B572" s="15" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="573" spans="1:2">
       <c r="A573" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B573" s="15" t="s">
         <v>4</v>
@@ -8400,2594 +8401,2594 @@
     </row>
     <row r="574" spans="1:2">
       <c r="A574" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B574" s="15" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B575" s="15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="576" spans="1:2">
       <c r="A576" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B576" s="15" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="577" spans="1:2">
       <c r="A577" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B577" s="15" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B578" s="15" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B579" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B580" s="15" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B581" s="15" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B582" s="15" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B583" s="15" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B584" s="15" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B585" s="15" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B586" s="15" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B587" s="15" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B588" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B589" s="15" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="590" spans="1:2">
       <c r="A590" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B590" s="15" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B591" s="15" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="592" spans="1:2">
       <c r="A592" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B592" s="15" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B593" s="15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B594" s="15" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B595" s="15" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B596" s="15" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B597" s="15" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B598" s="15" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="599" spans="1:2">
       <c r="A599" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B599" s="15" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B600" s="15" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B601" s="15" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B602" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B603" s="15" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B604" s="15" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B605" s="15" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" s="14" t="s">
+        <v>597</v>
+      </c>
+      <c r="B606" s="16" t="s">
         <v>598</v>
-      </c>
-      <c r="B606" s="16" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B607" s="16" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="608" spans="1:2">
       <c r="A608" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B608" s="16" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="609" spans="1:2">
       <c r="A609" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B609" s="16" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B610" s="16" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B611" s="16" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B612" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B613" s="16" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B614" s="16" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B615" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B616" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B617" s="16" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="618" spans="1:2">
       <c r="A618" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B618" s="16" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="619" spans="1:2">
       <c r="A619" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B619" s="16" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="620" spans="1:2">
       <c r="A620" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B620" s="16" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="621" spans="1:2">
       <c r="A621" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B621" s="16" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B622" s="16" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B623" s="16" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B624" s="16" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B625" s="16" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B626" s="16" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="627" spans="1:2">
       <c r="A627" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B627" s="16" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B628" s="16" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B629" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="630" spans="1:2">
       <c r="A630" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B630" s="16" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B631" s="16" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B632" s="16" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B633" s="16" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B634" s="16" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B635" s="16" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B636" s="16" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B637" s="16" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B638" s="16" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B639" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B640" s="16" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B641" s="16" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B642" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B643" s="16" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B644" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B645" s="16" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B646" s="16" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B647" s="16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B648" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="649" spans="1:2">
       <c r="A649" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B649" s="16" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B650" s="16" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B651" s="16" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B652" s="16" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B653" s="16" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B654" s="16" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="655" spans="1:2">
       <c r="A655" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B655" s="16" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="656" spans="1:2">
       <c r="A656" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B656" s="16" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B657" s="16" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B658" s="16" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B659" s="16" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B660" s="16" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B661" s="16" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="662" spans="1:2">
       <c r="A662" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B662" s="16" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="663" spans="1:2">
       <c r="A663" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B663" s="16" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="664" spans="1:2">
       <c r="A664" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B664" s="16" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="665" spans="1:2">
       <c r="A665" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B665" s="16" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="666" spans="1:2">
       <c r="A666" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="B666" s="16" t="s">
         <v>646</v>
-      </c>
-      <c r="B666" s="16" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="667" spans="1:2">
       <c r="A667" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B667" s="16" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B668" s="16" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="669" spans="1:2">
       <c r="A669" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B669" s="16" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="670" spans="1:2">
       <c r="A670" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B670" s="16" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="671" spans="1:2">
       <c r="A671" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B671" s="16" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="672" spans="1:2">
       <c r="A672" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B672" s="16" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="673" spans="1:2">
       <c r="A673" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B673" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B674" s="16" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B675" s="16" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B676" s="16" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B677" s="16" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="678" spans="1:2">
       <c r="A678" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B678" s="16" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B679" s="16" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="680" spans="1:2">
       <c r="A680" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B680" s="16" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="681" spans="1:2">
       <c r="A681" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B681" s="16" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B682" s="16" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B683" s="16" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B684" s="16" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B685" s="16" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B686" s="16" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B687" s="16" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="688" spans="1:2">
       <c r="A688" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B688" s="16" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="689" spans="1:2">
       <c r="A689" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B689" s="16" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B690" s="16" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B691" s="16" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B692" s="16" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="693" spans="1:2">
       <c r="A693" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B693" s="16" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="694" spans="1:2">
       <c r="A694" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B694" s="16" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="695" spans="1:2">
       <c r="A695" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B695" s="16" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="696" spans="1:2">
       <c r="A696" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B696" s="16" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="697" spans="1:2">
       <c r="A697" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B697" s="16" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="698" spans="1:2">
       <c r="A698" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B698" s="16" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="699" spans="1:2">
       <c r="A699" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B699" s="16" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="700" spans="1:2">
       <c r="A700" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B700" s="16" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B701" s="16" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="702" spans="1:2">
       <c r="A702" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B702" s="16" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="703" spans="1:2">
       <c r="A703" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B703" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B704" s="16" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="705" spans="1:2">
       <c r="A705" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B705" s="16" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="706" spans="1:2">
       <c r="A706" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B706" s="16" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B707" s="16" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B708" s="16" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B709" s="16" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B710" s="16" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B711" s="16" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B712" s="16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B713" s="16" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B714" s="16" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B715" s="16" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B716" s="16" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B717" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B718" s="16" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B719" s="16" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B720" s="16" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B721" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="722" spans="1:2">
       <c r="A722" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B722" s="16" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="723" spans="1:2">
       <c r="A723" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B723" s="16" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="724" spans="1:2">
       <c r="A724" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B724" s="16" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B725" s="16" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" s="14" t="s">
+        <v>696</v>
+      </c>
+      <c r="B726" s="15" t="s">
         <v>697</v>
-      </c>
-      <c r="B726" s="15" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="727" spans="1:2">
       <c r="A727" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B727" s="15" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="728" spans="1:2">
       <c r="A728" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B728" s="15" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B729" s="15" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="730" spans="1:2">
       <c r="A730" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B730" s="15" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B731" s="15" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B732" s="15" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B733" s="15" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B734" s="15" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B735" s="15" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B736" s="15" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="737" spans="1:2">
       <c r="A737" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B737" s="15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B738" s="15" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B739" s="15" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="740" spans="1:2">
       <c r="A740" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B740" s="15" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="741" spans="1:2">
       <c r="A741" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B741" s="15" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="742" spans="1:2">
       <c r="A742" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B742" s="15" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B743" s="15" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="744" spans="1:2">
       <c r="A744" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B744" s="15" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B745" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B746" s="15" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B747" s="15" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B748" s="15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B749" s="15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B750" s="15" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B751" s="15" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="752" spans="1:2">
       <c r="A752" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B752" s="15" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="753" spans="1:2">
       <c r="A753" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B753" s="15" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B754" s="15" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B755" s="15" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B756" s="15" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B757" s="15" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="758" spans="1:2">
       <c r="A758" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B758" s="15" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="759" spans="1:2">
       <c r="A759" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B759" s="15" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="760" spans="1:2">
       <c r="A760" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B760" s="15" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="761" spans="1:2">
       <c r="A761" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B761" s="15" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="762" spans="1:2">
       <c r="A762" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B762" s="15" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="763" spans="1:2">
       <c r="A763" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B763" s="15" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B764" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B765" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="766" spans="1:2">
       <c r="A766" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B766" s="15" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="767" spans="1:2">
       <c r="A767" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B767" s="15" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="768" spans="1:2">
       <c r="A768" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B768" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="769" spans="1:2">
       <c r="A769" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B769" s="15" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B770" s="15" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B771" s="15" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B772" s="15" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="773" spans="1:2">
       <c r="A773" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B773" s="15" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="774" spans="1:2">
       <c r="A774" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B774" s="15" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="775" spans="1:2">
       <c r="A775" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B775" s="15" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="776" spans="1:2">
       <c r="A776" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B776" s="15" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="777" spans="1:2">
       <c r="A777" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B777" s="15" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="778" spans="1:2">
       <c r="A778" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B778" s="15" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="779" spans="1:2">
       <c r="A779" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B779" s="15" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="780" spans="1:2">
       <c r="A780" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B780" s="15" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="781" spans="1:2">
       <c r="A781" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B781" s="15" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="782" spans="1:2">
       <c r="A782" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B782" s="15" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B783" s="15" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B784" s="15" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B785" s="15" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" s="11" t="s">
+        <v>740</v>
+      </c>
+      <c r="B786" s="7" t="s">
         <v>741</v>
-      </c>
-      <c r="B786" s="7" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="787" spans="1:2">
       <c r="A787" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B787" s="7" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="788" spans="1:2">
       <c r="A788" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B788" s="7" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="789" spans="1:2">
       <c r="A789" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B789" s="7" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="790" spans="1:2">
       <c r="A790" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B790" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B791" s="7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B792" s="7" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B793" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B794" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B795" s="7" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B796" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B797" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B798" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B799" s="7" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B800" s="7" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B801" s="7" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B802" s="7" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B803" s="7" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B804" s="7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B805" s="7" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B806" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B807" s="7" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B808" s="7" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B809" s="7" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B810" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B811" s="7" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B812" s="7" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="813" spans="1:2">
       <c r="A813" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B813" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="814" spans="1:2">
       <c r="A814" s="11" t="s">
+        <v>762</v>
+      </c>
+      <c r="B814" s="9" t="s">
         <v>763</v>
-      </c>
-      <c r="B814" s="9" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B815" s="9" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B816" s="9" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B817" s="9" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B818" s="9" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B819" s="9" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="820" spans="1:2">
       <c r="A820" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B820" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B821" s="9" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B822" s="9" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B823" s="9" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B824" s="9" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B825" s="9" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B826" s="9" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B827" s="9" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B828" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B829" s="9" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B830" s="9" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B831" s="9" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B832" s="9" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B833" s="9" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B834" s="9" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B835" s="9" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B836" s="9" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B837" s="9" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B838" s="9" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B839" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B840" s="9" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B841" s="9" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" s="11" t="s">
+        <v>787</v>
+      </c>
+      <c r="B842" s="8" t="s">
         <v>788</v>
-      </c>
-      <c r="B842" s="8" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B843" s="8" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B844" s="8" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B845" s="8" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B846" s="8" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B847" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B848" s="8" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B849" s="8" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B850" s="8" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B851" s="8" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B852" s="8" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B853" s="8" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B854" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B855" s="8" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B856" s="8" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B857" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B858" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B859" s="8" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B860" s="8" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B861" s="8" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B862" s="8" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B863" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B864" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B865" s="8" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="866" spans="1:2">
       <c r="A866" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B866" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B867" s="8" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B868" s="8" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" s="11" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B869" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" s="11" t="s">
+        <v>805</v>
+      </c>
+      <c r="B870" s="7" t="s">
         <v>806</v>
-      </c>
-      <c r="B870" s="7" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B871" s="7" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B872" s="7" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B873" s="7" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B874" s="7" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B875" s="7" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B876" s="7" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B877" s="7" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B878" s="7" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B879" s="7" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B880" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B881" s="7" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B882" s="7" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B883" s="7" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B884" s="7" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B885" s="7" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B886" s="7" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B887" s="7" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B888" s="7" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B889" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B890" s="9" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B891" s="7" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B892" s="7" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B893" s="7" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B894" s="7" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B895" s="7" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B896" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B897" s="7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m2610025/Desktop/チェックイン/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F97AB49E-17F9-4945-AB22-B4EDA734B9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13B77492-1FDA-E74F-A916-F81ADF8EF9D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{348E8972-E72E-5A4B-9183-B2C2B4112549}"/>
   </bookViews>
@@ -2727,10 +2727,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="@&quot;(1)&quot;"/>
     <numFmt numFmtId="177" formatCode="@&quot;(2)&quot;"/>
     <numFmt numFmtId="178" formatCode="@&quot;(3)&quot;"/>
+    <numFmt numFmtId="182" formatCode="@&quot;1&quot;"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -3025,7 +3026,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3078,9 +3079,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3152,7 +3150,16 @@
     <xf numFmtId="178" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3786,7 +3793,7 @@
       <c r="A2" t="s">
         <v>826</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>834</v>
       </c>
       <c r="C2" s="1"/>
@@ -3795,7 +3802,7 @@
       <c r="A3" t="s">
         <v>826</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="42" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="1"/>
@@ -3804,7 +3811,7 @@
       <c r="A4" t="s">
         <v>826</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="42" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="1"/>
@@ -3813,7 +3820,7 @@
       <c r="A5" t="s">
         <v>826</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="42" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="1"/>
@@ -3822,7 +3829,7 @@
       <c r="A6" t="s">
         <v>826</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="42" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="1"/>
@@ -3831,7 +3838,7 @@
       <c r="A7" t="s">
         <v>826</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="42" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="1"/>
@@ -3840,7 +3847,7 @@
       <c r="A8" t="s">
         <v>826</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="42" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="1"/>
@@ -3849,7 +3856,7 @@
       <c r="A9" t="s">
         <v>826</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="42" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="1"/>
@@ -3858,7 +3865,7 @@
       <c r="A10" t="s">
         <v>826</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="42" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="1"/>
@@ -3867,7 +3874,7 @@
       <c r="A11" t="s">
         <v>826</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="42" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="1"/>
@@ -3876,7 +3883,7 @@
       <c r="A12" t="s">
         <v>826</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="42" t="s">
         <v>0</v>
       </c>
       <c r="C12" s="1"/>
@@ -3885,7 +3892,7 @@
       <c r="A13" t="s">
         <v>826</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="42" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="1"/>
@@ -3894,7 +3901,7 @@
       <c r="A14" t="s">
         <v>826</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="42" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="1"/>
@@ -3903,7 +3910,7 @@
       <c r="A15" t="s">
         <v>826</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="42" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="1"/>
@@ -3912,7 +3919,7 @@
       <c r="A16" t="s">
         <v>826</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="42" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="1"/>
@@ -3921,7 +3928,7 @@
       <c r="A17" t="s">
         <v>826</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="42" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="1"/>
@@ -3930,7 +3937,7 @@
       <c r="A18" t="s">
         <v>826</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="42" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="2"/>
@@ -3939,7 +3946,7 @@
       <c r="A19" t="s">
         <v>826</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="42" t="s">
         <v>22</v>
       </c>
       <c r="C19" s="2"/>
@@ -3948,7 +3955,7 @@
       <c r="A20" t="s">
         <v>826</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="43" t="s">
         <v>23</v>
       </c>
       <c r="C20" s="2"/>
@@ -3957,7 +3964,7 @@
       <c r="A21" t="s">
         <v>826</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="42" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3"/>
@@ -3966,7 +3973,7 @@
       <c r="A22" t="s">
         <v>826</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="42" t="s">
         <v>25</v>
       </c>
     </row>
@@ -3974,7 +3981,7 @@
       <c r="A23" t="s">
         <v>826</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="42" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3982,7 +3989,7 @@
       <c r="A24" t="s">
         <v>826</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="42" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3990,7 +3997,7 @@
       <c r="A25" t="s">
         <v>826</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="42" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3998,7 +4005,7 @@
       <c r="A26" t="s">
         <v>826</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="42" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4006,7 +4013,7 @@
       <c r="A27" t="s">
         <v>826</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="42" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4014,7 +4021,7 @@
       <c r="A28" t="s">
         <v>826</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="42" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4022,7 +4029,7 @@
       <c r="A29" t="s">
         <v>826</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="42" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4030,7 +4037,7 @@
       <c r="A30" t="s">
         <v>826</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="42" t="s">
         <v>33</v>
       </c>
     </row>
@@ -4038,7 +4045,7 @@
       <c r="A31" t="s">
         <v>826</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="42" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4046,7 +4053,7 @@
       <c r="A32" t="s">
         <v>826</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="42" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4054,7 +4061,7 @@
       <c r="A33" t="s">
         <v>826</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="42" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4062,7 +4069,7 @@
       <c r="A34" t="s">
         <v>826</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="42" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4070,7 +4077,7 @@
       <c r="A35" t="s">
         <v>826</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="42" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4078,7 +4085,7 @@
       <c r="A36" t="s">
         <v>826</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="44" t="s">
         <v>39</v>
       </c>
     </row>
@@ -4086,7 +4093,7 @@
       <c r="A37" t="s">
         <v>827</v>
       </c>
-      <c r="B37" s="20" t="s">
+      <c r="B37" s="19" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4094,7 +4101,7 @@
       <c r="A38" t="s">
         <v>827</v>
       </c>
-      <c r="B38" s="20" t="s">
+      <c r="B38" s="19" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4102,7 +4109,7 @@
       <c r="A39" t="s">
         <v>827</v>
       </c>
-      <c r="B39" s="20" t="s">
+      <c r="B39" s="19" t="s">
         <v>42</v>
       </c>
     </row>
@@ -4110,7 +4117,7 @@
       <c r="A40" t="s">
         <v>827</v>
       </c>
-      <c r="B40" s="20" t="s">
+      <c r="B40" s="19" t="s">
         <v>43</v>
       </c>
     </row>
@@ -4118,7 +4125,7 @@
       <c r="A41" t="s">
         <v>827</v>
       </c>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="19" t="s">
         <v>44</v>
       </c>
     </row>
@@ -4126,7 +4133,7 @@
       <c r="A42" t="s">
         <v>827</v>
       </c>
-      <c r="B42" s="20" t="s">
+      <c r="B42" s="19" t="s">
         <v>45</v>
       </c>
     </row>
@@ -4134,7 +4141,7 @@
       <c r="A43" t="s">
         <v>827</v>
       </c>
-      <c r="B43" s="20" t="s">
+      <c r="B43" s="19" t="s">
         <v>4</v>
       </c>
       <c r="C43" s="5"/>
@@ -4143,7 +4150,7 @@
       <c r="A44" t="s">
         <v>827</v>
       </c>
-      <c r="B44" s="20" t="s">
+      <c r="B44" s="19" t="s">
         <v>46</v>
       </c>
       <c r="C44" s="5"/>
@@ -4152,7 +4159,7 @@
       <c r="A45" t="s">
         <v>827</v>
       </c>
-      <c r="B45" s="20" t="s">
+      <c r="B45" s="19" t="s">
         <v>47</v>
       </c>
       <c r="C45" s="5"/>
@@ -4161,7 +4168,7 @@
       <c r="A46" t="s">
         <v>827</v>
       </c>
-      <c r="B46" s="20" t="s">
+      <c r="B46" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C46" s="5"/>
@@ -4170,7 +4177,7 @@
       <c r="A47" t="s">
         <v>827</v>
       </c>
-      <c r="B47" s="20" t="s">
+      <c r="B47" s="19" t="s">
         <v>49</v>
       </c>
       <c r="C47" s="5"/>
@@ -4179,7 +4186,7 @@
       <c r="A48" t="s">
         <v>827</v>
       </c>
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="19" t="s">
         <v>50</v>
       </c>
       <c r="C48" s="5"/>
@@ -4188,7 +4195,7 @@
       <c r="A49" t="s">
         <v>827</v>
       </c>
-      <c r="B49" s="20" t="s">
+      <c r="B49" s="19" t="s">
         <v>51</v>
       </c>
       <c r="C49" s="5"/>
@@ -4197,7 +4204,7 @@
       <c r="A50" t="s">
         <v>827</v>
       </c>
-      <c r="B50" s="20" t="s">
+      <c r="B50" s="19" t="s">
         <v>52</v>
       </c>
       <c r="C50" s="5"/>
@@ -4206,7 +4213,7 @@
       <c r="A51" t="s">
         <v>827</v>
       </c>
-      <c r="B51" s="20" t="s">
+      <c r="B51" s="19" t="s">
         <v>53</v>
       </c>
       <c r="C51" s="5"/>
@@ -4215,7 +4222,7 @@
       <c r="A52" t="s">
         <v>827</v>
       </c>
-      <c r="B52" s="20" t="s">
+      <c r="B52" s="19" t="s">
         <v>54</v>
       </c>
       <c r="C52" s="5"/>
@@ -4224,7 +4231,7 @@
       <c r="A53" t="s">
         <v>827</v>
       </c>
-      <c r="B53" s="20" t="s">
+      <c r="B53" s="19" t="s">
         <v>55</v>
       </c>
       <c r="C53" s="5"/>
@@ -4233,7 +4240,7 @@
       <c r="A54" t="s">
         <v>827</v>
       </c>
-      <c r="B54" s="20" t="s">
+      <c r="B54" s="19" t="s">
         <v>56</v>
       </c>
       <c r="C54" s="5"/>
@@ -4242,7 +4249,7 @@
       <c r="A55" t="s">
         <v>827</v>
       </c>
-      <c r="B55" s="20" t="s">
+      <c r="B55" s="19" t="s">
         <v>57</v>
       </c>
       <c r="C55" s="5"/>
@@ -4251,7 +4258,7 @@
       <c r="A56" t="s">
         <v>827</v>
       </c>
-      <c r="B56" s="20" t="s">
+      <c r="B56" s="19" t="s">
         <v>58</v>
       </c>
       <c r="C56" s="5"/>
@@ -4260,7 +4267,7 @@
       <c r="A57" t="s">
         <v>827</v>
       </c>
-      <c r="B57" s="20" t="s">
+      <c r="B57" s="19" t="s">
         <v>59</v>
       </c>
       <c r="C57" s="5"/>
@@ -4269,7 +4276,7 @@
       <c r="A58" t="s">
         <v>827</v>
       </c>
-      <c r="B58" s="20" t="s">
+      <c r="B58" s="19" t="s">
         <v>1</v>
       </c>
       <c r="C58" s="5"/>
@@ -4278,7 +4285,7 @@
       <c r="A59" t="s">
         <v>827</v>
       </c>
-      <c r="B59" s="20" t="s">
+      <c r="B59" s="19" t="s">
         <v>60</v>
       </c>
       <c r="C59" s="5"/>
@@ -4287,7 +4294,7 @@
       <c r="A60" t="s">
         <v>827</v>
       </c>
-      <c r="B60" s="20" t="s">
+      <c r="B60" s="19" t="s">
         <v>61</v>
       </c>
       <c r="C60" s="5"/>
@@ -4296,7 +4303,7 @@
       <c r="A61" t="s">
         <v>827</v>
       </c>
-      <c r="B61" s="20" t="s">
+      <c r="B61" s="19" t="s">
         <v>62</v>
       </c>
       <c r="C61" s="5"/>
@@ -4305,7 +4312,7 @@
       <c r="A62" t="s">
         <v>827</v>
       </c>
-      <c r="B62" s="20" t="s">
+      <c r="B62" s="19" t="s">
         <v>63</v>
       </c>
       <c r="C62" s="5"/>
@@ -4314,7 +4321,7 @@
       <c r="A63" t="s">
         <v>827</v>
       </c>
-      <c r="B63" s="20" t="s">
+      <c r="B63" s="19" t="s">
         <v>64</v>
       </c>
       <c r="C63" s="6"/>
@@ -4323,7 +4330,7 @@
       <c r="A64" t="s">
         <v>827</v>
       </c>
-      <c r="B64" s="20" t="s">
+      <c r="B64" s="19" t="s">
         <v>65</v>
       </c>
     </row>
@@ -4331,7 +4338,7 @@
       <c r="A65" t="s">
         <v>827</v>
       </c>
-      <c r="B65" s="20" t="s">
+      <c r="B65" s="19" t="s">
         <v>66</v>
       </c>
     </row>
@@ -4339,7 +4346,7 @@
       <c r="A66" t="s">
         <v>827</v>
       </c>
-      <c r="B66" s="20" t="s">
+      <c r="B66" s="19" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4347,7 +4354,7 @@
       <c r="A67" t="s">
         <v>827</v>
       </c>
-      <c r="B67" s="20" t="s">
+      <c r="B67" s="19" t="s">
         <v>68</v>
       </c>
     </row>
@@ -4355,7 +4362,7 @@
       <c r="A68" t="s">
         <v>827</v>
       </c>
-      <c r="B68" s="20" t="s">
+      <c r="B68" s="19" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4363,7 +4370,7 @@
       <c r="A69" t="s">
         <v>827</v>
       </c>
-      <c r="B69" s="20" t="s">
+      <c r="B69" s="19" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4371,7 +4378,7 @@
       <c r="A70" t="s">
         <v>827</v>
       </c>
-      <c r="B70" s="20" t="s">
+      <c r="B70" s="19" t="s">
         <v>71</v>
       </c>
     </row>
@@ -4379,7 +4386,7 @@
       <c r="A71" t="s">
         <v>827</v>
       </c>
-      <c r="B71" s="21" t="s">
+      <c r="B71" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -4387,7 +4394,7 @@
       <c r="A72" t="s">
         <v>828</v>
       </c>
-      <c r="B72" s="22" t="s">
+      <c r="B72" s="21" t="s">
         <v>73</v>
       </c>
     </row>
@@ -4395,7 +4402,7 @@
       <c r="A73" t="s">
         <v>828</v>
       </c>
-      <c r="B73" s="22" t="s">
+      <c r="B73" s="21" t="s">
         <v>74</v>
       </c>
     </row>
@@ -4403,7 +4410,7 @@
       <c r="A74" t="s">
         <v>828</v>
       </c>
-      <c r="B74" s="22" t="s">
+      <c r="B74" s="21" t="s">
         <v>75</v>
       </c>
     </row>
@@ -4411,7 +4418,7 @@
       <c r="A75" t="s">
         <v>828</v>
       </c>
-      <c r="B75" s="22" t="s">
+      <c r="B75" s="21" t="s">
         <v>76</v>
       </c>
     </row>
@@ -4419,7 +4426,7 @@
       <c r="A76" t="s">
         <v>828</v>
       </c>
-      <c r="B76" s="22" t="s">
+      <c r="B76" s="21" t="s">
         <v>77</v>
       </c>
     </row>
@@ -4427,7 +4434,7 @@
       <c r="A77" t="s">
         <v>828</v>
       </c>
-      <c r="B77" s="22" t="s">
+      <c r="B77" s="21" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4435,7 +4442,7 @@
       <c r="A78" t="s">
         <v>828</v>
       </c>
-      <c r="B78" s="22" t="s">
+      <c r="B78" s="21" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4443,7 +4450,7 @@
       <c r="A79" t="s">
         <v>828</v>
       </c>
-      <c r="B79" s="22" t="s">
+      <c r="B79" s="21" t="s">
         <v>80</v>
       </c>
     </row>
@@ -4451,7 +4458,7 @@
       <c r="A80" t="s">
         <v>828</v>
       </c>
-      <c r="B80" s="22" t="s">
+      <c r="B80" s="21" t="s">
         <v>81</v>
       </c>
     </row>
@@ -4459,7 +4466,7 @@
       <c r="A81" t="s">
         <v>828</v>
       </c>
-      <c r="B81" s="22" t="s">
+      <c r="B81" s="21" t="s">
         <v>82</v>
       </c>
     </row>
@@ -4467,7 +4474,7 @@
       <c r="A82" t="s">
         <v>828</v>
       </c>
-      <c r="B82" s="22" t="s">
+      <c r="B82" s="21" t="s">
         <v>83</v>
       </c>
     </row>
@@ -4475,7 +4482,7 @@
       <c r="A83" t="s">
         <v>828</v>
       </c>
-      <c r="B83" s="22" t="s">
+      <c r="B83" s="21" t="s">
         <v>84</v>
       </c>
     </row>
@@ -4483,7 +4490,7 @@
       <c r="A84" t="s">
         <v>828</v>
       </c>
-      <c r="B84" s="22" t="s">
+      <c r="B84" s="21" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4491,7 +4498,7 @@
       <c r="A85" t="s">
         <v>828</v>
       </c>
-      <c r="B85" s="22" t="s">
+      <c r="B85" s="21" t="s">
         <v>86</v>
       </c>
     </row>
@@ -4499,7 +4506,7 @@
       <c r="A86" t="s">
         <v>828</v>
       </c>
-      <c r="B86" s="22" t="s">
+      <c r="B86" s="21" t="s">
         <v>87</v>
       </c>
     </row>
@@ -4507,7 +4514,7 @@
       <c r="A87" t="s">
         <v>828</v>
       </c>
-      <c r="B87" s="22" t="s">
+      <c r="B87" s="21" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4515,7 +4522,7 @@
       <c r="A88" t="s">
         <v>828</v>
       </c>
-      <c r="B88" s="22" t="s">
+      <c r="B88" s="21" t="s">
         <v>89</v>
       </c>
     </row>
@@ -4523,7 +4530,7 @@
       <c r="A89" t="s">
         <v>828</v>
       </c>
-      <c r="B89" s="22" t="s">
+      <c r="B89" s="21" t="s">
         <v>90</v>
       </c>
     </row>
@@ -4531,7 +4538,7 @@
       <c r="A90" t="s">
         <v>828</v>
       </c>
-      <c r="B90" s="22" t="s">
+      <c r="B90" s="21" t="s">
         <v>91</v>
       </c>
     </row>
@@ -4539,7 +4546,7 @@
       <c r="A91" t="s">
         <v>828</v>
       </c>
-      <c r="B91" s="22" t="s">
+      <c r="B91" s="21" t="s">
         <v>92</v>
       </c>
     </row>
@@ -4547,7 +4554,7 @@
       <c r="A92" t="s">
         <v>828</v>
       </c>
-      <c r="B92" s="22" t="s">
+      <c r="B92" s="21" t="s">
         <v>93</v>
       </c>
     </row>
@@ -4555,7 +4562,7 @@
       <c r="A93" t="s">
         <v>828</v>
       </c>
-      <c r="B93" s="22" t="s">
+      <c r="B93" s="21" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4563,7 +4570,7 @@
       <c r="A94" t="s">
         <v>828</v>
       </c>
-      <c r="B94" s="22" t="s">
+      <c r="B94" s="21" t="s">
         <v>95</v>
       </c>
     </row>
@@ -4571,7 +4578,7 @@
       <c r="A95" t="s">
         <v>828</v>
       </c>
-      <c r="B95" s="22" t="s">
+      <c r="B95" s="21" t="s">
         <v>96</v>
       </c>
     </row>
@@ -4579,7 +4586,7 @@
       <c r="A96" t="s">
         <v>828</v>
       </c>
-      <c r="B96" s="22" t="s">
+      <c r="B96" s="21" t="s">
         <v>97</v>
       </c>
     </row>
@@ -4587,7 +4594,7 @@
       <c r="A97" t="s">
         <v>828</v>
       </c>
-      <c r="B97" s="22" t="s">
+      <c r="B97" s="21" t="s">
         <v>98</v>
       </c>
     </row>
@@ -4595,7 +4602,7 @@
       <c r="A98" t="s">
         <v>828</v>
       </c>
-      <c r="B98" s="22" t="s">
+      <c r="B98" s="21" t="s">
         <v>99</v>
       </c>
     </row>
@@ -4603,7 +4610,7 @@
       <c r="A99" t="s">
         <v>828</v>
       </c>
-      <c r="B99" s="22" t="s">
+      <c r="B99" s="21" t="s">
         <v>100</v>
       </c>
     </row>
@@ -4611,7 +4618,7 @@
       <c r="A100" t="s">
         <v>828</v>
       </c>
-      <c r="B100" s="22" t="s">
+      <c r="B100" s="21" t="s">
         <v>101</v>
       </c>
     </row>
@@ -4619,7 +4626,7 @@
       <c r="A101" t="s">
         <v>828</v>
       </c>
-      <c r="B101" s="22" t="s">
+      <c r="B101" s="21" t="s">
         <v>102</v>
       </c>
     </row>
@@ -4627,7 +4634,7 @@
       <c r="A102" t="s">
         <v>828</v>
       </c>
-      <c r="B102" s="22" t="s">
+      <c r="B102" s="21" t="s">
         <v>103</v>
       </c>
     </row>
@@ -4635,7 +4642,7 @@
       <c r="A103" t="s">
         <v>828</v>
       </c>
-      <c r="B103" s="22" t="s">
+      <c r="B103" s="21" t="s">
         <v>104</v>
       </c>
     </row>
@@ -4643,7 +4650,7 @@
       <c r="A104" t="s">
         <v>828</v>
       </c>
-      <c r="B104" s="22" t="s">
+      <c r="B104" s="21" t="s">
         <v>105</v>
       </c>
     </row>
@@ -4651,7 +4658,7 @@
       <c r="A105" t="s">
         <v>828</v>
       </c>
-      <c r="B105" s="22" t="s">
+      <c r="B105" s="21" t="s">
         <v>106</v>
       </c>
     </row>
@@ -4659,7 +4666,7 @@
       <c r="A106" t="s">
         <v>828</v>
       </c>
-      <c r="B106" s="23" t="s">
+      <c r="B106" s="22" t="s">
         <v>107</v>
       </c>
     </row>
@@ -4939,7 +4946,7 @@
       <c r="A141" t="s">
         <v>829</v>
       </c>
-      <c r="B141" s="19" t="s">
+      <c r="B141" s="18" t="s">
         <v>142</v>
       </c>
     </row>
@@ -4947,7 +4954,7 @@
       <c r="A142" t="s">
         <v>826</v>
       </c>
-      <c r="B142" s="24" t="s">
+      <c r="B142" s="23" t="s">
         <v>143</v>
       </c>
     </row>
@@ -4955,7 +4962,7 @@
       <c r="A143" t="s">
         <v>826</v>
       </c>
-      <c r="B143" s="25" t="s">
+      <c r="B143" s="24" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4963,7 +4970,7 @@
       <c r="A144" t="s">
         <v>826</v>
       </c>
-      <c r="B144" s="25" t="s">
+      <c r="B144" s="24" t="s">
         <v>145</v>
       </c>
     </row>
@@ -4971,7 +4978,7 @@
       <c r="A145" t="s">
         <v>826</v>
       </c>
-      <c r="B145" s="25" t="s">
+      <c r="B145" s="24" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4979,7 +4986,7 @@
       <c r="A146" t="s">
         <v>826</v>
       </c>
-      <c r="B146" s="25" t="s">
+      <c r="B146" s="24" t="s">
         <v>147</v>
       </c>
     </row>
@@ -4987,7 +4994,7 @@
       <c r="A147" t="s">
         <v>826</v>
       </c>
-      <c r="B147" s="25" t="s">
+      <c r="B147" s="24" t="s">
         <v>148</v>
       </c>
     </row>
@@ -4995,7 +5002,7 @@
       <c r="A148" t="s">
         <v>826</v>
       </c>
-      <c r="B148" s="25" t="s">
+      <c r="B148" s="24" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5003,7 +5010,7 @@
       <c r="A149" t="s">
         <v>826</v>
       </c>
-      <c r="B149" s="25" t="s">
+      <c r="B149" s="24" t="s">
         <v>150</v>
       </c>
     </row>
@@ -5011,7 +5018,7 @@
       <c r="A150" t="s">
         <v>826</v>
       </c>
-      <c r="B150" s="25" t="s">
+      <c r="B150" s="24" t="s">
         <v>151</v>
       </c>
     </row>
@@ -5019,7 +5026,7 @@
       <c r="A151" t="s">
         <v>826</v>
       </c>
-      <c r="B151" s="25" t="s">
+      <c r="B151" s="24" t="s">
         <v>152</v>
       </c>
     </row>
@@ -5027,7 +5034,7 @@
       <c r="A152" t="s">
         <v>826</v>
       </c>
-      <c r="B152" s="25" t="s">
+      <c r="B152" s="24" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5035,7 +5042,7 @@
       <c r="A153" t="s">
         <v>826</v>
       </c>
-      <c r="B153" s="25" t="s">
+      <c r="B153" s="24" t="s">
         <v>154</v>
       </c>
     </row>
@@ -5043,7 +5050,7 @@
       <c r="A154" t="s">
         <v>826</v>
       </c>
-      <c r="B154" s="25" t="s">
+      <c r="B154" s="24" t="s">
         <v>155</v>
       </c>
     </row>
@@ -5051,7 +5058,7 @@
       <c r="A155" t="s">
         <v>826</v>
       </c>
-      <c r="B155" s="25" t="s">
+      <c r="B155" s="24" t="s">
         <v>156</v>
       </c>
     </row>
@@ -5059,7 +5066,7 @@
       <c r="A156" t="s">
         <v>826</v>
       </c>
-      <c r="B156" s="25" t="s">
+      <c r="B156" s="24" t="s">
         <v>157</v>
       </c>
     </row>
@@ -5067,7 +5074,7 @@
       <c r="A157" t="s">
         <v>826</v>
       </c>
-      <c r="B157" s="25" t="s">
+      <c r="B157" s="24" t="s">
         <v>158</v>
       </c>
     </row>
@@ -5075,7 +5082,7 @@
       <c r="A158" t="s">
         <v>826</v>
       </c>
-      <c r="B158" s="25" t="s">
+      <c r="B158" s="24" t="s">
         <v>159</v>
       </c>
     </row>
@@ -5083,7 +5090,7 @@
       <c r="A159" t="s">
         <v>826</v>
       </c>
-      <c r="B159" s="25" t="s">
+      <c r="B159" s="24" t="s">
         <v>160</v>
       </c>
     </row>
@@ -5091,7 +5098,7 @@
       <c r="A160" t="s">
         <v>826</v>
       </c>
-      <c r="B160" s="25" t="s">
+      <c r="B160" s="24" t="s">
         <v>161</v>
       </c>
     </row>
@@ -5099,7 +5106,7 @@
       <c r="A161" t="s">
         <v>826</v>
       </c>
-      <c r="B161" s="25" t="s">
+      <c r="B161" s="24" t="s">
         <v>162</v>
       </c>
     </row>
@@ -5107,7 +5114,7 @@
       <c r="A162" t="s">
         <v>826</v>
       </c>
-      <c r="B162" s="25" t="s">
+      <c r="B162" s="24" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5115,7 +5122,7 @@
       <c r="A163" t="s">
         <v>826</v>
       </c>
-      <c r="B163" s="25" t="s">
+      <c r="B163" s="24" t="s">
         <v>164</v>
       </c>
     </row>
@@ -5123,7 +5130,7 @@
       <c r="A164" t="s">
         <v>826</v>
       </c>
-      <c r="B164" s="25" t="s">
+      <c r="B164" s="24" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5131,7 +5138,7 @@
       <c r="A165" t="s">
         <v>826</v>
       </c>
-      <c r="B165" s="25" t="s">
+      <c r="B165" s="24" t="s">
         <v>166</v>
       </c>
     </row>
@@ -5139,7 +5146,7 @@
       <c r="A166" t="s">
         <v>826</v>
       </c>
-      <c r="B166" s="25" t="s">
+      <c r="B166" s="24" t="s">
         <v>167</v>
       </c>
     </row>
@@ -5147,7 +5154,7 @@
       <c r="A167" t="s">
         <v>826</v>
       </c>
-      <c r="B167" s="25" t="s">
+      <c r="B167" s="24" t="s">
         <v>168</v>
       </c>
     </row>
@@ -5155,7 +5162,7 @@
       <c r="A168" t="s">
         <v>826</v>
       </c>
-      <c r="B168" s="25" t="s">
+      <c r="B168" s="24" t="s">
         <v>169</v>
       </c>
     </row>
@@ -5163,7 +5170,7 @@
       <c r="A169" t="s">
         <v>826</v>
       </c>
-      <c r="B169" s="25" t="s">
+      <c r="B169" s="24" t="s">
         <v>170</v>
       </c>
     </row>
@@ -5171,7 +5178,7 @@
       <c r="A170" t="s">
         <v>826</v>
       </c>
-      <c r="B170" s="25" t="s">
+      <c r="B170" s="24" t="s">
         <v>171</v>
       </c>
     </row>
@@ -5179,7 +5186,7 @@
       <c r="A171" t="s">
         <v>826</v>
       </c>
-      <c r="B171" s="25" t="s">
+      <c r="B171" s="24" t="s">
         <v>172</v>
       </c>
     </row>
@@ -5187,7 +5194,7 @@
       <c r="A172" t="s">
         <v>826</v>
       </c>
-      <c r="B172" s="25" t="s">
+      <c r="B172" s="24" t="s">
         <v>173</v>
       </c>
     </row>
@@ -5195,7 +5202,7 @@
       <c r="A173" t="s">
         <v>826</v>
       </c>
-      <c r="B173" s="25" t="s">
+      <c r="B173" s="24" t="s">
         <v>174</v>
       </c>
     </row>
@@ -5203,7 +5210,7 @@
       <c r="A174" t="s">
         <v>826</v>
       </c>
-      <c r="B174" s="25" t="s">
+      <c r="B174" s="24" t="s">
         <v>175</v>
       </c>
     </row>
@@ -5211,7 +5218,7 @@
       <c r="A175" t="s">
         <v>826</v>
       </c>
-      <c r="B175" s="25" t="s">
+      <c r="B175" s="24" t="s">
         <v>176</v>
       </c>
     </row>
@@ -5219,7 +5226,7 @@
       <c r="A176" t="s">
         <v>826</v>
       </c>
-      <c r="B176" s="26" t="s">
+      <c r="B176" s="25" t="s">
         <v>177</v>
       </c>
     </row>
@@ -5227,7 +5234,7 @@
       <c r="A177" t="s">
         <v>830</v>
       </c>
-      <c r="B177" s="27" t="s">
+      <c r="B177" s="26" t="s">
         <v>178</v>
       </c>
     </row>
@@ -5235,7 +5242,7 @@
       <c r="A178" t="s">
         <v>830</v>
       </c>
-      <c r="B178" s="27" t="s">
+      <c r="B178" s="26" t="s">
         <v>179</v>
       </c>
     </row>
@@ -5243,7 +5250,7 @@
       <c r="A179" t="s">
         <v>830</v>
       </c>
-      <c r="B179" s="27" t="s">
+      <c r="B179" s="26" t="s">
         <v>180</v>
       </c>
     </row>
@@ -5251,7 +5258,7 @@
       <c r="A180" t="s">
         <v>830</v>
       </c>
-      <c r="B180" s="27" t="s">
+      <c r="B180" s="26" t="s">
         <v>181</v>
       </c>
     </row>
@@ -5259,7 +5266,7 @@
       <c r="A181" t="s">
         <v>830</v>
       </c>
-      <c r="B181" s="27" t="s">
+      <c r="B181" s="26" t="s">
         <v>182</v>
       </c>
     </row>
@@ -5267,7 +5274,7 @@
       <c r="A182" t="s">
         <v>830</v>
       </c>
-      <c r="B182" s="27" t="s">
+      <c r="B182" s="26" t="s">
         <v>183</v>
       </c>
     </row>
@@ -5275,7 +5282,7 @@
       <c r="A183" t="s">
         <v>830</v>
       </c>
-      <c r="B183" s="27" t="s">
+      <c r="B183" s="26" t="s">
         <v>184</v>
       </c>
     </row>
@@ -5283,7 +5290,7 @@
       <c r="A184" t="s">
         <v>830</v>
       </c>
-      <c r="B184" s="27" t="s">
+      <c r="B184" s="26" t="s">
         <v>185</v>
       </c>
     </row>
@@ -5291,7 +5298,7 @@
       <c r="A185" t="s">
         <v>830</v>
       </c>
-      <c r="B185" s="27" t="s">
+      <c r="B185" s="26" t="s">
         <v>186</v>
       </c>
     </row>
@@ -5299,7 +5306,7 @@
       <c r="A186" t="s">
         <v>830</v>
       </c>
-      <c r="B186" s="27" t="s">
+      <c r="B186" s="26" t="s">
         <v>187</v>
       </c>
     </row>
@@ -5307,7 +5314,7 @@
       <c r="A187" t="s">
         <v>830</v>
       </c>
-      <c r="B187" s="27" t="s">
+      <c r="B187" s="26" t="s">
         <v>188</v>
       </c>
     </row>
@@ -5315,7 +5322,7 @@
       <c r="A188" t="s">
         <v>830</v>
       </c>
-      <c r="B188" s="27" t="s">
+      <c r="B188" s="26" t="s">
         <v>189</v>
       </c>
     </row>
@@ -5323,7 +5330,7 @@
       <c r="A189" t="s">
         <v>830</v>
       </c>
-      <c r="B189" s="27" t="s">
+      <c r="B189" s="26" t="s">
         <v>190</v>
       </c>
     </row>
@@ -5331,7 +5338,7 @@
       <c r="A190" t="s">
         <v>830</v>
       </c>
-      <c r="B190" s="27" t="s">
+      <c r="B190" s="26" t="s">
         <v>191</v>
       </c>
     </row>
@@ -5339,7 +5346,7 @@
       <c r="A191" t="s">
         <v>830</v>
       </c>
-      <c r="B191" s="27" t="s">
+      <c r="B191" s="26" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5347,7 +5354,7 @@
       <c r="A192" t="s">
         <v>830</v>
       </c>
-      <c r="B192" s="27" t="s">
+      <c r="B192" s="26" t="s">
         <v>193</v>
       </c>
     </row>
@@ -5355,7 +5362,7 @@
       <c r="A193" t="s">
         <v>830</v>
       </c>
-      <c r="B193" s="27" t="s">
+      <c r="B193" s="26" t="s">
         <v>194</v>
       </c>
     </row>
@@ -5363,7 +5370,7 @@
       <c r="A194" t="s">
         <v>830</v>
       </c>
-      <c r="B194" s="27" t="s">
+      <c r="B194" s="26" t="s">
         <v>195</v>
       </c>
     </row>
@@ -5371,7 +5378,7 @@
       <c r="A195" t="s">
         <v>830</v>
       </c>
-      <c r="B195" s="27" t="s">
+      <c r="B195" s="26" t="s">
         <v>196</v>
       </c>
     </row>
@@ -5379,7 +5386,7 @@
       <c r="A196" t="s">
         <v>830</v>
       </c>
-      <c r="B196" s="27" t="s">
+      <c r="B196" s="26" t="s">
         <v>197</v>
       </c>
     </row>
@@ -5387,7 +5394,7 @@
       <c r="A197" t="s">
         <v>830</v>
       </c>
-      <c r="B197" s="27" t="s">
+      <c r="B197" s="26" t="s">
         <v>3</v>
       </c>
     </row>
@@ -5395,7 +5402,7 @@
       <c r="A198" t="s">
         <v>830</v>
       </c>
-      <c r="B198" s="27" t="s">
+      <c r="B198" s="26" t="s">
         <v>198</v>
       </c>
     </row>
@@ -5403,7 +5410,7 @@
       <c r="A199" t="s">
         <v>830</v>
       </c>
-      <c r="B199" s="27" t="s">
+      <c r="B199" s="26" t="s">
         <v>199</v>
       </c>
     </row>
@@ -5411,7 +5418,7 @@
       <c r="A200" t="s">
         <v>830</v>
       </c>
-      <c r="B200" s="27" t="s">
+      <c r="B200" s="26" t="s">
         <v>200</v>
       </c>
     </row>
@@ -5419,7 +5426,7 @@
       <c r="A201" t="s">
         <v>830</v>
       </c>
-      <c r="B201" s="27" t="s">
+      <c r="B201" s="26" t="s">
         <v>201</v>
       </c>
     </row>
@@ -5427,7 +5434,7 @@
       <c r="A202" t="s">
         <v>830</v>
       </c>
-      <c r="B202" s="27" t="s">
+      <c r="B202" s="26" t="s">
         <v>202</v>
       </c>
     </row>
@@ -5435,7 +5442,7 @@
       <c r="A203" t="s">
         <v>830</v>
       </c>
-      <c r="B203" s="27" t="s">
+      <c r="B203" s="26" t="s">
         <v>203</v>
       </c>
     </row>
@@ -5443,7 +5450,7 @@
       <c r="A204" t="s">
         <v>830</v>
       </c>
-      <c r="B204" s="27" t="s">
+      <c r="B204" s="26" t="s">
         <v>204</v>
       </c>
     </row>
@@ -5451,7 +5458,7 @@
       <c r="A205" t="s">
         <v>830</v>
       </c>
-      <c r="B205" s="27" t="s">
+      <c r="B205" s="26" t="s">
         <v>205</v>
       </c>
     </row>
@@ -5459,7 +5466,7 @@
       <c r="A206" t="s">
         <v>830</v>
       </c>
-      <c r="B206" s="27" t="s">
+      <c r="B206" s="26" t="s">
         <v>206</v>
       </c>
     </row>
@@ -5467,7 +5474,7 @@
       <c r="A207" t="s">
         <v>830</v>
       </c>
-      <c r="B207" s="27" t="s">
+      <c r="B207" s="26" t="s">
         <v>207</v>
       </c>
     </row>
@@ -5475,7 +5482,7 @@
       <c r="A208" t="s">
         <v>830</v>
       </c>
-      <c r="B208" s="27" t="s">
+      <c r="B208" s="26" t="s">
         <v>208</v>
       </c>
     </row>
@@ -5483,7 +5490,7 @@
       <c r="A209" t="s">
         <v>830</v>
       </c>
-      <c r="B209" s="27" t="s">
+      <c r="B209" s="26" t="s">
         <v>209</v>
       </c>
     </row>
@@ -5491,7 +5498,7 @@
       <c r="A210" t="s">
         <v>830</v>
       </c>
-      <c r="B210" s="27" t="s">
+      <c r="B210" s="26" t="s">
         <v>210</v>
       </c>
     </row>
@@ -5499,7 +5506,7 @@
       <c r="A211" t="s">
         <v>830</v>
       </c>
-      <c r="B211" s="28" t="s">
+      <c r="B211" s="27" t="s">
         <v>211</v>
       </c>
     </row>
@@ -5507,7 +5514,7 @@
       <c r="A212" t="s">
         <v>831</v>
       </c>
-      <c r="B212" s="29" t="s">
+      <c r="B212" s="28" t="s">
         <v>212</v>
       </c>
     </row>
@@ -5515,7 +5522,7 @@
       <c r="A213" t="s">
         <v>831</v>
       </c>
-      <c r="B213" s="29" t="s">
+      <c r="B213" s="28" t="s">
         <v>213</v>
       </c>
     </row>
@@ -5523,7 +5530,7 @@
       <c r="A214" t="s">
         <v>831</v>
       </c>
-      <c r="B214" s="29" t="s">
+      <c r="B214" s="28" t="s">
         <v>214</v>
       </c>
     </row>
@@ -5531,7 +5538,7 @@
       <c r="A215" t="s">
         <v>831</v>
       </c>
-      <c r="B215" s="29" t="s">
+      <c r="B215" s="28" t="s">
         <v>215</v>
       </c>
     </row>
@@ -5539,7 +5546,7 @@
       <c r="A216" t="s">
         <v>831</v>
       </c>
-      <c r="B216" s="29" t="s">
+      <c r="B216" s="28" t="s">
         <v>216</v>
       </c>
     </row>
@@ -5547,7 +5554,7 @@
       <c r="A217" t="s">
         <v>831</v>
       </c>
-      <c r="B217" s="29" t="s">
+      <c r="B217" s="28" t="s">
         <v>217</v>
       </c>
     </row>
@@ -5555,7 +5562,7 @@
       <c r="A218" t="s">
         <v>831</v>
       </c>
-      <c r="B218" s="29" t="s">
+      <c r="B218" s="28" t="s">
         <v>218</v>
       </c>
     </row>
@@ -5563,7 +5570,7 @@
       <c r="A219" t="s">
         <v>831</v>
       </c>
-      <c r="B219" s="29" t="s">
+      <c r="B219" s="28" t="s">
         <v>219</v>
       </c>
     </row>
@@ -5571,7 +5578,7 @@
       <c r="A220" t="s">
         <v>831</v>
       </c>
-      <c r="B220" s="29" t="s">
+      <c r="B220" s="28" t="s">
         <v>220</v>
       </c>
     </row>
@@ -5579,7 +5586,7 @@
       <c r="A221" t="s">
         <v>831</v>
       </c>
-      <c r="B221" s="29" t="s">
+      <c r="B221" s="28" t="s">
         <v>221</v>
       </c>
     </row>
@@ -5587,7 +5594,7 @@
       <c r="A222" t="s">
         <v>831</v>
       </c>
-      <c r="B222" s="29" t="s">
+      <c r="B222" s="28" t="s">
         <v>222</v>
       </c>
     </row>
@@ -5595,7 +5602,7 @@
       <c r="A223" t="s">
         <v>831</v>
       </c>
-      <c r="B223" s="29" t="s">
+      <c r="B223" s="28" t="s">
         <v>223</v>
       </c>
     </row>
@@ -5603,7 +5610,7 @@
       <c r="A224" t="s">
         <v>831</v>
       </c>
-      <c r="B224" s="29" t="s">
+      <c r="B224" s="28" t="s">
         <v>224</v>
       </c>
     </row>
@@ -5611,7 +5618,7 @@
       <c r="A225" t="s">
         <v>831</v>
       </c>
-      <c r="B225" s="29" t="s">
+      <c r="B225" s="28" t="s">
         <v>225</v>
       </c>
     </row>
@@ -5619,7 +5626,7 @@
       <c r="A226" t="s">
         <v>831</v>
       </c>
-      <c r="B226" s="29" t="s">
+      <c r="B226" s="28" t="s">
         <v>226</v>
       </c>
     </row>
@@ -5627,7 +5634,7 @@
       <c r="A227" t="s">
         <v>831</v>
       </c>
-      <c r="B227" s="29" t="s">
+      <c r="B227" s="28" t="s">
         <v>227</v>
       </c>
     </row>
@@ -5635,7 +5642,7 @@
       <c r="A228" t="s">
         <v>831</v>
       </c>
-      <c r="B228" s="29" t="s">
+      <c r="B228" s="28" t="s">
         <v>228</v>
       </c>
     </row>
@@ -5643,7 +5650,7 @@
       <c r="A229" t="s">
         <v>831</v>
       </c>
-      <c r="B229" s="29" t="s">
+      <c r="B229" s="28" t="s">
         <v>229</v>
       </c>
     </row>
@@ -5651,7 +5658,7 @@
       <c r="A230" t="s">
         <v>831</v>
       </c>
-      <c r="B230" s="29" t="s">
+      <c r="B230" s="28" t="s">
         <v>230</v>
       </c>
     </row>
@@ -5659,7 +5666,7 @@
       <c r="A231" t="s">
         <v>831</v>
       </c>
-      <c r="B231" s="29" t="s">
+      <c r="B231" s="28" t="s">
         <v>231</v>
       </c>
     </row>
@@ -5667,7 +5674,7 @@
       <c r="A232" t="s">
         <v>831</v>
       </c>
-      <c r="B232" s="29" t="s">
+      <c r="B232" s="28" t="s">
         <v>232</v>
       </c>
     </row>
@@ -5675,7 +5682,7 @@
       <c r="A233" t="s">
         <v>831</v>
       </c>
-      <c r="B233" s="29" t="s">
+      <c r="B233" s="28" t="s">
         <v>233</v>
       </c>
     </row>
@@ -5683,7 +5690,7 @@
       <c r="A234" t="s">
         <v>831</v>
       </c>
-      <c r="B234" s="29" t="s">
+      <c r="B234" s="28" t="s">
         <v>234</v>
       </c>
     </row>
@@ -5691,7 +5698,7 @@
       <c r="A235" t="s">
         <v>831</v>
       </c>
-      <c r="B235" s="29" t="s">
+      <c r="B235" s="28" t="s">
         <v>235</v>
       </c>
     </row>
@@ -5699,7 +5706,7 @@
       <c r="A236" t="s">
         <v>831</v>
       </c>
-      <c r="B236" s="29" t="s">
+      <c r="B236" s="28" t="s">
         <v>236</v>
       </c>
     </row>
@@ -5707,7 +5714,7 @@
       <c r="A237" t="s">
         <v>831</v>
       </c>
-      <c r="B237" s="29" t="s">
+      <c r="B237" s="28" t="s">
         <v>237</v>
       </c>
     </row>
@@ -5715,7 +5722,7 @@
       <c r="A238" t="s">
         <v>831</v>
       </c>
-      <c r="B238" s="29" t="s">
+      <c r="B238" s="28" t="s">
         <v>238</v>
       </c>
     </row>
@@ -5723,7 +5730,7 @@
       <c r="A239" t="s">
         <v>831</v>
       </c>
-      <c r="B239" s="29" t="s">
+      <c r="B239" s="28" t="s">
         <v>239</v>
       </c>
     </row>
@@ -5731,7 +5738,7 @@
       <c r="A240" t="s">
         <v>831</v>
       </c>
-      <c r="B240" s="29" t="s">
+      <c r="B240" s="28" t="s">
         <v>240</v>
       </c>
     </row>
@@ -5739,7 +5746,7 @@
       <c r="A241" t="s">
         <v>831</v>
       </c>
-      <c r="B241" s="29" t="s">
+      <c r="B241" s="28" t="s">
         <v>241</v>
       </c>
     </row>
@@ -5747,7 +5754,7 @@
       <c r="A242" t="s">
         <v>831</v>
       </c>
-      <c r="B242" s="29" t="s">
+      <c r="B242" s="28" t="s">
         <v>242</v>
       </c>
     </row>
@@ -5755,7 +5762,7 @@
       <c r="A243" t="s">
         <v>831</v>
       </c>
-      <c r="B243" s="29" t="s">
+      <c r="B243" s="28" t="s">
         <v>243</v>
       </c>
     </row>
@@ -5763,7 +5770,7 @@
       <c r="A244" t="s">
         <v>831</v>
       </c>
-      <c r="B244" s="29" t="s">
+      <c r="B244" s="28" t="s">
         <v>244</v>
       </c>
     </row>
@@ -5771,7 +5778,7 @@
       <c r="A245" t="s">
         <v>831</v>
       </c>
-      <c r="B245" s="29" t="s">
+      <c r="B245" s="28" t="s">
         <v>245</v>
       </c>
     </row>
@@ -5779,7 +5786,7 @@
       <c r="A246" t="s">
         <v>831</v>
       </c>
-      <c r="B246" s="30" t="s">
+      <c r="B246" s="29" t="s">
         <v>246</v>
       </c>
     </row>
@@ -5787,7 +5794,7 @@
       <c r="A247" t="s">
         <v>829</v>
       </c>
-      <c r="B247" s="25" t="s">
+      <c r="B247" s="24" t="s">
         <v>247</v>
       </c>
     </row>
@@ -5795,7 +5802,7 @@
       <c r="A248" t="s">
         <v>829</v>
       </c>
-      <c r="B248" s="25" t="s">
+      <c r="B248" s="24" t="s">
         <v>248</v>
       </c>
     </row>
@@ -5803,7 +5810,7 @@
       <c r="A249" t="s">
         <v>829</v>
       </c>
-      <c r="B249" s="25" t="s">
+      <c r="B249" s="24" t="s">
         <v>249</v>
       </c>
     </row>
@@ -5811,7 +5818,7 @@
       <c r="A250" t="s">
         <v>829</v>
       </c>
-      <c r="B250" s="25" t="s">
+      <c r="B250" s="24" t="s">
         <v>250</v>
       </c>
     </row>
@@ -5819,7 +5826,7 @@
       <c r="A251" t="s">
         <v>829</v>
       </c>
-      <c r="B251" s="25" t="s">
+      <c r="B251" s="24" t="s">
         <v>251</v>
       </c>
     </row>
@@ -5827,7 +5834,7 @@
       <c r="A252" t="s">
         <v>829</v>
       </c>
-      <c r="B252" s="25" t="s">
+      <c r="B252" s="24" t="s">
         <v>252</v>
       </c>
     </row>
@@ -5835,7 +5842,7 @@
       <c r="A253" t="s">
         <v>829</v>
       </c>
-      <c r="B253" s="25" t="s">
+      <c r="B253" s="24" t="s">
         <v>253</v>
       </c>
     </row>
@@ -5843,7 +5850,7 @@
       <c r="A254" t="s">
         <v>829</v>
       </c>
-      <c r="B254" s="31" t="s">
+      <c r="B254" s="30" t="s">
         <v>254</v>
       </c>
     </row>
@@ -5851,7 +5858,7 @@
       <c r="A255" t="s">
         <v>829</v>
       </c>
-      <c r="B255" s="25" t="s">
+      <c r="B255" s="24" t="s">
         <v>255</v>
       </c>
     </row>
@@ -5859,7 +5866,7 @@
       <c r="A256" t="s">
         <v>829</v>
       </c>
-      <c r="B256" s="25" t="s">
+      <c r="B256" s="24" t="s">
         <v>256</v>
       </c>
     </row>
@@ -5867,7 +5874,7 @@
       <c r="A257" t="s">
         <v>829</v>
       </c>
-      <c r="B257" s="25" t="s">
+      <c r="B257" s="24" t="s">
         <v>257</v>
       </c>
     </row>
@@ -5875,7 +5882,7 @@
       <c r="A258" t="s">
         <v>829</v>
       </c>
-      <c r="B258" s="25" t="s">
+      <c r="B258" s="24" t="s">
         <v>258</v>
       </c>
     </row>
@@ -5883,7 +5890,7 @@
       <c r="A259" t="s">
         <v>829</v>
       </c>
-      <c r="B259" s="25" t="s">
+      <c r="B259" s="24" t="s">
         <v>259</v>
       </c>
     </row>
@@ -5891,7 +5898,7 @@
       <c r="A260" t="s">
         <v>829</v>
       </c>
-      <c r="B260" s="25" t="s">
+      <c r="B260" s="24" t="s">
         <v>260</v>
       </c>
     </row>
@@ -5899,7 +5906,7 @@
       <c r="A261" t="s">
         <v>829</v>
       </c>
-      <c r="B261" s="25" t="s">
+      <c r="B261" s="24" t="s">
         <v>261</v>
       </c>
     </row>
@@ -5907,7 +5914,7 @@
       <c r="A262" t="s">
         <v>829</v>
       </c>
-      <c r="B262" s="25" t="s">
+      <c r="B262" s="24" t="s">
         <v>262</v>
       </c>
     </row>
@@ -5915,7 +5922,7 @@
       <c r="A263" t="s">
         <v>829</v>
       </c>
-      <c r="B263" s="25" t="s">
+      <c r="B263" s="24" t="s">
         <v>263</v>
       </c>
     </row>
@@ -5923,7 +5930,7 @@
       <c r="A264" t="s">
         <v>829</v>
       </c>
-      <c r="B264" s="25" t="s">
+      <c r="B264" s="24" t="s">
         <v>264</v>
       </c>
     </row>
@@ -5931,7 +5938,7 @@
       <c r="A265" t="s">
         <v>829</v>
       </c>
-      <c r="B265" s="25" t="s">
+      <c r="B265" s="24" t="s">
         <v>265</v>
       </c>
     </row>
@@ -5939,7 +5946,7 @@
       <c r="A266" t="s">
         <v>829</v>
       </c>
-      <c r="B266" s="25" t="s">
+      <c r="B266" s="24" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5947,7 +5954,7 @@
       <c r="A267" t="s">
         <v>829</v>
       </c>
-      <c r="B267" s="25" t="s">
+      <c r="B267" s="24" t="s">
         <v>267</v>
       </c>
     </row>
@@ -5955,7 +5962,7 @@
       <c r="A268" t="s">
         <v>829</v>
       </c>
-      <c r="B268" s="25" t="s">
+      <c r="B268" s="24" t="s">
         <v>268</v>
       </c>
     </row>
@@ -5963,7 +5970,7 @@
       <c r="A269" t="s">
         <v>829</v>
       </c>
-      <c r="B269" s="25" t="s">
+      <c r="B269" s="24" t="s">
         <v>269</v>
       </c>
     </row>
@@ -5971,7 +5978,7 @@
       <c r="A270" t="s">
         <v>829</v>
       </c>
-      <c r="B270" s="25" t="s">
+      <c r="B270" s="24" t="s">
         <v>270</v>
       </c>
     </row>
@@ -5979,7 +5986,7 @@
       <c r="A271" t="s">
         <v>829</v>
       </c>
-      <c r="B271" s="25" t="s">
+      <c r="B271" s="24" t="s">
         <v>271</v>
       </c>
     </row>
@@ -5987,7 +5994,7 @@
       <c r="A272" t="s">
         <v>829</v>
       </c>
-      <c r="B272" s="25" t="s">
+      <c r="B272" s="24" t="s">
         <v>272</v>
       </c>
     </row>
@@ -5995,7 +6002,7 @@
       <c r="A273" t="s">
         <v>829</v>
       </c>
-      <c r="B273" s="25" t="s">
+      <c r="B273" s="24" t="s">
         <v>273</v>
       </c>
     </row>
@@ -6003,7 +6010,7 @@
       <c r="A274" t="s">
         <v>829</v>
       </c>
-      <c r="B274" s="25" t="s">
+      <c r="B274" s="24" t="s">
         <v>274</v>
       </c>
     </row>
@@ -6011,7 +6018,7 @@
       <c r="A275" t="s">
         <v>829</v>
       </c>
-      <c r="B275" s="25" t="s">
+      <c r="B275" s="24" t="s">
         <v>275</v>
       </c>
     </row>
@@ -6019,7 +6026,7 @@
       <c r="A276" t="s">
         <v>829</v>
       </c>
-      <c r="B276" s="25" t="s">
+      <c r="B276" s="24" t="s">
         <v>276</v>
       </c>
     </row>
@@ -6027,7 +6034,7 @@
       <c r="A277" t="s">
         <v>829</v>
       </c>
-      <c r="B277" s="25" t="s">
+      <c r="B277" s="24" t="s">
         <v>277</v>
       </c>
     </row>
@@ -6035,7 +6042,7 @@
       <c r="A278" t="s">
         <v>829</v>
       </c>
-      <c r="B278" s="25" t="s">
+      <c r="B278" s="24" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6043,7 +6050,7 @@
       <c r="A279" t="s">
         <v>829</v>
       </c>
-      <c r="B279" s="25" t="s">
+      <c r="B279" s="24" t="s">
         <v>279</v>
       </c>
     </row>
@@ -6051,7 +6058,7 @@
       <c r="A280" t="s">
         <v>829</v>
       </c>
-      <c r="B280" s="25" t="s">
+      <c r="B280" s="24" t="s">
         <v>280</v>
       </c>
     </row>
@@ -6059,7 +6066,7 @@
       <c r="A281" t="s">
         <v>829</v>
       </c>
-      <c r="B281" s="26" t="s">
+      <c r="B281" s="25" t="s">
         <v>281</v>
       </c>
     </row>
@@ -6067,7 +6074,7 @@
       <c r="A282" t="s">
         <v>826</v>
       </c>
-      <c r="B282" s="32" t="s">
+      <c r="B282" s="31" t="s">
         <v>282</v>
       </c>
     </row>
@@ -6075,7 +6082,7 @@
       <c r="A283" t="s">
         <v>826</v>
       </c>
-      <c r="B283" s="33" t="s">
+      <c r="B283" s="32" t="s">
         <v>283</v>
       </c>
     </row>
@@ -6083,7 +6090,7 @@
       <c r="A284" t="s">
         <v>826</v>
       </c>
-      <c r="B284" s="33" t="s">
+      <c r="B284" s="32" t="s">
         <v>284</v>
       </c>
     </row>
@@ -6091,7 +6098,7 @@
       <c r="A285" t="s">
         <v>826</v>
       </c>
-      <c r="B285" s="33" t="s">
+      <c r="B285" s="32" t="s">
         <v>285</v>
       </c>
     </row>
@@ -6099,7 +6106,7 @@
       <c r="A286" t="s">
         <v>826</v>
       </c>
-      <c r="B286" s="33" t="s">
+      <c r="B286" s="32" t="s">
         <v>286</v>
       </c>
     </row>
@@ -6107,7 +6114,7 @@
       <c r="A287" t="s">
         <v>826</v>
       </c>
-      <c r="B287" s="33" t="s">
+      <c r="B287" s="32" t="s">
         <v>287</v>
       </c>
     </row>
@@ -6115,7 +6122,7 @@
       <c r="A288" t="s">
         <v>826</v>
       </c>
-      <c r="B288" s="33" t="s">
+      <c r="B288" s="32" t="s">
         <v>288</v>
       </c>
     </row>
@@ -6123,7 +6130,7 @@
       <c r="A289" t="s">
         <v>826</v>
       </c>
-      <c r="B289" s="33" t="s">
+      <c r="B289" s="32" t="s">
         <v>289</v>
       </c>
     </row>
@@ -6131,7 +6138,7 @@
       <c r="A290" t="s">
         <v>826</v>
       </c>
-      <c r="B290" s="33" t="s">
+      <c r="B290" s="32" t="s">
         <v>290</v>
       </c>
     </row>
@@ -6139,7 +6146,7 @@
       <c r="A291" t="s">
         <v>826</v>
       </c>
-      <c r="B291" s="33" t="s">
+      <c r="B291" s="32" t="s">
         <v>291</v>
       </c>
     </row>
@@ -6147,7 +6154,7 @@
       <c r="A292" t="s">
         <v>826</v>
       </c>
-      <c r="B292" s="33" t="s">
+      <c r="B292" s="32" t="s">
         <v>292</v>
       </c>
     </row>
@@ -6155,7 +6162,7 @@
       <c r="A293" t="s">
         <v>826</v>
       </c>
-      <c r="B293" s="33" t="s">
+      <c r="B293" s="32" t="s">
         <v>293</v>
       </c>
     </row>
@@ -6163,7 +6170,7 @@
       <c r="A294" t="s">
         <v>826</v>
       </c>
-      <c r="B294" s="33" t="s">
+      <c r="B294" s="32" t="s">
         <v>294</v>
       </c>
     </row>
@@ -6171,7 +6178,7 @@
       <c r="A295" t="s">
         <v>826</v>
       </c>
-      <c r="B295" s="33" t="s">
+      <c r="B295" s="32" t="s">
         <v>295</v>
       </c>
     </row>
@@ -6179,7 +6186,7 @@
       <c r="A296" t="s">
         <v>826</v>
       </c>
-      <c r="B296" s="33" t="s">
+      <c r="B296" s="32" t="s">
         <v>296</v>
       </c>
     </row>
@@ -6187,7 +6194,7 @@
       <c r="A297" t="s">
         <v>826</v>
       </c>
-      <c r="B297" s="33" t="s">
+      <c r="B297" s="32" t="s">
         <v>297</v>
       </c>
     </row>
@@ -6195,7 +6202,7 @@
       <c r="A298" t="s">
         <v>826</v>
       </c>
-      <c r="B298" s="33" t="s">
+      <c r="B298" s="32" t="s">
         <v>298</v>
       </c>
     </row>
@@ -6203,7 +6210,7 @@
       <c r="A299" t="s">
         <v>826</v>
       </c>
-      <c r="B299" s="33" t="s">
+      <c r="B299" s="32" t="s">
         <v>299</v>
       </c>
     </row>
@@ -6211,7 +6218,7 @@
       <c r="A300" t="s">
         <v>826</v>
       </c>
-      <c r="B300" s="33" t="s">
+      <c r="B300" s="32" t="s">
         <v>300</v>
       </c>
     </row>
@@ -6219,7 +6226,7 @@
       <c r="A301" t="s">
         <v>826</v>
       </c>
-      <c r="B301" s="33" t="s">
+      <c r="B301" s="32" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6227,7 +6234,7 @@
       <c r="A302" t="s">
         <v>826</v>
       </c>
-      <c r="B302" s="34" t="s">
+      <c r="B302" s="33" t="s">
         <v>302</v>
       </c>
     </row>
@@ -6235,7 +6242,7 @@
       <c r="A303" t="s">
         <v>832</v>
       </c>
-      <c r="B303" s="35" t="s">
+      <c r="B303" s="34" t="s">
         <v>303</v>
       </c>
     </row>
@@ -6243,7 +6250,7 @@
       <c r="A304" t="s">
         <v>832</v>
       </c>
-      <c r="B304" s="35" t="s">
+      <c r="B304" s="34" t="s">
         <v>304</v>
       </c>
     </row>
@@ -6251,7 +6258,7 @@
       <c r="A305" t="s">
         <v>832</v>
       </c>
-      <c r="B305" s="35" t="s">
+      <c r="B305" s="34" t="s">
         <v>305</v>
       </c>
     </row>
@@ -6259,7 +6266,7 @@
       <c r="A306" t="s">
         <v>832</v>
       </c>
-      <c r="B306" s="35" t="s">
+      <c r="B306" s="34" t="s">
         <v>306</v>
       </c>
     </row>
@@ -6267,7 +6274,7 @@
       <c r="A307" t="s">
         <v>832</v>
       </c>
-      <c r="B307" s="35" t="s">
+      <c r="B307" s="34" t="s">
         <v>307</v>
       </c>
     </row>
@@ -6275,7 +6282,7 @@
       <c r="A308" t="s">
         <v>832</v>
       </c>
-      <c r="B308" s="35" t="s">
+      <c r="B308" s="34" t="s">
         <v>308</v>
       </c>
     </row>
@@ -6283,7 +6290,7 @@
       <c r="A309" t="s">
         <v>832</v>
       </c>
-      <c r="B309" s="35" t="s">
+      <c r="B309" s="34" t="s">
         <v>309</v>
       </c>
     </row>
@@ -6291,7 +6298,7 @@
       <c r="A310" t="s">
         <v>832</v>
       </c>
-      <c r="B310" s="35" t="s">
+      <c r="B310" s="34" t="s">
         <v>310</v>
       </c>
     </row>
@@ -6299,7 +6306,7 @@
       <c r="A311" t="s">
         <v>832</v>
       </c>
-      <c r="B311" s="35" t="s">
+      <c r="B311" s="34" t="s">
         <v>311</v>
       </c>
     </row>
@@ -6307,7 +6314,7 @@
       <c r="A312" t="s">
         <v>832</v>
       </c>
-      <c r="B312" s="35" t="s">
+      <c r="B312" s="34" t="s">
         <v>2</v>
       </c>
     </row>
@@ -6315,7 +6322,7 @@
       <c r="A313" t="s">
         <v>832</v>
       </c>
-      <c r="B313" s="35" t="s">
+      <c r="B313" s="34" t="s">
         <v>312</v>
       </c>
     </row>
@@ -6323,7 +6330,7 @@
       <c r="A314" t="s">
         <v>832</v>
       </c>
-      <c r="B314" s="35" t="s">
+      <c r="B314" s="34" t="s">
         <v>313</v>
       </c>
     </row>
@@ -6331,7 +6338,7 @@
       <c r="A315" t="s">
         <v>832</v>
       </c>
-      <c r="B315" s="35" t="s">
+      <c r="B315" s="34" t="s">
         <v>314</v>
       </c>
     </row>
@@ -6339,7 +6346,7 @@
       <c r="A316" t="s">
         <v>832</v>
       </c>
-      <c r="B316" s="35" t="s">
+      <c r="B316" s="34" t="s">
         <v>315</v>
       </c>
     </row>
@@ -6347,7 +6354,7 @@
       <c r="A317" t="s">
         <v>832</v>
       </c>
-      <c r="B317" s="35" t="s">
+      <c r="B317" s="34" t="s">
         <v>316</v>
       </c>
     </row>
@@ -6355,7 +6362,7 @@
       <c r="A318" t="s">
         <v>832</v>
       </c>
-      <c r="B318" s="35" t="s">
+      <c r="B318" s="34" t="s">
         <v>317</v>
       </c>
     </row>
@@ -6363,7 +6370,7 @@
       <c r="A319" t="s">
         <v>832</v>
       </c>
-      <c r="B319" s="35" t="s">
+      <c r="B319" s="34" t="s">
         <v>318</v>
       </c>
     </row>
@@ -6371,7 +6378,7 @@
       <c r="A320" t="s">
         <v>832</v>
       </c>
-      <c r="B320" s="35" t="s">
+      <c r="B320" s="34" t="s">
         <v>319</v>
       </c>
     </row>
@@ -6379,7 +6386,7 @@
       <c r="A321" t="s">
         <v>832</v>
       </c>
-      <c r="B321" s="35" t="s">
+      <c r="B321" s="34" t="s">
         <v>320</v>
       </c>
     </row>
@@ -6387,7 +6394,7 @@
       <c r="A322" t="s">
         <v>832</v>
       </c>
-      <c r="B322" s="35" t="s">
+      <c r="B322" s="34" t="s">
         <v>321</v>
       </c>
     </row>
@@ -6395,7 +6402,7 @@
       <c r="A323" t="s">
         <v>832</v>
       </c>
-      <c r="B323" s="36" t="s">
+      <c r="B323" s="35" t="s">
         <v>322</v>
       </c>
     </row>
@@ -6403,7 +6410,7 @@
       <c r="A324" t="s">
         <v>833</v>
       </c>
-      <c r="B324" s="37" t="s">
+      <c r="B324" s="36" t="s">
         <v>323</v>
       </c>
     </row>
@@ -6411,7 +6418,7 @@
       <c r="A325" t="s">
         <v>833</v>
       </c>
-      <c r="B325" s="37" t="s">
+      <c r="B325" s="36" t="s">
         <v>324</v>
       </c>
     </row>
@@ -6419,7 +6426,7 @@
       <c r="A326" t="s">
         <v>833</v>
       </c>
-      <c r="B326" s="37" t="s">
+      <c r="B326" s="36" t="s">
         <v>325</v>
       </c>
     </row>
@@ -6427,7 +6434,7 @@
       <c r="A327" t="s">
         <v>833</v>
       </c>
-      <c r="B327" s="37" t="s">
+      <c r="B327" s="36" t="s">
         <v>326</v>
       </c>
     </row>
@@ -6435,7 +6442,7 @@
       <c r="A328" t="s">
         <v>833</v>
       </c>
-      <c r="B328" s="37" t="s">
+      <c r="B328" s="36" t="s">
         <v>327</v>
       </c>
     </row>
@@ -6443,7 +6450,7 @@
       <c r="A329" t="s">
         <v>833</v>
       </c>
-      <c r="B329" s="37" t="s">
+      <c r="B329" s="36" t="s">
         <v>328</v>
       </c>
     </row>
@@ -6451,7 +6458,7 @@
       <c r="A330" t="s">
         <v>833</v>
       </c>
-      <c r="B330" s="37" t="s">
+      <c r="B330" s="36" t="s">
         <v>329</v>
       </c>
     </row>
@@ -6459,7 +6466,7 @@
       <c r="A331" t="s">
         <v>833</v>
       </c>
-      <c r="B331" s="37" t="s">
+      <c r="B331" s="36" t="s">
         <v>330</v>
       </c>
     </row>
@@ -6467,7 +6474,7 @@
       <c r="A332" t="s">
         <v>833</v>
       </c>
-      <c r="B332" s="38" t="s">
+      <c r="B332" s="37" t="s">
         <v>331</v>
       </c>
     </row>
@@ -6475,7 +6482,7 @@
       <c r="A333" t="s">
         <v>833</v>
       </c>
-      <c r="B333" s="37" t="s">
+      <c r="B333" s="36" t="s">
         <v>332</v>
       </c>
     </row>
@@ -6483,7 +6490,7 @@
       <c r="A334" t="s">
         <v>833</v>
       </c>
-      <c r="B334" s="37" t="s">
+      <c r="B334" s="36" t="s">
         <v>333</v>
       </c>
     </row>
@@ -6491,7 +6498,7 @@
       <c r="A335" t="s">
         <v>833</v>
       </c>
-      <c r="B335" s="37" t="s">
+      <c r="B335" s="36" t="s">
         <v>334</v>
       </c>
     </row>
@@ -6499,7 +6506,7 @@
       <c r="A336" t="s">
         <v>833</v>
       </c>
-      <c r="B336" s="37" t="s">
+      <c r="B336" s="36" t="s">
         <v>335</v>
       </c>
     </row>
@@ -6507,7 +6514,7 @@
       <c r="A337" t="s">
         <v>833</v>
       </c>
-      <c r="B337" s="37" t="s">
+      <c r="B337" s="36" t="s">
         <v>336</v>
       </c>
     </row>
@@ -6515,7 +6522,7 @@
       <c r="A338" t="s">
         <v>833</v>
       </c>
-      <c r="B338" s="37" t="s">
+      <c r="B338" s="36" t="s">
         <v>337</v>
       </c>
     </row>
@@ -6523,7 +6530,7 @@
       <c r="A339" t="s">
         <v>833</v>
       </c>
-      <c r="B339" s="37" t="s">
+      <c r="B339" s="36" t="s">
         <v>338</v>
       </c>
     </row>
@@ -6531,7 +6538,7 @@
       <c r="A340" t="s">
         <v>833</v>
       </c>
-      <c r="B340" s="37" t="s">
+      <c r="B340" s="36" t="s">
         <v>339</v>
       </c>
     </row>
@@ -6539,7 +6546,7 @@
       <c r="A341" t="s">
         <v>833</v>
       </c>
-      <c r="B341" s="37" t="s">
+      <c r="B341" s="36" t="s">
         <v>340</v>
       </c>
     </row>
@@ -6547,7 +6554,7 @@
       <c r="A342" t="s">
         <v>833</v>
       </c>
-      <c r="B342" s="37" t="s">
+      <c r="B342" s="36" t="s">
         <v>341</v>
       </c>
     </row>
@@ -6555,7 +6562,7 @@
       <c r="A343" t="s">
         <v>833</v>
       </c>
-      <c r="B343" s="37" t="s">
+      <c r="B343" s="36" t="s">
         <v>342</v>
       </c>
     </row>
@@ -6563,7 +6570,7 @@
       <c r="A344" t="s">
         <v>833</v>
       </c>
-      <c r="B344" s="39" t="s">
+      <c r="B344" s="38" t="s">
         <v>343</v>
       </c>
     </row>
@@ -6571,7 +6578,7 @@
       <c r="A345" t="s">
         <v>829</v>
       </c>
-      <c r="B345" s="40" t="s">
+      <c r="B345" s="39" t="s">
         <v>344</v>
       </c>
     </row>
@@ -6579,7 +6586,7 @@
       <c r="A346" t="s">
         <v>829</v>
       </c>
-      <c r="B346" s="40" t="s">
+      <c r="B346" s="39" t="s">
         <v>345</v>
       </c>
     </row>
@@ -6587,7 +6594,7 @@
       <c r="A347" t="s">
         <v>829</v>
       </c>
-      <c r="B347" s="40" t="s">
+      <c r="B347" s="39" t="s">
         <v>346</v>
       </c>
     </row>
@@ -6595,7 +6602,7 @@
       <c r="A348" t="s">
         <v>829</v>
       </c>
-      <c r="B348" s="40" t="s">
+      <c r="B348" s="39" t="s">
         <v>347</v>
       </c>
     </row>
@@ -6603,7 +6610,7 @@
       <c r="A349" t="s">
         <v>829</v>
       </c>
-      <c r="B349" s="40" t="s">
+      <c r="B349" s="39" t="s">
         <v>348</v>
       </c>
     </row>
@@ -6611,7 +6618,7 @@
       <c r="A350" t="s">
         <v>829</v>
       </c>
-      <c r="B350" s="40" t="s">
+      <c r="B350" s="39" t="s">
         <v>349</v>
       </c>
     </row>
@@ -6619,7 +6626,7 @@
       <c r="A351" t="s">
         <v>829</v>
       </c>
-      <c r="B351" s="40" t="s">
+      <c r="B351" s="39" t="s">
         <v>350</v>
       </c>
     </row>
@@ -6627,7 +6634,7 @@
       <c r="A352" t="s">
         <v>829</v>
       </c>
-      <c r="B352" s="40" t="s">
+      <c r="B352" s="39" t="s">
         <v>351</v>
       </c>
     </row>
@@ -6635,7 +6642,7 @@
       <c r="A353" t="s">
         <v>829</v>
       </c>
-      <c r="B353" s="40" t="s">
+      <c r="B353" s="39" t="s">
         <v>352</v>
       </c>
     </row>
@@ -6643,7 +6650,7 @@
       <c r="A354" t="s">
         <v>829</v>
       </c>
-      <c r="B354" s="40" t="s">
+      <c r="B354" s="39" t="s">
         <v>353</v>
       </c>
     </row>
@@ -6651,7 +6658,7 @@
       <c r="A355" t="s">
         <v>829</v>
       </c>
-      <c r="B355" s="40" t="s">
+      <c r="B355" s="39" t="s">
         <v>354</v>
       </c>
     </row>
@@ -6659,7 +6666,7 @@
       <c r="A356" t="s">
         <v>829</v>
       </c>
-      <c r="B356" s="40" t="s">
+      <c r="B356" s="39" t="s">
         <v>355</v>
       </c>
     </row>
@@ -6667,7 +6674,7 @@
       <c r="A357" t="s">
         <v>829</v>
       </c>
-      <c r="B357" s="40" t="s">
+      <c r="B357" s="39" t="s">
         <v>356</v>
       </c>
     </row>
@@ -6675,7 +6682,7 @@
       <c r="A358" t="s">
         <v>829</v>
       </c>
-      <c r="B358" s="40" t="s">
+      <c r="B358" s="39" t="s">
         <v>357</v>
       </c>
     </row>
@@ -6683,7 +6690,7 @@
       <c r="A359" t="s">
         <v>829</v>
       </c>
-      <c r="B359" s="40" t="s">
+      <c r="B359" s="39" t="s">
         <v>358</v>
       </c>
     </row>
@@ -6691,7 +6698,7 @@
       <c r="A360" t="s">
         <v>829</v>
       </c>
-      <c r="B360" s="40" t="s">
+      <c r="B360" s="39" t="s">
         <v>359</v>
       </c>
     </row>
@@ -6699,7 +6706,7 @@
       <c r="A361" t="s">
         <v>829</v>
       </c>
-      <c r="B361" s="40" t="s">
+      <c r="B361" s="39" t="s">
         <v>360</v>
       </c>
     </row>
@@ -6707,7 +6714,7 @@
       <c r="A362" t="s">
         <v>829</v>
       </c>
-      <c r="B362" s="40" t="s">
+      <c r="B362" s="39" t="s">
         <v>361</v>
       </c>
     </row>
@@ -6715,7 +6722,7 @@
       <c r="A363" t="s">
         <v>829</v>
       </c>
-      <c r="B363" s="40" t="s">
+      <c r="B363" s="39" t="s">
         <v>362</v>
       </c>
     </row>
@@ -6723,7 +6730,7 @@
       <c r="A364" t="s">
         <v>829</v>
       </c>
-      <c r="B364" s="40" t="s">
+      <c r="B364" s="39" t="s">
         <v>363</v>
       </c>
     </row>
@@ -6731,7 +6738,7 @@
       <c r="A365" t="s">
         <v>829</v>
       </c>
-      <c r="B365" s="41" t="s">
+      <c r="B365" s="40" t="s">
         <v>364</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m2610025/Desktop/チェックイン/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13B77492-1FDA-E74F-A916-F81ADF8EF9D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD705295-D2B1-A346-BEF5-EEA465B39E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{348E8972-E72E-5A4B-9183-B2C2B4112549}"/>
   </bookViews>
@@ -2727,11 +2727,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="@&quot;(1)&quot;"/>
     <numFmt numFmtId="177" formatCode="@&quot;(2)&quot;"/>
     <numFmt numFmtId="178" formatCode="@&quot;(3)&quot;"/>
-    <numFmt numFmtId="182" formatCode="@&quot;1&quot;"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -3026,7 +3025,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3079,6 +3078,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3150,16 +3152,7 @@
     <xf numFmtId="178" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3793,7 +3786,7 @@
       <c r="A2" t="s">
         <v>826</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="42" t="s">
         <v>834</v>
       </c>
       <c r="C2" s="1"/>
@@ -3802,7 +3795,7 @@
       <c r="A3" t="s">
         <v>826</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="17" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="1"/>
@@ -3811,7 +3804,7 @@
       <c r="A4" t="s">
         <v>826</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="17" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="1"/>
@@ -3820,7 +3813,7 @@
       <c r="A5" t="s">
         <v>826</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="1"/>
@@ -3829,7 +3822,7 @@
       <c r="A6" t="s">
         <v>826</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="17" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="1"/>
@@ -3838,7 +3831,7 @@
       <c r="A7" t="s">
         <v>826</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="17" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="1"/>
@@ -3847,7 +3840,7 @@
       <c r="A8" t="s">
         <v>826</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="17" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="1"/>
@@ -3856,7 +3849,7 @@
       <c r="A9" t="s">
         <v>826</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="17" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="1"/>
@@ -3865,7 +3858,7 @@
       <c r="A10" t="s">
         <v>826</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="17" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="1"/>
@@ -3874,7 +3867,7 @@
       <c r="A11" t="s">
         <v>826</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="1"/>
@@ -3883,7 +3876,7 @@
       <c r="A12" t="s">
         <v>826</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="17" t="s">
         <v>0</v>
       </c>
       <c r="C12" s="1"/>
@@ -3892,7 +3885,7 @@
       <c r="A13" t="s">
         <v>826</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="1"/>
@@ -3901,7 +3894,7 @@
       <c r="A14" t="s">
         <v>826</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="17" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="1"/>
@@ -3910,7 +3903,7 @@
       <c r="A15" t="s">
         <v>826</v>
       </c>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="17" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="1"/>
@@ -3919,7 +3912,7 @@
       <c r="A16" t="s">
         <v>826</v>
       </c>
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="17" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="1"/>
@@ -3928,7 +3921,7 @@
       <c r="A17" t="s">
         <v>826</v>
       </c>
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="17" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="1"/>
@@ -3937,7 +3930,7 @@
       <c r="A18" t="s">
         <v>826</v>
       </c>
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="2"/>
@@ -3946,7 +3939,7 @@
       <c r="A19" t="s">
         <v>826</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="17" t="s">
         <v>22</v>
       </c>
       <c r="C19" s="2"/>
@@ -3955,7 +3948,7 @@
       <c r="A20" t="s">
         <v>826</v>
       </c>
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C20" s="2"/>
@@ -3964,7 +3957,7 @@
       <c r="A21" t="s">
         <v>826</v>
       </c>
-      <c r="B21" s="42" t="s">
+      <c r="B21" s="17" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3"/>
@@ -3973,7 +3966,7 @@
       <c r="A22" t="s">
         <v>826</v>
       </c>
-      <c r="B22" s="42" t="s">
+      <c r="B22" s="17" t="s">
         <v>25</v>
       </c>
     </row>
@@ -3981,7 +3974,7 @@
       <c r="A23" t="s">
         <v>826</v>
       </c>
-      <c r="B23" s="42" t="s">
+      <c r="B23" s="17" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3989,7 +3982,7 @@
       <c r="A24" t="s">
         <v>826</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="17" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3997,7 +3990,7 @@
       <c r="A25" t="s">
         <v>826</v>
       </c>
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="17" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4005,7 +3998,7 @@
       <c r="A26" t="s">
         <v>826</v>
       </c>
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="17" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4013,7 +4006,7 @@
       <c r="A27" t="s">
         <v>826</v>
       </c>
-      <c r="B27" s="42" t="s">
+      <c r="B27" s="17" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4021,7 +4014,7 @@
       <c r="A28" t="s">
         <v>826</v>
       </c>
-      <c r="B28" s="42" t="s">
+      <c r="B28" s="17" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4029,7 +4022,7 @@
       <c r="A29" t="s">
         <v>826</v>
       </c>
-      <c r="B29" s="42" t="s">
+      <c r="B29" s="17" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4037,7 +4030,7 @@
       <c r="A30" t="s">
         <v>826</v>
       </c>
-      <c r="B30" s="42" t="s">
+      <c r="B30" s="17" t="s">
         <v>33</v>
       </c>
     </row>
@@ -4045,7 +4038,7 @@
       <c r="A31" t="s">
         <v>826</v>
       </c>
-      <c r="B31" s="42" t="s">
+      <c r="B31" s="17" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4053,7 +4046,7 @@
       <c r="A32" t="s">
         <v>826</v>
       </c>
-      <c r="B32" s="42" t="s">
+      <c r="B32" s="17" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4061,7 +4054,7 @@
       <c r="A33" t="s">
         <v>826</v>
       </c>
-      <c r="B33" s="42" t="s">
+      <c r="B33" s="17" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4069,7 +4062,7 @@
       <c r="A34" t="s">
         <v>826</v>
       </c>
-      <c r="B34" s="42" t="s">
+      <c r="B34" s="17" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4077,7 +4070,7 @@
       <c r="A35" t="s">
         <v>826</v>
       </c>
-      <c r="B35" s="42" t="s">
+      <c r="B35" s="17" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4085,7 +4078,7 @@
       <c r="A36" t="s">
         <v>826</v>
       </c>
-      <c r="B36" s="44" t="s">
+      <c r="B36" s="19" t="s">
         <v>39</v>
       </c>
     </row>
@@ -4093,7 +4086,7 @@
       <c r="A37" t="s">
         <v>827</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="B37" s="20" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4101,7 +4094,7 @@
       <c r="A38" t="s">
         <v>827</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="20" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4109,7 +4102,7 @@
       <c r="A39" t="s">
         <v>827</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="20" t="s">
         <v>42</v>
       </c>
     </row>
@@ -4117,7 +4110,7 @@
       <c r="A40" t="s">
         <v>827</v>
       </c>
-      <c r="B40" s="19" t="s">
+      <c r="B40" s="20" t="s">
         <v>43</v>
       </c>
     </row>
@@ -4125,7 +4118,7 @@
       <c r="A41" t="s">
         <v>827</v>
       </c>
-      <c r="B41" s="19" t="s">
+      <c r="B41" s="20" t="s">
         <v>44</v>
       </c>
     </row>
@@ -4133,7 +4126,7 @@
       <c r="A42" t="s">
         <v>827</v>
       </c>
-      <c r="B42" s="19" t="s">
+      <c r="B42" s="20" t="s">
         <v>45</v>
       </c>
     </row>
@@ -4141,7 +4134,7 @@
       <c r="A43" t="s">
         <v>827</v>
       </c>
-      <c r="B43" s="19" t="s">
+      <c r="B43" s="20" t="s">
         <v>4</v>
       </c>
       <c r="C43" s="5"/>
@@ -4150,7 +4143,7 @@
       <c r="A44" t="s">
         <v>827</v>
       </c>
-      <c r="B44" s="19" t="s">
+      <c r="B44" s="20" t="s">
         <v>46</v>
       </c>
       <c r="C44" s="5"/>
@@ -4159,7 +4152,7 @@
       <c r="A45" t="s">
         <v>827</v>
       </c>
-      <c r="B45" s="19" t="s">
+      <c r="B45" s="20" t="s">
         <v>47</v>
       </c>
       <c r="C45" s="5"/>
@@ -4168,7 +4161,7 @@
       <c r="A46" t="s">
         <v>827</v>
       </c>
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="20" t="s">
         <v>48</v>
       </c>
       <c r="C46" s="5"/>
@@ -4177,7 +4170,7 @@
       <c r="A47" t="s">
         <v>827</v>
       </c>
-      <c r="B47" s="19" t="s">
+      <c r="B47" s="20" t="s">
         <v>49</v>
       </c>
       <c r="C47" s="5"/>
@@ -4186,7 +4179,7 @@
       <c r="A48" t="s">
         <v>827</v>
       </c>
-      <c r="B48" s="19" t="s">
+      <c r="B48" s="20" t="s">
         <v>50</v>
       </c>
       <c r="C48" s="5"/>
@@ -4195,7 +4188,7 @@
       <c r="A49" t="s">
         <v>827</v>
       </c>
-      <c r="B49" s="19" t="s">
+      <c r="B49" s="20" t="s">
         <v>51</v>
       </c>
       <c r="C49" s="5"/>
@@ -4204,7 +4197,7 @@
       <c r="A50" t="s">
         <v>827</v>
       </c>
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="20" t="s">
         <v>52</v>
       </c>
       <c r="C50" s="5"/>
@@ -4213,7 +4206,7 @@
       <c r="A51" t="s">
         <v>827</v>
       </c>
-      <c r="B51" s="19" t="s">
+      <c r="B51" s="20" t="s">
         <v>53</v>
       </c>
       <c r="C51" s="5"/>
@@ -4222,7 +4215,7 @@
       <c r="A52" t="s">
         <v>827</v>
       </c>
-      <c r="B52" s="19" t="s">
+      <c r="B52" s="20" t="s">
         <v>54</v>
       </c>
       <c r="C52" s="5"/>
@@ -4231,7 +4224,7 @@
       <c r="A53" t="s">
         <v>827</v>
       </c>
-      <c r="B53" s="19" t="s">
+      <c r="B53" s="20" t="s">
         <v>55</v>
       </c>
       <c r="C53" s="5"/>
@@ -4240,7 +4233,7 @@
       <c r="A54" t="s">
         <v>827</v>
       </c>
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="20" t="s">
         <v>56</v>
       </c>
       <c r="C54" s="5"/>
@@ -4249,7 +4242,7 @@
       <c r="A55" t="s">
         <v>827</v>
       </c>
-      <c r="B55" s="19" t="s">
+      <c r="B55" s="20" t="s">
         <v>57</v>
       </c>
       <c r="C55" s="5"/>
@@ -4258,7 +4251,7 @@
       <c r="A56" t="s">
         <v>827</v>
       </c>
-      <c r="B56" s="19" t="s">
+      <c r="B56" s="20" t="s">
         <v>58</v>
       </c>
       <c r="C56" s="5"/>
@@ -4267,7 +4260,7 @@
       <c r="A57" t="s">
         <v>827</v>
       </c>
-      <c r="B57" s="19" t="s">
+      <c r="B57" s="20" t="s">
         <v>59</v>
       </c>
       <c r="C57" s="5"/>
@@ -4276,7 +4269,7 @@
       <c r="A58" t="s">
         <v>827</v>
       </c>
-      <c r="B58" s="19" t="s">
+      <c r="B58" s="20" t="s">
         <v>1</v>
       </c>
       <c r="C58" s="5"/>
@@ -4285,7 +4278,7 @@
       <c r="A59" t="s">
         <v>827</v>
       </c>
-      <c r="B59" s="19" t="s">
+      <c r="B59" s="20" t="s">
         <v>60</v>
       </c>
       <c r="C59" s="5"/>
@@ -4294,7 +4287,7 @@
       <c r="A60" t="s">
         <v>827</v>
       </c>
-      <c r="B60" s="19" t="s">
+      <c r="B60" s="20" t="s">
         <v>61</v>
       </c>
       <c r="C60" s="5"/>
@@ -4303,7 +4296,7 @@
       <c r="A61" t="s">
         <v>827</v>
       </c>
-      <c r="B61" s="19" t="s">
+      <c r="B61" s="20" t="s">
         <v>62</v>
       </c>
       <c r="C61" s="5"/>
@@ -4312,7 +4305,7 @@
       <c r="A62" t="s">
         <v>827</v>
       </c>
-      <c r="B62" s="19" t="s">
+      <c r="B62" s="20" t="s">
         <v>63</v>
       </c>
       <c r="C62" s="5"/>
@@ -4321,7 +4314,7 @@
       <c r="A63" t="s">
         <v>827</v>
       </c>
-      <c r="B63" s="19" t="s">
+      <c r="B63" s="20" t="s">
         <v>64</v>
       </c>
       <c r="C63" s="6"/>
@@ -4330,7 +4323,7 @@
       <c r="A64" t="s">
         <v>827</v>
       </c>
-      <c r="B64" s="19" t="s">
+      <c r="B64" s="20" t="s">
         <v>65</v>
       </c>
     </row>
@@ -4338,7 +4331,7 @@
       <c r="A65" t="s">
         <v>827</v>
       </c>
-      <c r="B65" s="19" t="s">
+      <c r="B65" s="20" t="s">
         <v>66</v>
       </c>
     </row>
@@ -4346,7 +4339,7 @@
       <c r="A66" t="s">
         <v>827</v>
       </c>
-      <c r="B66" s="19" t="s">
+      <c r="B66" s="20" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4354,7 +4347,7 @@
       <c r="A67" t="s">
         <v>827</v>
       </c>
-      <c r="B67" s="19" t="s">
+      <c r="B67" s="20" t="s">
         <v>68</v>
       </c>
     </row>
@@ -4362,7 +4355,7 @@
       <c r="A68" t="s">
         <v>827</v>
       </c>
-      <c r="B68" s="19" t="s">
+      <c r="B68" s="20" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4370,7 +4363,7 @@
       <c r="A69" t="s">
         <v>827</v>
       </c>
-      <c r="B69" s="19" t="s">
+      <c r="B69" s="20" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4378,7 +4371,7 @@
       <c r="A70" t="s">
         <v>827</v>
       </c>
-      <c r="B70" s="19" t="s">
+      <c r="B70" s="20" t="s">
         <v>71</v>
       </c>
     </row>
@@ -4386,7 +4379,7 @@
       <c r="A71" t="s">
         <v>827</v>
       </c>
-      <c r="B71" s="20" t="s">
+      <c r="B71" s="21" t="s">
         <v>72</v>
       </c>
     </row>
@@ -4394,7 +4387,7 @@
       <c r="A72" t="s">
         <v>828</v>
       </c>
-      <c r="B72" s="21" t="s">
+      <c r="B72" s="22" t="s">
         <v>73</v>
       </c>
     </row>
@@ -4402,7 +4395,7 @@
       <c r="A73" t="s">
         <v>828</v>
       </c>
-      <c r="B73" s="21" t="s">
+      <c r="B73" s="22" t="s">
         <v>74</v>
       </c>
     </row>
@@ -4410,7 +4403,7 @@
       <c r="A74" t="s">
         <v>828</v>
       </c>
-      <c r="B74" s="21" t="s">
+      <c r="B74" s="22" t="s">
         <v>75</v>
       </c>
     </row>
@@ -4418,7 +4411,7 @@
       <c r="A75" t="s">
         <v>828</v>
       </c>
-      <c r="B75" s="21" t="s">
+      <c r="B75" s="22" t="s">
         <v>76</v>
       </c>
     </row>
@@ -4426,7 +4419,7 @@
       <c r="A76" t="s">
         <v>828</v>
       </c>
-      <c r="B76" s="21" t="s">
+      <c r="B76" s="22" t="s">
         <v>77</v>
       </c>
     </row>
@@ -4434,7 +4427,7 @@
       <c r="A77" t="s">
         <v>828</v>
       </c>
-      <c r="B77" s="21" t="s">
+      <c r="B77" s="22" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4442,7 +4435,7 @@
       <c r="A78" t="s">
         <v>828</v>
       </c>
-      <c r="B78" s="21" t="s">
+      <c r="B78" s="22" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4450,7 +4443,7 @@
       <c r="A79" t="s">
         <v>828</v>
       </c>
-      <c r="B79" s="21" t="s">
+      <c r="B79" s="22" t="s">
         <v>80</v>
       </c>
     </row>
@@ -4458,7 +4451,7 @@
       <c r="A80" t="s">
         <v>828</v>
       </c>
-      <c r="B80" s="21" t="s">
+      <c r="B80" s="22" t="s">
         <v>81</v>
       </c>
     </row>
@@ -4466,7 +4459,7 @@
       <c r="A81" t="s">
         <v>828</v>
       </c>
-      <c r="B81" s="21" t="s">
+      <c r="B81" s="22" t="s">
         <v>82</v>
       </c>
     </row>
@@ -4474,7 +4467,7 @@
       <c r="A82" t="s">
         <v>828</v>
       </c>
-      <c r="B82" s="21" t="s">
+      <c r="B82" s="22" t="s">
         <v>83</v>
       </c>
     </row>
@@ -4482,7 +4475,7 @@
       <c r="A83" t="s">
         <v>828</v>
       </c>
-      <c r="B83" s="21" t="s">
+      <c r="B83" s="22" t="s">
         <v>84</v>
       </c>
     </row>
@@ -4490,7 +4483,7 @@
       <c r="A84" t="s">
         <v>828</v>
       </c>
-      <c r="B84" s="21" t="s">
+      <c r="B84" s="22" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4498,7 +4491,7 @@
       <c r="A85" t="s">
         <v>828</v>
       </c>
-      <c r="B85" s="21" t="s">
+      <c r="B85" s="22" t="s">
         <v>86</v>
       </c>
     </row>
@@ -4506,7 +4499,7 @@
       <c r="A86" t="s">
         <v>828</v>
       </c>
-      <c r="B86" s="21" t="s">
+      <c r="B86" s="22" t="s">
         <v>87</v>
       </c>
     </row>
@@ -4514,7 +4507,7 @@
       <c r="A87" t="s">
         <v>828</v>
       </c>
-      <c r="B87" s="21" t="s">
+      <c r="B87" s="22" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4522,7 +4515,7 @@
       <c r="A88" t="s">
         <v>828</v>
       </c>
-      <c r="B88" s="21" t="s">
+      <c r="B88" s="22" t="s">
         <v>89</v>
       </c>
     </row>
@@ -4530,7 +4523,7 @@
       <c r="A89" t="s">
         <v>828</v>
       </c>
-      <c r="B89" s="21" t="s">
+      <c r="B89" s="22" t="s">
         <v>90</v>
       </c>
     </row>
@@ -4538,7 +4531,7 @@
       <c r="A90" t="s">
         <v>828</v>
       </c>
-      <c r="B90" s="21" t="s">
+      <c r="B90" s="22" t="s">
         <v>91</v>
       </c>
     </row>
@@ -4546,7 +4539,7 @@
       <c r="A91" t="s">
         <v>828</v>
       </c>
-      <c r="B91" s="21" t="s">
+      <c r="B91" s="22" t="s">
         <v>92</v>
       </c>
     </row>
@@ -4554,7 +4547,7 @@
       <c r="A92" t="s">
         <v>828</v>
       </c>
-      <c r="B92" s="21" t="s">
+      <c r="B92" s="22" t="s">
         <v>93</v>
       </c>
     </row>
@@ -4562,7 +4555,7 @@
       <c r="A93" t="s">
         <v>828</v>
       </c>
-      <c r="B93" s="21" t="s">
+      <c r="B93" s="22" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4570,7 +4563,7 @@
       <c r="A94" t="s">
         <v>828</v>
       </c>
-      <c r="B94" s="21" t="s">
+      <c r="B94" s="22" t="s">
         <v>95</v>
       </c>
     </row>
@@ -4578,7 +4571,7 @@
       <c r="A95" t="s">
         <v>828</v>
       </c>
-      <c r="B95" s="21" t="s">
+      <c r="B95" s="22" t="s">
         <v>96</v>
       </c>
     </row>
@@ -4586,7 +4579,7 @@
       <c r="A96" t="s">
         <v>828</v>
       </c>
-      <c r="B96" s="21" t="s">
+      <c r="B96" s="22" t="s">
         <v>97</v>
       </c>
     </row>
@@ -4594,7 +4587,7 @@
       <c r="A97" t="s">
         <v>828</v>
       </c>
-      <c r="B97" s="21" t="s">
+      <c r="B97" s="22" t="s">
         <v>98</v>
       </c>
     </row>
@@ -4602,7 +4595,7 @@
       <c r="A98" t="s">
         <v>828</v>
       </c>
-      <c r="B98" s="21" t="s">
+      <c r="B98" s="22" t="s">
         <v>99</v>
       </c>
     </row>
@@ -4610,7 +4603,7 @@
       <c r="A99" t="s">
         <v>828</v>
       </c>
-      <c r="B99" s="21" t="s">
+      <c r="B99" s="22" t="s">
         <v>100</v>
       </c>
     </row>
@@ -4618,7 +4611,7 @@
       <c r="A100" t="s">
         <v>828</v>
       </c>
-      <c r="B100" s="21" t="s">
+      <c r="B100" s="22" t="s">
         <v>101</v>
       </c>
     </row>
@@ -4626,7 +4619,7 @@
       <c r="A101" t="s">
         <v>828</v>
       </c>
-      <c r="B101" s="21" t="s">
+      <c r="B101" s="22" t="s">
         <v>102</v>
       </c>
     </row>
@@ -4634,7 +4627,7 @@
       <c r="A102" t="s">
         <v>828</v>
       </c>
-      <c r="B102" s="21" t="s">
+      <c r="B102" s="22" t="s">
         <v>103</v>
       </c>
     </row>
@@ -4642,7 +4635,7 @@
       <c r="A103" t="s">
         <v>828</v>
       </c>
-      <c r="B103" s="21" t="s">
+      <c r="B103" s="22" t="s">
         <v>104</v>
       </c>
     </row>
@@ -4650,7 +4643,7 @@
       <c r="A104" t="s">
         <v>828</v>
       </c>
-      <c r="B104" s="21" t="s">
+      <c r="B104" s="22" t="s">
         <v>105</v>
       </c>
     </row>
@@ -4658,7 +4651,7 @@
       <c r="A105" t="s">
         <v>828</v>
       </c>
-      <c r="B105" s="21" t="s">
+      <c r="B105" s="22" t="s">
         <v>106</v>
       </c>
     </row>
@@ -4666,7 +4659,7 @@
       <c r="A106" t="s">
         <v>828</v>
       </c>
-      <c r="B106" s="22" t="s">
+      <c r="B106" s="23" t="s">
         <v>107</v>
       </c>
     </row>
@@ -4946,7 +4939,7 @@
       <c r="A141" t="s">
         <v>829</v>
       </c>
-      <c r="B141" s="18" t="s">
+      <c r="B141" s="19" t="s">
         <v>142</v>
       </c>
     </row>
@@ -4954,7 +4947,7 @@
       <c r="A142" t="s">
         <v>826</v>
       </c>
-      <c r="B142" s="23" t="s">
+      <c r="B142" s="24" t="s">
         <v>143</v>
       </c>
     </row>
@@ -4962,7 +4955,7 @@
       <c r="A143" t="s">
         <v>826</v>
       </c>
-      <c r="B143" s="24" t="s">
+      <c r="B143" s="25" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4970,7 +4963,7 @@
       <c r="A144" t="s">
         <v>826</v>
       </c>
-      <c r="B144" s="24" t="s">
+      <c r="B144" s="25" t="s">
         <v>145</v>
       </c>
     </row>
@@ -4978,7 +4971,7 @@
       <c r="A145" t="s">
         <v>826</v>
       </c>
-      <c r="B145" s="24" t="s">
+      <c r="B145" s="25" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4986,7 +4979,7 @@
       <c r="A146" t="s">
         <v>826</v>
       </c>
-      <c r="B146" s="24" t="s">
+      <c r="B146" s="25" t="s">
         <v>147</v>
       </c>
     </row>
@@ -4994,7 +4987,7 @@
       <c r="A147" t="s">
         <v>826</v>
       </c>
-      <c r="B147" s="24" t="s">
+      <c r="B147" s="25" t="s">
         <v>148</v>
       </c>
     </row>
@@ -5002,7 +4995,7 @@
       <c r="A148" t="s">
         <v>826</v>
       </c>
-      <c r="B148" s="24" t="s">
+      <c r="B148" s="25" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5010,7 +5003,7 @@
       <c r="A149" t="s">
         <v>826</v>
       </c>
-      <c r="B149" s="24" t="s">
+      <c r="B149" s="25" t="s">
         <v>150</v>
       </c>
     </row>
@@ -5018,7 +5011,7 @@
       <c r="A150" t="s">
         <v>826</v>
       </c>
-      <c r="B150" s="24" t="s">
+      <c r="B150" s="25" t="s">
         <v>151</v>
       </c>
     </row>
@@ -5026,7 +5019,7 @@
       <c r="A151" t="s">
         <v>826</v>
       </c>
-      <c r="B151" s="24" t="s">
+      <c r="B151" s="25" t="s">
         <v>152</v>
       </c>
     </row>
@@ -5034,7 +5027,7 @@
       <c r="A152" t="s">
         <v>826</v>
       </c>
-      <c r="B152" s="24" t="s">
+      <c r="B152" s="25" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5042,7 +5035,7 @@
       <c r="A153" t="s">
         <v>826</v>
       </c>
-      <c r="B153" s="24" t="s">
+      <c r="B153" s="25" t="s">
         <v>154</v>
       </c>
     </row>
@@ -5050,7 +5043,7 @@
       <c r="A154" t="s">
         <v>826</v>
       </c>
-      <c r="B154" s="24" t="s">
+      <c r="B154" s="25" t="s">
         <v>155</v>
       </c>
     </row>
@@ -5058,7 +5051,7 @@
       <c r="A155" t="s">
         <v>826</v>
       </c>
-      <c r="B155" s="24" t="s">
+      <c r="B155" s="25" t="s">
         <v>156</v>
       </c>
     </row>
@@ -5066,7 +5059,7 @@
       <c r="A156" t="s">
         <v>826</v>
       </c>
-      <c r="B156" s="24" t="s">
+      <c r="B156" s="25" t="s">
         <v>157</v>
       </c>
     </row>
@@ -5074,7 +5067,7 @@
       <c r="A157" t="s">
         <v>826</v>
       </c>
-      <c r="B157" s="24" t="s">
+      <c r="B157" s="25" t="s">
         <v>158</v>
       </c>
     </row>
@@ -5082,7 +5075,7 @@
       <c r="A158" t="s">
         <v>826</v>
       </c>
-      <c r="B158" s="24" t="s">
+      <c r="B158" s="25" t="s">
         <v>159</v>
       </c>
     </row>
@@ -5090,7 +5083,7 @@
       <c r="A159" t="s">
         <v>826</v>
       </c>
-      <c r="B159" s="24" t="s">
+      <c r="B159" s="25" t="s">
         <v>160</v>
       </c>
     </row>
@@ -5098,7 +5091,7 @@
       <c r="A160" t="s">
         <v>826</v>
       </c>
-      <c r="B160" s="24" t="s">
+      <c r="B160" s="25" t="s">
         <v>161</v>
       </c>
     </row>
@@ -5106,7 +5099,7 @@
       <c r="A161" t="s">
         <v>826</v>
       </c>
-      <c r="B161" s="24" t="s">
+      <c r="B161" s="25" t="s">
         <v>162</v>
       </c>
     </row>
@@ -5114,7 +5107,7 @@
       <c r="A162" t="s">
         <v>826</v>
       </c>
-      <c r="B162" s="24" t="s">
+      <c r="B162" s="25" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5122,7 +5115,7 @@
       <c r="A163" t="s">
         <v>826</v>
       </c>
-      <c r="B163" s="24" t="s">
+      <c r="B163" s="25" t="s">
         <v>164</v>
       </c>
     </row>
@@ -5130,7 +5123,7 @@
       <c r="A164" t="s">
         <v>826</v>
       </c>
-      <c r="B164" s="24" t="s">
+      <c r="B164" s="25" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5138,7 +5131,7 @@
       <c r="A165" t="s">
         <v>826</v>
       </c>
-      <c r="B165" s="24" t="s">
+      <c r="B165" s="25" t="s">
         <v>166</v>
       </c>
     </row>
@@ -5146,7 +5139,7 @@
       <c r="A166" t="s">
         <v>826</v>
       </c>
-      <c r="B166" s="24" t="s">
+      <c r="B166" s="25" t="s">
         <v>167</v>
       </c>
     </row>
@@ -5154,7 +5147,7 @@
       <c r="A167" t="s">
         <v>826</v>
       </c>
-      <c r="B167" s="24" t="s">
+      <c r="B167" s="25" t="s">
         <v>168</v>
       </c>
     </row>
@@ -5162,7 +5155,7 @@
       <c r="A168" t="s">
         <v>826</v>
       </c>
-      <c r="B168" s="24" t="s">
+      <c r="B168" s="25" t="s">
         <v>169</v>
       </c>
     </row>
@@ -5170,7 +5163,7 @@
       <c r="A169" t="s">
         <v>826</v>
       </c>
-      <c r="B169" s="24" t="s">
+      <c r="B169" s="25" t="s">
         <v>170</v>
       </c>
     </row>
@@ -5178,7 +5171,7 @@
       <c r="A170" t="s">
         <v>826</v>
       </c>
-      <c r="B170" s="24" t="s">
+      <c r="B170" s="25" t="s">
         <v>171</v>
       </c>
     </row>
@@ -5186,7 +5179,7 @@
       <c r="A171" t="s">
         <v>826</v>
       </c>
-      <c r="B171" s="24" t="s">
+      <c r="B171" s="25" t="s">
         <v>172</v>
       </c>
     </row>
@@ -5194,7 +5187,7 @@
       <c r="A172" t="s">
         <v>826</v>
       </c>
-      <c r="B172" s="24" t="s">
+      <c r="B172" s="25" t="s">
         <v>173</v>
       </c>
     </row>
@@ -5202,7 +5195,7 @@
       <c r="A173" t="s">
         <v>826</v>
       </c>
-      <c r="B173" s="24" t="s">
+      <c r="B173" s="25" t="s">
         <v>174</v>
       </c>
     </row>
@@ -5210,7 +5203,7 @@
       <c r="A174" t="s">
         <v>826</v>
       </c>
-      <c r="B174" s="24" t="s">
+      <c r="B174" s="25" t="s">
         <v>175</v>
       </c>
     </row>
@@ -5218,7 +5211,7 @@
       <c r="A175" t="s">
         <v>826</v>
       </c>
-      <c r="B175" s="24" t="s">
+      <c r="B175" s="25" t="s">
         <v>176</v>
       </c>
     </row>
@@ -5226,7 +5219,7 @@
       <c r="A176" t="s">
         <v>826</v>
       </c>
-      <c r="B176" s="25" t="s">
+      <c r="B176" s="26" t="s">
         <v>177</v>
       </c>
     </row>
@@ -5234,7 +5227,7 @@
       <c r="A177" t="s">
         <v>830</v>
       </c>
-      <c r="B177" s="26" t="s">
+      <c r="B177" s="27" t="s">
         <v>178</v>
       </c>
     </row>
@@ -5242,7 +5235,7 @@
       <c r="A178" t="s">
         <v>830</v>
       </c>
-      <c r="B178" s="26" t="s">
+      <c r="B178" s="27" t="s">
         <v>179</v>
       </c>
     </row>
@@ -5250,7 +5243,7 @@
       <c r="A179" t="s">
         <v>830</v>
       </c>
-      <c r="B179" s="26" t="s">
+      <c r="B179" s="27" t="s">
         <v>180</v>
       </c>
     </row>
@@ -5258,7 +5251,7 @@
       <c r="A180" t="s">
         <v>830</v>
       </c>
-      <c r="B180" s="26" t="s">
+      <c r="B180" s="27" t="s">
         <v>181</v>
       </c>
     </row>
@@ -5266,7 +5259,7 @@
       <c r="A181" t="s">
         <v>830</v>
       </c>
-      <c r="B181" s="26" t="s">
+      <c r="B181" s="27" t="s">
         <v>182</v>
       </c>
     </row>
@@ -5274,7 +5267,7 @@
       <c r="A182" t="s">
         <v>830</v>
       </c>
-      <c r="B182" s="26" t="s">
+      <c r="B182" s="27" t="s">
         <v>183</v>
       </c>
     </row>
@@ -5282,7 +5275,7 @@
       <c r="A183" t="s">
         <v>830</v>
       </c>
-      <c r="B183" s="26" t="s">
+      <c r="B183" s="27" t="s">
         <v>184</v>
       </c>
     </row>
@@ -5290,7 +5283,7 @@
       <c r="A184" t="s">
         <v>830</v>
       </c>
-      <c r="B184" s="26" t="s">
+      <c r="B184" s="27" t="s">
         <v>185</v>
       </c>
     </row>
@@ -5298,7 +5291,7 @@
       <c r="A185" t="s">
         <v>830</v>
       </c>
-      <c r="B185" s="26" t="s">
+      <c r="B185" s="27" t="s">
         <v>186</v>
       </c>
     </row>
@@ -5306,7 +5299,7 @@
       <c r="A186" t="s">
         <v>830</v>
       </c>
-      <c r="B186" s="26" t="s">
+      <c r="B186" s="27" t="s">
         <v>187</v>
       </c>
     </row>
@@ -5314,7 +5307,7 @@
       <c r="A187" t="s">
         <v>830</v>
       </c>
-      <c r="B187" s="26" t="s">
+      <c r="B187" s="27" t="s">
         <v>188</v>
       </c>
     </row>
@@ -5322,7 +5315,7 @@
       <c r="A188" t="s">
         <v>830</v>
       </c>
-      <c r="B188" s="26" t="s">
+      <c r="B188" s="27" t="s">
         <v>189</v>
       </c>
     </row>
@@ -5330,7 +5323,7 @@
       <c r="A189" t="s">
         <v>830</v>
       </c>
-      <c r="B189" s="26" t="s">
+      <c r="B189" s="27" t="s">
         <v>190</v>
       </c>
     </row>
@@ -5338,7 +5331,7 @@
       <c r="A190" t="s">
         <v>830</v>
       </c>
-      <c r="B190" s="26" t="s">
+      <c r="B190" s="27" t="s">
         <v>191</v>
       </c>
     </row>
@@ -5346,7 +5339,7 @@
       <c r="A191" t="s">
         <v>830</v>
       </c>
-      <c r="B191" s="26" t="s">
+      <c r="B191" s="27" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5354,7 +5347,7 @@
       <c r="A192" t="s">
         <v>830</v>
       </c>
-      <c r="B192" s="26" t="s">
+      <c r="B192" s="27" t="s">
         <v>193</v>
       </c>
     </row>
@@ -5362,7 +5355,7 @@
       <c r="A193" t="s">
         <v>830</v>
       </c>
-      <c r="B193" s="26" t="s">
+      <c r="B193" s="27" t="s">
         <v>194</v>
       </c>
     </row>
@@ -5370,7 +5363,7 @@
       <c r="A194" t="s">
         <v>830</v>
       </c>
-      <c r="B194" s="26" t="s">
+      <c r="B194" s="27" t="s">
         <v>195</v>
       </c>
     </row>
@@ -5378,7 +5371,7 @@
       <c r="A195" t="s">
         <v>830</v>
       </c>
-      <c r="B195" s="26" t="s">
+      <c r="B195" s="27" t="s">
         <v>196</v>
       </c>
     </row>
@@ -5386,7 +5379,7 @@
       <c r="A196" t="s">
         <v>830</v>
       </c>
-      <c r="B196" s="26" t="s">
+      <c r="B196" s="27" t="s">
         <v>197</v>
       </c>
     </row>
@@ -5394,7 +5387,7 @@
       <c r="A197" t="s">
         <v>830</v>
       </c>
-      <c r="B197" s="26" t="s">
+      <c r="B197" s="27" t="s">
         <v>3</v>
       </c>
     </row>
@@ -5402,7 +5395,7 @@
       <c r="A198" t="s">
         <v>830</v>
       </c>
-      <c r="B198" s="26" t="s">
+      <c r="B198" s="27" t="s">
         <v>198</v>
       </c>
     </row>
@@ -5410,7 +5403,7 @@
       <c r="A199" t="s">
         <v>830</v>
       </c>
-      <c r="B199" s="26" t="s">
+      <c r="B199" s="27" t="s">
         <v>199</v>
       </c>
     </row>
@@ -5418,7 +5411,7 @@
       <c r="A200" t="s">
         <v>830</v>
       </c>
-      <c r="B200" s="26" t="s">
+      <c r="B200" s="27" t="s">
         <v>200</v>
       </c>
     </row>
@@ -5426,7 +5419,7 @@
       <c r="A201" t="s">
         <v>830</v>
       </c>
-      <c r="B201" s="26" t="s">
+      <c r="B201" s="27" t="s">
         <v>201</v>
       </c>
     </row>
@@ -5434,7 +5427,7 @@
       <c r="A202" t="s">
         <v>830</v>
       </c>
-      <c r="B202" s="26" t="s">
+      <c r="B202" s="27" t="s">
         <v>202</v>
       </c>
     </row>
@@ -5442,7 +5435,7 @@
       <c r="A203" t="s">
         <v>830</v>
       </c>
-      <c r="B203" s="26" t="s">
+      <c r="B203" s="27" t="s">
         <v>203</v>
       </c>
     </row>
@@ -5450,7 +5443,7 @@
       <c r="A204" t="s">
         <v>830</v>
       </c>
-      <c r="B204" s="26" t="s">
+      <c r="B204" s="27" t="s">
         <v>204</v>
       </c>
     </row>
@@ -5458,7 +5451,7 @@
       <c r="A205" t="s">
         <v>830</v>
       </c>
-      <c r="B205" s="26" t="s">
+      <c r="B205" s="27" t="s">
         <v>205</v>
       </c>
     </row>
@@ -5466,7 +5459,7 @@
       <c r="A206" t="s">
         <v>830</v>
       </c>
-      <c r="B206" s="26" t="s">
+      <c r="B206" s="27" t="s">
         <v>206</v>
       </c>
     </row>
@@ -5474,7 +5467,7 @@
       <c r="A207" t="s">
         <v>830</v>
       </c>
-      <c r="B207" s="26" t="s">
+      <c r="B207" s="27" t="s">
         <v>207</v>
       </c>
     </row>
@@ -5482,7 +5475,7 @@
       <c r="A208" t="s">
         <v>830</v>
       </c>
-      <c r="B208" s="26" t="s">
+      <c r="B208" s="27" t="s">
         <v>208</v>
       </c>
     </row>
@@ -5490,7 +5483,7 @@
       <c r="A209" t="s">
         <v>830</v>
       </c>
-      <c r="B209" s="26" t="s">
+      <c r="B209" s="27" t="s">
         <v>209</v>
       </c>
     </row>
@@ -5498,7 +5491,7 @@
       <c r="A210" t="s">
         <v>830</v>
       </c>
-      <c r="B210" s="26" t="s">
+      <c r="B210" s="27" t="s">
         <v>210</v>
       </c>
     </row>
@@ -5506,7 +5499,7 @@
       <c r="A211" t="s">
         <v>830</v>
       </c>
-      <c r="B211" s="27" t="s">
+      <c r="B211" s="28" t="s">
         <v>211</v>
       </c>
     </row>
@@ -5514,7 +5507,7 @@
       <c r="A212" t="s">
         <v>831</v>
       </c>
-      <c r="B212" s="28" t="s">
+      <c r="B212" s="29" t="s">
         <v>212</v>
       </c>
     </row>
@@ -5522,7 +5515,7 @@
       <c r="A213" t="s">
         <v>831</v>
       </c>
-      <c r="B213" s="28" t="s">
+      <c r="B213" s="29" t="s">
         <v>213</v>
       </c>
     </row>
@@ -5530,7 +5523,7 @@
       <c r="A214" t="s">
         <v>831</v>
       </c>
-      <c r="B214" s="28" t="s">
+      <c r="B214" s="29" t="s">
         <v>214</v>
       </c>
     </row>
@@ -5538,7 +5531,7 @@
       <c r="A215" t="s">
         <v>831</v>
       </c>
-      <c r="B215" s="28" t="s">
+      <c r="B215" s="29" t="s">
         <v>215</v>
       </c>
     </row>
@@ -5546,7 +5539,7 @@
       <c r="A216" t="s">
         <v>831</v>
       </c>
-      <c r="B216" s="28" t="s">
+      <c r="B216" s="29" t="s">
         <v>216</v>
       </c>
     </row>
@@ -5554,7 +5547,7 @@
       <c r="A217" t="s">
         <v>831</v>
       </c>
-      <c r="B217" s="28" t="s">
+      <c r="B217" s="29" t="s">
         <v>217</v>
       </c>
     </row>
@@ -5562,7 +5555,7 @@
       <c r="A218" t="s">
         <v>831</v>
       </c>
-      <c r="B218" s="28" t="s">
+      <c r="B218" s="29" t="s">
         <v>218</v>
       </c>
     </row>
@@ -5570,7 +5563,7 @@
       <c r="A219" t="s">
         <v>831</v>
       </c>
-      <c r="B219" s="28" t="s">
+      <c r="B219" s="29" t="s">
         <v>219</v>
       </c>
     </row>
@@ -5578,7 +5571,7 @@
       <c r="A220" t="s">
         <v>831</v>
       </c>
-      <c r="B220" s="28" t="s">
+      <c r="B220" s="29" t="s">
         <v>220</v>
       </c>
     </row>
@@ -5586,7 +5579,7 @@
       <c r="A221" t="s">
         <v>831</v>
       </c>
-      <c r="B221" s="28" t="s">
+      <c r="B221" s="29" t="s">
         <v>221</v>
       </c>
     </row>
@@ -5594,7 +5587,7 @@
       <c r="A222" t="s">
         <v>831</v>
       </c>
-      <c r="B222" s="28" t="s">
+      <c r="B222" s="29" t="s">
         <v>222</v>
       </c>
     </row>
@@ -5602,7 +5595,7 @@
       <c r="A223" t="s">
         <v>831</v>
       </c>
-      <c r="B223" s="28" t="s">
+      <c r="B223" s="29" t="s">
         <v>223</v>
       </c>
     </row>
@@ -5610,7 +5603,7 @@
       <c r="A224" t="s">
         <v>831</v>
       </c>
-      <c r="B224" s="28" t="s">
+      <c r="B224" s="29" t="s">
         <v>224</v>
       </c>
     </row>
@@ -5618,7 +5611,7 @@
       <c r="A225" t="s">
         <v>831</v>
       </c>
-      <c r="B225" s="28" t="s">
+      <c r="B225" s="29" t="s">
         <v>225</v>
       </c>
     </row>
@@ -5626,7 +5619,7 @@
       <c r="A226" t="s">
         <v>831</v>
       </c>
-      <c r="B226" s="28" t="s">
+      <c r="B226" s="29" t="s">
         <v>226</v>
       </c>
     </row>
@@ -5634,7 +5627,7 @@
       <c r="A227" t="s">
         <v>831</v>
       </c>
-      <c r="B227" s="28" t="s">
+      <c r="B227" s="29" t="s">
         <v>227</v>
       </c>
     </row>
@@ -5642,7 +5635,7 @@
       <c r="A228" t="s">
         <v>831</v>
       </c>
-      <c r="B228" s="28" t="s">
+      <c r="B228" s="29" t="s">
         <v>228</v>
       </c>
     </row>
@@ -5650,7 +5643,7 @@
       <c r="A229" t="s">
         <v>831</v>
       </c>
-      <c r="B229" s="28" t="s">
+      <c r="B229" s="29" t="s">
         <v>229</v>
       </c>
     </row>
@@ -5658,7 +5651,7 @@
       <c r="A230" t="s">
         <v>831</v>
       </c>
-      <c r="B230" s="28" t="s">
+      <c r="B230" s="29" t="s">
         <v>230</v>
       </c>
     </row>
@@ -5666,7 +5659,7 @@
       <c r="A231" t="s">
         <v>831</v>
       </c>
-      <c r="B231" s="28" t="s">
+      <c r="B231" s="29" t="s">
         <v>231</v>
       </c>
     </row>
@@ -5674,7 +5667,7 @@
       <c r="A232" t="s">
         <v>831</v>
       </c>
-      <c r="B232" s="28" t="s">
+      <c r="B232" s="29" t="s">
         <v>232</v>
       </c>
     </row>
@@ -5682,7 +5675,7 @@
       <c r="A233" t="s">
         <v>831</v>
       </c>
-      <c r="B233" s="28" t="s">
+      <c r="B233" s="29" t="s">
         <v>233</v>
       </c>
     </row>
@@ -5690,7 +5683,7 @@
       <c r="A234" t="s">
         <v>831</v>
       </c>
-      <c r="B234" s="28" t="s">
+      <c r="B234" s="29" t="s">
         <v>234</v>
       </c>
     </row>
@@ -5698,7 +5691,7 @@
       <c r="A235" t="s">
         <v>831</v>
       </c>
-      <c r="B235" s="28" t="s">
+      <c r="B235" s="29" t="s">
         <v>235</v>
       </c>
     </row>
@@ -5706,7 +5699,7 @@
       <c r="A236" t="s">
         <v>831</v>
       </c>
-      <c r="B236" s="28" t="s">
+      <c r="B236" s="29" t="s">
         <v>236</v>
       </c>
     </row>
@@ -5714,7 +5707,7 @@
       <c r="A237" t="s">
         <v>831</v>
       </c>
-      <c r="B237" s="28" t="s">
+      <c r="B237" s="29" t="s">
         <v>237</v>
       </c>
     </row>
@@ -5722,7 +5715,7 @@
       <c r="A238" t="s">
         <v>831</v>
       </c>
-      <c r="B238" s="28" t="s">
+      <c r="B238" s="29" t="s">
         <v>238</v>
       </c>
     </row>
@@ -5730,7 +5723,7 @@
       <c r="A239" t="s">
         <v>831</v>
       </c>
-      <c r="B239" s="28" t="s">
+      <c r="B239" s="29" t="s">
         <v>239</v>
       </c>
     </row>
@@ -5738,7 +5731,7 @@
       <c r="A240" t="s">
         <v>831</v>
       </c>
-      <c r="B240" s="28" t="s">
+      <c r="B240" s="29" t="s">
         <v>240</v>
       </c>
     </row>
@@ -5746,7 +5739,7 @@
       <c r="A241" t="s">
         <v>831</v>
       </c>
-      <c r="B241" s="28" t="s">
+      <c r="B241" s="29" t="s">
         <v>241</v>
       </c>
     </row>
@@ -5754,7 +5747,7 @@
       <c r="A242" t="s">
         <v>831</v>
       </c>
-      <c r="B242" s="28" t="s">
+      <c r="B242" s="29" t="s">
         <v>242</v>
       </c>
     </row>
@@ -5762,7 +5755,7 @@
       <c r="A243" t="s">
         <v>831</v>
       </c>
-      <c r="B243" s="28" t="s">
+      <c r="B243" s="29" t="s">
         <v>243</v>
       </c>
     </row>
@@ -5770,7 +5763,7 @@
       <c r="A244" t="s">
         <v>831</v>
       </c>
-      <c r="B244" s="28" t="s">
+      <c r="B244" s="29" t="s">
         <v>244</v>
       </c>
     </row>
@@ -5778,7 +5771,7 @@
       <c r="A245" t="s">
         <v>831</v>
       </c>
-      <c r="B245" s="28" t="s">
+      <c r="B245" s="29" t="s">
         <v>245</v>
       </c>
     </row>
@@ -5786,7 +5779,7 @@
       <c r="A246" t="s">
         <v>831</v>
       </c>
-      <c r="B246" s="29" t="s">
+      <c r="B246" s="30" t="s">
         <v>246</v>
       </c>
     </row>
@@ -5794,7 +5787,7 @@
       <c r="A247" t="s">
         <v>829</v>
       </c>
-      <c r="B247" s="24" t="s">
+      <c r="B247" s="25" t="s">
         <v>247</v>
       </c>
     </row>
@@ -5802,7 +5795,7 @@
       <c r="A248" t="s">
         <v>829</v>
       </c>
-      <c r="B248" s="24" t="s">
+      <c r="B248" s="25" t="s">
         <v>248</v>
       </c>
     </row>
@@ -5810,7 +5803,7 @@
       <c r="A249" t="s">
         <v>829</v>
       </c>
-      <c r="B249" s="24" t="s">
+      <c r="B249" s="25" t="s">
         <v>249</v>
       </c>
     </row>
@@ -5818,7 +5811,7 @@
       <c r="A250" t="s">
         <v>829</v>
       </c>
-      <c r="B250" s="24" t="s">
+      <c r="B250" s="25" t="s">
         <v>250</v>
       </c>
     </row>
@@ -5826,7 +5819,7 @@
       <c r="A251" t="s">
         <v>829</v>
       </c>
-      <c r="B251" s="24" t="s">
+      <c r="B251" s="25" t="s">
         <v>251</v>
       </c>
     </row>
@@ -5834,7 +5827,7 @@
       <c r="A252" t="s">
         <v>829</v>
       </c>
-      <c r="B252" s="24" t="s">
+      <c r="B252" s="25" t="s">
         <v>252</v>
       </c>
     </row>
@@ -5842,7 +5835,7 @@
       <c r="A253" t="s">
         <v>829</v>
       </c>
-      <c r="B253" s="24" t="s">
+      <c r="B253" s="25" t="s">
         <v>253</v>
       </c>
     </row>
@@ -5850,7 +5843,7 @@
       <c r="A254" t="s">
         <v>829</v>
       </c>
-      <c r="B254" s="30" t="s">
+      <c r="B254" s="31" t="s">
         <v>254</v>
       </c>
     </row>
@@ -5858,7 +5851,7 @@
       <c r="A255" t="s">
         <v>829</v>
       </c>
-      <c r="B255" s="24" t="s">
+      <c r="B255" s="25" t="s">
         <v>255</v>
       </c>
     </row>
@@ -5866,7 +5859,7 @@
       <c r="A256" t="s">
         <v>829</v>
       </c>
-      <c r="B256" s="24" t="s">
+      <c r="B256" s="25" t="s">
         <v>256</v>
       </c>
     </row>
@@ -5874,7 +5867,7 @@
       <c r="A257" t="s">
         <v>829</v>
       </c>
-      <c r="B257" s="24" t="s">
+      <c r="B257" s="25" t="s">
         <v>257</v>
       </c>
     </row>
@@ -5882,7 +5875,7 @@
       <c r="A258" t="s">
         <v>829</v>
       </c>
-      <c r="B258" s="24" t="s">
+      <c r="B258" s="25" t="s">
         <v>258</v>
       </c>
     </row>
@@ -5890,7 +5883,7 @@
       <c r="A259" t="s">
         <v>829</v>
       </c>
-      <c r="B259" s="24" t="s">
+      <c r="B259" s="25" t="s">
         <v>259</v>
       </c>
     </row>
@@ -5898,7 +5891,7 @@
       <c r="A260" t="s">
         <v>829</v>
       </c>
-      <c r="B260" s="24" t="s">
+      <c r="B260" s="25" t="s">
         <v>260</v>
       </c>
     </row>
@@ -5906,7 +5899,7 @@
       <c r="A261" t="s">
         <v>829</v>
       </c>
-      <c r="B261" s="24" t="s">
+      <c r="B261" s="25" t="s">
         <v>261</v>
       </c>
     </row>
@@ -5914,7 +5907,7 @@
       <c r="A262" t="s">
         <v>829</v>
       </c>
-      <c r="B262" s="24" t="s">
+      <c r="B262" s="25" t="s">
         <v>262</v>
       </c>
     </row>
@@ -5922,7 +5915,7 @@
       <c r="A263" t="s">
         <v>829</v>
       </c>
-      <c r="B263" s="24" t="s">
+      <c r="B263" s="25" t="s">
         <v>263</v>
       </c>
     </row>
@@ -5930,7 +5923,7 @@
       <c r="A264" t="s">
         <v>829</v>
       </c>
-      <c r="B264" s="24" t="s">
+      <c r="B264" s="25" t="s">
         <v>264</v>
       </c>
     </row>
@@ -5938,7 +5931,7 @@
       <c r="A265" t="s">
         <v>829</v>
       </c>
-      <c r="B265" s="24" t="s">
+      <c r="B265" s="25" t="s">
         <v>265</v>
       </c>
     </row>
@@ -5946,7 +5939,7 @@
       <c r="A266" t="s">
         <v>829</v>
       </c>
-      <c r="B266" s="24" t="s">
+      <c r="B266" s="25" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5954,7 +5947,7 @@
       <c r="A267" t="s">
         <v>829</v>
       </c>
-      <c r="B267" s="24" t="s">
+      <c r="B267" s="25" t="s">
         <v>267</v>
       </c>
     </row>
@@ -5962,7 +5955,7 @@
       <c r="A268" t="s">
         <v>829</v>
       </c>
-      <c r="B268" s="24" t="s">
+      <c r="B268" s="25" t="s">
         <v>268</v>
       </c>
     </row>
@@ -5970,7 +5963,7 @@
       <c r="A269" t="s">
         <v>829</v>
       </c>
-      <c r="B269" s="24" t="s">
+      <c r="B269" s="25" t="s">
         <v>269</v>
       </c>
     </row>
@@ -5978,7 +5971,7 @@
       <c r="A270" t="s">
         <v>829</v>
       </c>
-      <c r="B270" s="24" t="s">
+      <c r="B270" s="25" t="s">
         <v>270</v>
       </c>
     </row>
@@ -5986,7 +5979,7 @@
       <c r="A271" t="s">
         <v>829</v>
       </c>
-      <c r="B271" s="24" t="s">
+      <c r="B271" s="25" t="s">
         <v>271</v>
       </c>
     </row>
@@ -5994,7 +5987,7 @@
       <c r="A272" t="s">
         <v>829</v>
       </c>
-      <c r="B272" s="24" t="s">
+      <c r="B272" s="25" t="s">
         <v>272</v>
       </c>
     </row>
@@ -6002,7 +5995,7 @@
       <c r="A273" t="s">
         <v>829</v>
       </c>
-      <c r="B273" s="24" t="s">
+      <c r="B273" s="25" t="s">
         <v>273</v>
       </c>
     </row>
@@ -6010,7 +6003,7 @@
       <c r="A274" t="s">
         <v>829</v>
       </c>
-      <c r="B274" s="24" t="s">
+      <c r="B274" s="25" t="s">
         <v>274</v>
       </c>
     </row>
@@ -6018,7 +6011,7 @@
       <c r="A275" t="s">
         <v>829</v>
       </c>
-      <c r="B275" s="24" t="s">
+      <c r="B275" s="25" t="s">
         <v>275</v>
       </c>
     </row>
@@ -6026,7 +6019,7 @@
       <c r="A276" t="s">
         <v>829</v>
       </c>
-      <c r="B276" s="24" t="s">
+      <c r="B276" s="25" t="s">
         <v>276</v>
       </c>
     </row>
@@ -6034,7 +6027,7 @@
       <c r="A277" t="s">
         <v>829</v>
       </c>
-      <c r="B277" s="24" t="s">
+      <c r="B277" s="25" t="s">
         <v>277</v>
       </c>
     </row>
@@ -6042,7 +6035,7 @@
       <c r="A278" t="s">
         <v>829</v>
       </c>
-      <c r="B278" s="24" t="s">
+      <c r="B278" s="25" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6050,7 +6043,7 @@
       <c r="A279" t="s">
         <v>829</v>
       </c>
-      <c r="B279" s="24" t="s">
+      <c r="B279" s="25" t="s">
         <v>279</v>
       </c>
     </row>
@@ -6058,7 +6051,7 @@
       <c r="A280" t="s">
         <v>829</v>
       </c>
-      <c r="B280" s="24" t="s">
+      <c r="B280" s="25" t="s">
         <v>280</v>
       </c>
     </row>
@@ -6066,7 +6059,7 @@
       <c r="A281" t="s">
         <v>829</v>
       </c>
-      <c r="B281" s="25" t="s">
+      <c r="B281" s="26" t="s">
         <v>281</v>
       </c>
     </row>
@@ -6074,7 +6067,7 @@
       <c r="A282" t="s">
         <v>826</v>
       </c>
-      <c r="B282" s="31" t="s">
+      <c r="B282" s="32" t="s">
         <v>282</v>
       </c>
     </row>
@@ -6082,7 +6075,7 @@
       <c r="A283" t="s">
         <v>826</v>
       </c>
-      <c r="B283" s="32" t="s">
+      <c r="B283" s="33" t="s">
         <v>283</v>
       </c>
     </row>
@@ -6090,7 +6083,7 @@
       <c r="A284" t="s">
         <v>826</v>
       </c>
-      <c r="B284" s="32" t="s">
+      <c r="B284" s="33" t="s">
         <v>284</v>
       </c>
     </row>
@@ -6098,7 +6091,7 @@
       <c r="A285" t="s">
         <v>826</v>
       </c>
-      <c r="B285" s="32" t="s">
+      <c r="B285" s="33" t="s">
         <v>285</v>
       </c>
     </row>
@@ -6106,7 +6099,7 @@
       <c r="A286" t="s">
         <v>826</v>
       </c>
-      <c r="B286" s="32" t="s">
+      <c r="B286" s="33" t="s">
         <v>286</v>
       </c>
     </row>
@@ -6114,7 +6107,7 @@
       <c r="A287" t="s">
         <v>826</v>
       </c>
-      <c r="B287" s="32" t="s">
+      <c r="B287" s="33" t="s">
         <v>287</v>
       </c>
     </row>
@@ -6122,7 +6115,7 @@
       <c r="A288" t="s">
         <v>826</v>
       </c>
-      <c r="B288" s="32" t="s">
+      <c r="B288" s="33" t="s">
         <v>288</v>
       </c>
     </row>
@@ -6130,7 +6123,7 @@
       <c r="A289" t="s">
         <v>826</v>
       </c>
-      <c r="B289" s="32" t="s">
+      <c r="B289" s="33" t="s">
         <v>289</v>
       </c>
     </row>
@@ -6138,7 +6131,7 @@
       <c r="A290" t="s">
         <v>826</v>
       </c>
-      <c r="B290" s="32" t="s">
+      <c r="B290" s="33" t="s">
         <v>290</v>
       </c>
     </row>
@@ -6146,7 +6139,7 @@
       <c r="A291" t="s">
         <v>826</v>
       </c>
-      <c r="B291" s="32" t="s">
+      <c r="B291" s="33" t="s">
         <v>291</v>
       </c>
     </row>
@@ -6154,7 +6147,7 @@
       <c r="A292" t="s">
         <v>826</v>
       </c>
-      <c r="B292" s="32" t="s">
+      <c r="B292" s="33" t="s">
         <v>292</v>
       </c>
     </row>
@@ -6162,7 +6155,7 @@
       <c r="A293" t="s">
         <v>826</v>
       </c>
-      <c r="B293" s="32" t="s">
+      <c r="B293" s="33" t="s">
         <v>293</v>
       </c>
     </row>
@@ -6170,7 +6163,7 @@
       <c r="A294" t="s">
         <v>826</v>
       </c>
-      <c r="B294" s="32" t="s">
+      <c r="B294" s="33" t="s">
         <v>294</v>
       </c>
     </row>
@@ -6178,7 +6171,7 @@
       <c r="A295" t="s">
         <v>826</v>
       </c>
-      <c r="B295" s="32" t="s">
+      <c r="B295" s="33" t="s">
         <v>295</v>
       </c>
     </row>
@@ -6186,7 +6179,7 @@
       <c r="A296" t="s">
         <v>826</v>
       </c>
-      <c r="B296" s="32" t="s">
+      <c r="B296" s="33" t="s">
         <v>296</v>
       </c>
     </row>
@@ -6194,7 +6187,7 @@
       <c r="A297" t="s">
         <v>826</v>
       </c>
-      <c r="B297" s="32" t="s">
+      <c r="B297" s="33" t="s">
         <v>297</v>
       </c>
     </row>
@@ -6202,7 +6195,7 @@
       <c r="A298" t="s">
         <v>826</v>
       </c>
-      <c r="B298" s="32" t="s">
+      <c r="B298" s="33" t="s">
         <v>298</v>
       </c>
     </row>
@@ -6210,7 +6203,7 @@
       <c r="A299" t="s">
         <v>826</v>
       </c>
-      <c r="B299" s="32" t="s">
+      <c r="B299" s="33" t="s">
         <v>299</v>
       </c>
     </row>
@@ -6218,7 +6211,7 @@
       <c r="A300" t="s">
         <v>826</v>
       </c>
-      <c r="B300" s="32" t="s">
+      <c r="B300" s="33" t="s">
         <v>300</v>
       </c>
     </row>
@@ -6226,7 +6219,7 @@
       <c r="A301" t="s">
         <v>826</v>
       </c>
-      <c r="B301" s="32" t="s">
+      <c r="B301" s="33" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6234,7 +6227,7 @@
       <c r="A302" t="s">
         <v>826</v>
       </c>
-      <c r="B302" s="33" t="s">
+      <c r="B302" s="34" t="s">
         <v>302</v>
       </c>
     </row>
@@ -6242,7 +6235,7 @@
       <c r="A303" t="s">
         <v>832</v>
       </c>
-      <c r="B303" s="34" t="s">
+      <c r="B303" s="35" t="s">
         <v>303</v>
       </c>
     </row>
@@ -6250,7 +6243,7 @@
       <c r="A304" t="s">
         <v>832</v>
       </c>
-      <c r="B304" s="34" t="s">
+      <c r="B304" s="35" t="s">
         <v>304</v>
       </c>
     </row>
@@ -6258,7 +6251,7 @@
       <c r="A305" t="s">
         <v>832</v>
       </c>
-      <c r="B305" s="34" t="s">
+      <c r="B305" s="35" t="s">
         <v>305</v>
       </c>
     </row>
@@ -6266,7 +6259,7 @@
       <c r="A306" t="s">
         <v>832</v>
       </c>
-      <c r="B306" s="34" t="s">
+      <c r="B306" s="35" t="s">
         <v>306</v>
       </c>
     </row>
@@ -6274,7 +6267,7 @@
       <c r="A307" t="s">
         <v>832</v>
       </c>
-      <c r="B307" s="34" t="s">
+      <c r="B307" s="35" t="s">
         <v>307</v>
       </c>
     </row>
@@ -6282,7 +6275,7 @@
       <c r="A308" t="s">
         <v>832</v>
       </c>
-      <c r="B308" s="34" t="s">
+      <c r="B308" s="35" t="s">
         <v>308</v>
       </c>
     </row>
@@ -6290,7 +6283,7 @@
       <c r="A309" t="s">
         <v>832</v>
       </c>
-      <c r="B309" s="34" t="s">
+      <c r="B309" s="35" t="s">
         <v>309</v>
       </c>
     </row>
@@ -6298,7 +6291,7 @@
       <c r="A310" t="s">
         <v>832</v>
       </c>
-      <c r="B310" s="34" t="s">
+      <c r="B310" s="35" t="s">
         <v>310</v>
       </c>
     </row>
@@ -6306,7 +6299,7 @@
       <c r="A311" t="s">
         <v>832</v>
       </c>
-      <c r="B311" s="34" t="s">
+      <c r="B311" s="35" t="s">
         <v>311</v>
       </c>
     </row>
@@ -6314,7 +6307,7 @@
       <c r="A312" t="s">
         <v>832</v>
       </c>
-      <c r="B312" s="34" t="s">
+      <c r="B312" s="35" t="s">
         <v>2</v>
       </c>
     </row>
@@ -6322,7 +6315,7 @@
       <c r="A313" t="s">
         <v>832</v>
       </c>
-      <c r="B313" s="34" t="s">
+      <c r="B313" s="35" t="s">
         <v>312</v>
       </c>
     </row>
@@ -6330,7 +6323,7 @@
       <c r="A314" t="s">
         <v>832</v>
       </c>
-      <c r="B314" s="34" t="s">
+      <c r="B314" s="35" t="s">
         <v>313</v>
       </c>
     </row>
@@ -6338,7 +6331,7 @@
       <c r="A315" t="s">
         <v>832</v>
       </c>
-      <c r="B315" s="34" t="s">
+      <c r="B315" s="35" t="s">
         <v>314</v>
       </c>
     </row>
@@ -6346,7 +6339,7 @@
       <c r="A316" t="s">
         <v>832</v>
       </c>
-      <c r="B316" s="34" t="s">
+      <c r="B316" s="35" t="s">
         <v>315</v>
       </c>
     </row>
@@ -6354,7 +6347,7 @@
       <c r="A317" t="s">
         <v>832</v>
       </c>
-      <c r="B317" s="34" t="s">
+      <c r="B317" s="35" t="s">
         <v>316</v>
       </c>
     </row>
@@ -6362,7 +6355,7 @@
       <c r="A318" t="s">
         <v>832</v>
       </c>
-      <c r="B318" s="34" t="s">
+      <c r="B318" s="35" t="s">
         <v>317</v>
       </c>
     </row>
@@ -6370,7 +6363,7 @@
       <c r="A319" t="s">
         <v>832</v>
       </c>
-      <c r="B319" s="34" t="s">
+      <c r="B319" s="35" t="s">
         <v>318</v>
       </c>
     </row>
@@ -6378,7 +6371,7 @@
       <c r="A320" t="s">
         <v>832</v>
       </c>
-      <c r="B320" s="34" t="s">
+      <c r="B320" s="35" t="s">
         <v>319</v>
       </c>
     </row>
@@ -6386,7 +6379,7 @@
       <c r="A321" t="s">
         <v>832</v>
       </c>
-      <c r="B321" s="34" t="s">
+      <c r="B321" s="35" t="s">
         <v>320</v>
       </c>
     </row>
@@ -6394,7 +6387,7 @@
       <c r="A322" t="s">
         <v>832</v>
       </c>
-      <c r="B322" s="34" t="s">
+      <c r="B322" s="35" t="s">
         <v>321</v>
       </c>
     </row>
@@ -6402,7 +6395,7 @@
       <c r="A323" t="s">
         <v>832</v>
       </c>
-      <c r="B323" s="35" t="s">
+      <c r="B323" s="36" t="s">
         <v>322</v>
       </c>
     </row>
@@ -6410,7 +6403,7 @@
       <c r="A324" t="s">
         <v>833</v>
       </c>
-      <c r="B324" s="36" t="s">
+      <c r="B324" s="37" t="s">
         <v>323</v>
       </c>
     </row>
@@ -6418,7 +6411,7 @@
       <c r="A325" t="s">
         <v>833</v>
       </c>
-      <c r="B325" s="36" t="s">
+      <c r="B325" s="37" t="s">
         <v>324</v>
       </c>
     </row>
@@ -6426,7 +6419,7 @@
       <c r="A326" t="s">
         <v>833</v>
       </c>
-      <c r="B326" s="36" t="s">
+      <c r="B326" s="37" t="s">
         <v>325</v>
       </c>
     </row>
@@ -6434,7 +6427,7 @@
       <c r="A327" t="s">
         <v>833</v>
       </c>
-      <c r="B327" s="36" t="s">
+      <c r="B327" s="37" t="s">
         <v>326</v>
       </c>
     </row>
@@ -6442,7 +6435,7 @@
       <c r="A328" t="s">
         <v>833</v>
       </c>
-      <c r="B328" s="36" t="s">
+      <c r="B328" s="37" t="s">
         <v>327</v>
       </c>
     </row>
@@ -6450,7 +6443,7 @@
       <c r="A329" t="s">
         <v>833</v>
       </c>
-      <c r="B329" s="36" t="s">
+      <c r="B329" s="37" t="s">
         <v>328</v>
       </c>
     </row>
@@ -6458,7 +6451,7 @@
       <c r="A330" t="s">
         <v>833</v>
       </c>
-      <c r="B330" s="36" t="s">
+      <c r="B330" s="37" t="s">
         <v>329</v>
       </c>
     </row>
@@ -6466,7 +6459,7 @@
       <c r="A331" t="s">
         <v>833</v>
       </c>
-      <c r="B331" s="36" t="s">
+      <c r="B331" s="37" t="s">
         <v>330</v>
       </c>
     </row>
@@ -6474,7 +6467,7 @@
       <c r="A332" t="s">
         <v>833</v>
       </c>
-      <c r="B332" s="37" t="s">
+      <c r="B332" s="38" t="s">
         <v>331</v>
       </c>
     </row>
@@ -6482,7 +6475,7 @@
       <c r="A333" t="s">
         <v>833</v>
       </c>
-      <c r="B333" s="36" t="s">
+      <c r="B333" s="37" t="s">
         <v>332</v>
       </c>
     </row>
@@ -6490,7 +6483,7 @@
       <c r="A334" t="s">
         <v>833</v>
       </c>
-      <c r="B334" s="36" t="s">
+      <c r="B334" s="37" t="s">
         <v>333</v>
       </c>
     </row>
@@ -6498,7 +6491,7 @@
       <c r="A335" t="s">
         <v>833</v>
       </c>
-      <c r="B335" s="36" t="s">
+      <c r="B335" s="37" t="s">
         <v>334</v>
       </c>
     </row>
@@ -6506,7 +6499,7 @@
       <c r="A336" t="s">
         <v>833</v>
       </c>
-      <c r="B336" s="36" t="s">
+      <c r="B336" s="37" t="s">
         <v>335</v>
       </c>
     </row>
@@ -6514,7 +6507,7 @@
       <c r="A337" t="s">
         <v>833</v>
       </c>
-      <c r="B337" s="36" t="s">
+      <c r="B337" s="37" t="s">
         <v>336</v>
       </c>
     </row>
@@ -6522,7 +6515,7 @@
       <c r="A338" t="s">
         <v>833</v>
       </c>
-      <c r="B338" s="36" t="s">
+      <c r="B338" s="37" t="s">
         <v>337</v>
       </c>
     </row>
@@ -6530,7 +6523,7 @@
       <c r="A339" t="s">
         <v>833</v>
       </c>
-      <c r="B339" s="36" t="s">
+      <c r="B339" s="37" t="s">
         <v>338</v>
       </c>
     </row>
@@ -6538,7 +6531,7 @@
       <c r="A340" t="s">
         <v>833</v>
       </c>
-      <c r="B340" s="36" t="s">
+      <c r="B340" s="37" t="s">
         <v>339</v>
       </c>
     </row>
@@ -6546,7 +6539,7 @@
       <c r="A341" t="s">
         <v>833</v>
       </c>
-      <c r="B341" s="36" t="s">
+      <c r="B341" s="37" t="s">
         <v>340</v>
       </c>
     </row>
@@ -6554,7 +6547,7 @@
       <c r="A342" t="s">
         <v>833</v>
       </c>
-      <c r="B342" s="36" t="s">
+      <c r="B342" s="37" t="s">
         <v>341</v>
       </c>
     </row>
@@ -6562,7 +6555,7 @@
       <c r="A343" t="s">
         <v>833</v>
       </c>
-      <c r="B343" s="36" t="s">
+      <c r="B343" s="37" t="s">
         <v>342</v>
       </c>
     </row>
@@ -6570,7 +6563,7 @@
       <c r="A344" t="s">
         <v>833</v>
       </c>
-      <c r="B344" s="38" t="s">
+      <c r="B344" s="39" t="s">
         <v>343</v>
       </c>
     </row>
@@ -6578,7 +6571,7 @@
       <c r="A345" t="s">
         <v>829</v>
       </c>
-      <c r="B345" s="39" t="s">
+      <c r="B345" s="40" t="s">
         <v>344</v>
       </c>
     </row>
@@ -6586,7 +6579,7 @@
       <c r="A346" t="s">
         <v>829</v>
       </c>
-      <c r="B346" s="39" t="s">
+      <c r="B346" s="40" t="s">
         <v>345</v>
       </c>
     </row>
@@ -6594,7 +6587,7 @@
       <c r="A347" t="s">
         <v>829</v>
       </c>
-      <c r="B347" s="39" t="s">
+      <c r="B347" s="40" t="s">
         <v>346</v>
       </c>
     </row>
@@ -6602,7 +6595,7 @@
       <c r="A348" t="s">
         <v>829</v>
       </c>
-      <c r="B348" s="39" t="s">
+      <c r="B348" s="40" t="s">
         <v>347</v>
       </c>
     </row>
@@ -6610,7 +6603,7 @@
       <c r="A349" t="s">
         <v>829</v>
       </c>
-      <c r="B349" s="39" t="s">
+      <c r="B349" s="40" t="s">
         <v>348</v>
       </c>
     </row>
@@ -6618,7 +6611,7 @@
       <c r="A350" t="s">
         <v>829</v>
       </c>
-      <c r="B350" s="39" t="s">
+      <c r="B350" s="40" t="s">
         <v>349</v>
       </c>
     </row>
@@ -6626,7 +6619,7 @@
       <c r="A351" t="s">
         <v>829</v>
       </c>
-      <c r="B351" s="39" t="s">
+      <c r="B351" s="40" t="s">
         <v>350</v>
       </c>
     </row>
@@ -6634,7 +6627,7 @@
       <c r="A352" t="s">
         <v>829</v>
       </c>
-      <c r="B352" s="39" t="s">
+      <c r="B352" s="40" t="s">
         <v>351</v>
       </c>
     </row>
@@ -6642,7 +6635,7 @@
       <c r="A353" t="s">
         <v>829</v>
       </c>
-      <c r="B353" s="39" t="s">
+      <c r="B353" s="40" t="s">
         <v>352</v>
       </c>
     </row>
@@ -6650,7 +6643,7 @@
       <c r="A354" t="s">
         <v>829</v>
       </c>
-      <c r="B354" s="39" t="s">
+      <c r="B354" s="40" t="s">
         <v>353</v>
       </c>
     </row>
@@ -6658,7 +6651,7 @@
       <c r="A355" t="s">
         <v>829</v>
       </c>
-      <c r="B355" s="39" t="s">
+      <c r="B355" s="40" t="s">
         <v>354</v>
       </c>
     </row>
@@ -6666,7 +6659,7 @@
       <c r="A356" t="s">
         <v>829</v>
       </c>
-      <c r="B356" s="39" t="s">
+      <c r="B356" s="40" t="s">
         <v>355</v>
       </c>
     </row>
@@ -6674,7 +6667,7 @@
       <c r="A357" t="s">
         <v>829</v>
       </c>
-      <c r="B357" s="39" t="s">
+      <c r="B357" s="40" t="s">
         <v>356</v>
       </c>
     </row>
@@ -6682,7 +6675,7 @@
       <c r="A358" t="s">
         <v>829</v>
       </c>
-      <c r="B358" s="39" t="s">
+      <c r="B358" s="40" t="s">
         <v>357</v>
       </c>
     </row>
@@ -6690,7 +6683,7 @@
       <c r="A359" t="s">
         <v>829</v>
       </c>
-      <c r="B359" s="39" t="s">
+      <c r="B359" s="40" t="s">
         <v>358</v>
       </c>
     </row>
@@ -6698,7 +6691,7 @@
       <c r="A360" t="s">
         <v>829</v>
       </c>
-      <c r="B360" s="39" t="s">
+      <c r="B360" s="40" t="s">
         <v>359</v>
       </c>
     </row>
@@ -6706,7 +6699,7 @@
       <c r="A361" t="s">
         <v>829</v>
       </c>
-      <c r="B361" s="39" t="s">
+      <c r="B361" s="40" t="s">
         <v>360</v>
       </c>
     </row>
@@ -6714,7 +6707,7 @@
       <c r="A362" t="s">
         <v>829</v>
       </c>
-      <c r="B362" s="39" t="s">
+      <c r="B362" s="40" t="s">
         <v>361</v>
       </c>
     </row>
@@ -6722,7 +6715,7 @@
       <c r="A363" t="s">
         <v>829</v>
       </c>
-      <c r="B363" s="39" t="s">
+      <c r="B363" s="40" t="s">
         <v>362</v>
       </c>
     </row>
@@ -6730,7 +6723,7 @@
       <c r="A364" t="s">
         <v>829</v>
       </c>
-      <c r="B364" s="39" t="s">
+      <c r="B364" s="40" t="s">
         <v>363</v>
       </c>
     </row>
@@ -6738,7 +6731,7 @@
       <c r="A365" t="s">
         <v>829</v>
       </c>
-      <c r="B365" s="40" t="s">
+      <c r="B365" s="41" t="s">
         <v>364</v>
       </c>
     </row>
